--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-calibration\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06641E14-21DC-4145-949A-E72A3CBD9CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CB3D61-2644-4B08-8BA5-549C12CAEB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10008" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="89">
   <si>
     <t>TTS Transportation Technology Shareweights</t>
   </si>
@@ -275,6 +275,45 @@
   </si>
   <si>
     <t>Max Fraction of Production (dimensionless)</t>
+  </si>
+  <si>
+    <t>Calibration record (2026-09-22)</t>
+  </si>
+  <si>
+    <t>On-road anchors (Data tab columns D-E) rewritten by calibration/steps/03-trans-shareweights/solve_base_year.py:</t>
+  </si>
+  <si>
+    <t>logit inversion at the start year from 'BAU New Vehicle Cost per Mile' in the BAU export and observed technology shares</t>
+  </si>
+  <si>
+    <t>(calibration/benchmarks/vehicle-technology-shares.csv), ZEV-mandate correction for passenger LDVs (3 passes), then the</t>
+  </si>
+  <si>
+    <t>existing s-curve formulas carry the trajectory to the unchanged 2050 targets. Confirmed by a headless run after the third pass.</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr natural gas vehicle: IT-year cell set to =E11 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr gasoline vehicle: IT-year cell set to =E12 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr diesel vehicle: IT-year cell set to =E13 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr plugin hybrid vehicle: 2050 target pinned at its pre-calibration value 0.091009</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr LPG vehicle: IT-year cell set to =E15 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr hydrogen vehicle: IT-year cell set to =E16 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-frgt battery electric vehicle: IT-year cell set to =E17 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-frgt plugin hybrid vehicle: 2050 target pinned at its pre-calibration value 0.00100885</t>
   </si>
 </sst>
 </file>
@@ -1044,18 +1083,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B67"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="63.42578125" customWidth="1"/>
+    <col min="2" max="2" width="63.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1063,193 +1102,258 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B53" s="1"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1266,12 +1370,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -1384,7 +1488,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1497,7 +1601,7 @@
         <v>0.93664816810144857</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1610,7 +1714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1723,7 +1827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1836,7 +1940,7 @@
         <v>6.3351831898551425E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -1949,7 +2053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -2062,7 +2166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2186,12 +2290,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -2304,7 +2408,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -2417,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -2530,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -2643,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -2756,7 +2860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -2869,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -2982,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -3106,12 +3210,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -3224,7 +3328,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -3337,7 +3441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -3450,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -3563,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -3676,7 +3780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -3789,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -3902,7 +4006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -4026,12 +4130,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -4144,7 +4248,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -4257,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -4370,7 +4474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -4483,7 +4587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -4596,7 +4700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -4709,7 +4813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -4822,7 +4926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -4946,12 +5050,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -5064,233 +5168,233 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
       <c r="B2">
         <f>Data!I80</f>
-        <v>0.18123793393000001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="C2">
         <f>Data!J80</f>
-        <v>0.23279812904258823</v>
+        <v>0.20439829056518796</v>
       </c>
       <c r="D2">
         <f>Data!K80</f>
-        <v>0.24933658275197695</v>
+        <v>0.22154895526074969</v>
       </c>
       <c r="E2">
         <f>Data!L80</f>
-        <v>0.2705622726537894</v>
+        <v>0.24356036556758487</v>
       </c>
       <c r="F2">
         <f>Data!M80</f>
-        <v>0.29738020490215311</v>
+        <v>0.27137102863815177</v>
       </c>
       <c r="G2">
         <f>Data!N80</f>
-        <v>0.33060103270559432</v>
+        <v>0.30582160597612668</v>
       </c>
       <c r="H2">
         <f>Data!O80</f>
-        <v>0.37076106043634494</v>
+        <v>0.34746825456114855</v>
       </c>
       <c r="I2">
         <f>Data!P80</f>
-        <v>0.41790151635931294</v>
+        <v>0.39635372882237035</v>
       </c>
       <c r="J2">
         <f>Data!Q80</f>
-        <v>0.47136110874344317</v>
+        <v>0.45179225771102483</v>
       </c>
       <c r="K2">
         <f>Data!R80</f>
-        <v>0.52966825809683538</v>
+        <v>0.5122577876502824</v>
       </c>
       <c r="L2">
         <f>Data!S80</f>
-        <v>0.59061896696500005</v>
+        <v>0.57546473487299998</v>
       </c>
       <c r="M2">
         <f>Data!T80</f>
-        <v>0.65156967583316472</v>
+        <v>0.63867168209571767</v>
       </c>
       <c r="N2">
         <f>Data!U80</f>
-        <v>0.70987682518655681</v>
+        <v>0.69913721203497514</v>
       </c>
       <c r="O2">
         <f>Data!V80</f>
-        <v>0.76333641757068704</v>
+        <v>0.75457574092362967</v>
       </c>
       <c r="P2">
         <f>Data!W80</f>
-        <v>0.81047687349365505</v>
+        <v>0.80346121518485136</v>
       </c>
       <c r="Q2">
         <f>Data!X80</f>
-        <v>0.85063690122440572</v>
+        <v>0.84510786376987324</v>
       </c>
       <c r="R2">
         <f>Data!Y80</f>
-        <v>0.88385772902784698</v>
+        <v>0.87955844110784831</v>
       </c>
       <c r="S2">
         <f>Data!Z80</f>
-        <v>0.91067566127621058</v>
+        <v>0.9073691041784151</v>
       </c>
       <c r="T2">
         <f>Data!AA80</f>
-        <v>0.93190135117802309</v>
+        <v>0.92938051448525039</v>
       </c>
       <c r="U2">
         <f>Data!AB80</f>
-        <v>0.94843980488741186</v>
+        <v>0.94653117918081209</v>
       </c>
       <c r="V2">
         <f>Data!AC80</f>
-        <v>0.96116949409196173</v>
+        <v>0.95973208871336446</v>
       </c>
       <c r="W2">
         <f>Data!AD80</f>
-        <v>0.97087565957856936</v>
+        <v>0.96979755146251745</v>
       </c>
       <c r="X2">
         <f>Data!AE80</f>
-        <v>0.97822339058775476</v>
+        <v>0.97741727656052824</v>
       </c>
       <c r="Y2">
         <f>Data!AF80</f>
-        <v>0.98375551028570629</v>
+        <v>0.98315418108996533</v>
       </c>
       <c r="Z2">
         <f>Data!AG80</f>
-        <v>0.98790358328663208</v>
+        <v>0.98745580507620323</v>
       </c>
       <c r="AA2">
         <f>Data!AH80</f>
-        <v>0.99100430815198304</v>
+        <v>0.990671310794772</v>
       </c>
       <c r="AB2">
         <f>Data!AI80</f>
-        <v>0.99331679637819548</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <v>0.99306940138275057</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
       <c r="B3">
         <f>Data!I81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="C3">
         <f>Data!J81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="D3">
         <f>Data!K81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="E3">
         <f>Data!L81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="F3">
         <f>Data!M81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="G3">
         <f>Data!N81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="H3">
         <f>Data!O81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="I3">
         <f>Data!P81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="J3">
         <f>Data!Q81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="K3">
         <f>Data!R81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="L3">
         <f>Data!S81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="M3">
         <f>Data!T81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="N3">
         <f>Data!U81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="O3">
         <f>Data!V81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="P3">
         <f>Data!W81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Q3">
         <f>Data!X81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="R3">
         <f>Data!Y81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="S3">
         <f>Data!Z81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="T3">
         <f>Data!AA81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="U3">
         <f>Data!AB81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="V3">
         <f>Data!AC81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="W3">
         <f>Data!AD81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="X3">
         <f>Data!AE81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Y3">
         <f>Data!AF81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Z3">
         <f>Data!AG81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AA3">
         <f>Data!AH81</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AB3">
         <f>Data!AI81</f>
-        <v>1.06732008758E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+        <v>1.0695408416000001E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -5403,233 +5507,233 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
       <c r="B5">
         <f>Data!I83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="C5">
         <f>Data!J83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="D5">
         <f>Data!K83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="E5">
         <f>Data!L83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="F5">
         <f>Data!M83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="G5">
         <f>Data!N83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="H5">
         <f>Data!O83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="I5">
         <f>Data!P83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="K5">
         <f>Data!R83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="L5">
         <f>Data!S83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="M5">
         <f>Data!T83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="N5">
         <f>Data!U83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="O5">
         <f>Data!V83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="P5">
         <f>Data!W83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH83</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI83</f>
-        <v>6.7938858436000005E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+        <v>6.7938939010499994E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
       <c r="B6">
         <f>Data!I84</f>
-        <v>1.3970074369600001E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="C6">
         <f>Data!J84</f>
-        <v>1.5110140554321749E-2</v>
+        <v>1.2806537318706219E-2</v>
       </c>
       <c r="D6">
         <f>Data!K84</f>
-        <v>1.550108920235292E-2</v>
+        <v>1.3208673429906077E-2</v>
       </c>
       <c r="E6">
         <f>Data!L84</f>
-        <v>1.6022481838446352E-2</v>
+        <v>1.3744986339907847E-2</v>
       </c>
       <c r="F6">
         <f>Data!M84</f>
-        <v>1.6714992675043627E-2</v>
+        <v>1.4457314202391682E-2</v>
       </c>
       <c r="G6">
         <f>Data!N84</f>
-        <v>1.7629781849127387E-2</v>
+        <v>1.5398281162851517E-2</v>
       </c>
       <c r="H6">
         <f>Data!O84</f>
-        <v>1.8829532862010948E-2</v>
+        <v>1.663236448596514E-2</v>
       </c>
       <c r="I6">
         <f>Data!P84</f>
-        <v>2.0388253288765361E-2</v>
+        <v>1.8235689562083129E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q84</f>
-        <v>2.2388737554300295E-2</v>
+        <v>2.0293420077612576E-2</v>
       </c>
       <c r="K6">
         <f>Data!R84</f>
-        <v>2.4916280910733307E-2</v>
+        <v>2.2893292110330199E-2</v>
       </c>
       <c r="L6">
         <f>Data!S84</f>
-        <v>2.8047286009566623E-2</v>
+        <v>2.611389466499453E-2</v>
       </c>
       <c r="M6">
         <f>Data!T84</f>
-        <v>3.18322986028182E-2</v>
+        <v>3.0007219920774212E-2</v>
       </c>
       <c r="N6">
         <f>Data!U84</f>
-        <v>3.6275204382572757E-2</v>
+        <v>3.4577264763480553E-2</v>
       </c>
       <c r="O6">
         <f>Data!V84</f>
-        <v>4.1313677756162917E-2</v>
+        <v>3.9759920079065703E-2</v>
       </c>
       <c r="P6">
         <f>Data!W84</f>
-        <v>4.6809024922225891E-2</v>
+        <v>4.5412523177152192E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X84</f>
-        <v>5.2553522963420404E-2</v>
+        <v>5.1321406900666118E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y84</f>
-        <v>5.8298021004614918E-2</v>
+        <v>5.7230290624180044E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z84</f>
-        <v>6.3793368170677878E-2</v>
+        <v>6.2882893722266534E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA84</f>
-        <v>6.8831841544268038E-2</v>
+        <v>6.8065549037851683E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB84</f>
-        <v>7.3274747324022602E-2</v>
+        <v>7.2635593880558014E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC84</f>
-        <v>7.7059759917274179E-2</v>
+        <v>7.6528919136337692E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD84</f>
-        <v>8.0190765016107501E-2</v>
+        <v>7.9749521691002051E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE84</f>
-        <v>8.2718308372540517E-2</v>
+        <v>8.234939372371966E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF84</f>
-        <v>8.4718792638075455E-2</v>
+        <v>8.4407124239249121E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG84</f>
-        <v>8.6277513064829864E-2</v>
+        <v>8.601044931536711E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH84</f>
-        <v>8.7477264077713432E-2</v>
+        <v>8.7244532638480726E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI84</f>
-        <v>8.8392053251797179E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+        <v>8.8185499598940564E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -5742,7 +5846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -5866,12 +5970,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -5984,7 +6088,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -6070,7 +6174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -6156,7 +6260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -6242,7 +6346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -6328,7 +6432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -6414,7 +6518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -6500,7 +6604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -6594,18 +6698,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="8" width="23.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" customWidth="1"/>
+    <col min="6" max="8" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -6631,7 +6735,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -6658,7 +6762,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -6686,7 +6790,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="18"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -6712,7 +6816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -6738,7 +6842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -6764,7 +6868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -6790,7 +6894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -6810,20 +6914,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AK93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
     <col min="6" max="6" width="18" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="9" width="9.109375" customWidth="1"/>
+    <col min="14" max="14" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -6852,7 +6956,7 @@
       </c>
       <c r="X1" s="11"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -6887,7 +6991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -6925,7 +7029,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -6963,12 +7067,12 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -6986,7 +7090,7 @@
       <c r="O6" s="16"/>
       <c r="R6" s="19"/>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
@@ -7002,7 +7106,7 @@
       <c r="G7" s="2"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="1:37" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -7015,7 +7119,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>68</v>
       </c>
@@ -7145,7 +7249,7 @@
       <c r="AJ9" s="15"/>
       <c r="AK9" s="15"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -7156,10 +7260,10 @@
         <v>37</v>
       </c>
       <c r="D10">
-        <v>0.18218700570900001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="E10" s="16">
-        <v>0.18123793393000001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -7170,126 +7274,126 @@
       </c>
       <c r="I10">
         <f>D10</f>
-        <v>0.18218700570900001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="J10" s="16">
         <f>E10</f>
-        <v>0.18123793393000001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="K10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,K$9))</f>
-        <v>0.22006843983803839</v>
+        <v>0.19119738103263559</v>
       </c>
       <c r="L10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,L$9))</f>
-        <v>0.23279812904258823</v>
+        <v>0.20439829056518796</v>
       </c>
       <c r="M10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,M$9))</f>
-        <v>0.24933658275197695</v>
+        <v>0.22154895526074969</v>
       </c>
       <c r="N10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,N$9))</f>
-        <v>0.2705622726537894</v>
+        <v>0.24356036556758487</v>
       </c>
       <c r="O10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,O$9))</f>
-        <v>0.29738020490215311</v>
+        <v>0.27137102863815177</v>
       </c>
       <c r="P10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,P$9))</f>
-        <v>0.33060103270559432</v>
+        <v>0.30582160597612668</v>
       </c>
       <c r="Q10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Q$9))</f>
-        <v>0.37076106043634494</v>
+        <v>0.34746825456114855</v>
       </c>
       <c r="R10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,R$9))</f>
-        <v>0.41790151635931294</v>
+        <v>0.39635372882237035</v>
       </c>
       <c r="S10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,S$9))</f>
-        <v>0.47136110874344317</v>
+        <v>0.45179225771102483</v>
       </c>
       <c r="T10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,T$9))</f>
-        <v>0.52966825809683538</v>
+        <v>0.5122577876502824</v>
       </c>
       <c r="U10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,U$9))</f>
-        <v>0.59061896696500005</v>
+        <v>0.57546473487299998</v>
       </c>
       <c r="V10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,V$9))</f>
-        <v>0.65156967583316472</v>
+        <v>0.63867168209571767</v>
       </c>
       <c r="W10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,W$9))</f>
-        <v>0.70987682518655681</v>
+        <v>0.69913721203497514</v>
       </c>
       <c r="X10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,X$9))</f>
-        <v>0.76333641757068704</v>
+        <v>0.75457574092362967</v>
       </c>
       <c r="Y10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Y$9))</f>
-        <v>0.81047687349365505</v>
+        <v>0.80346121518485136</v>
       </c>
       <c r="Z10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Z$9))</f>
-        <v>0.85063690122440572</v>
+        <v>0.84510786376987324</v>
       </c>
       <c r="AA10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AA$9))</f>
-        <v>0.88385772902784698</v>
+        <v>0.87955844110784831</v>
       </c>
       <c r="AB10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AB$9))</f>
-        <v>0.91067566127621058</v>
+        <v>0.9073691041784151</v>
       </c>
       <c r="AC10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AC$9))</f>
-        <v>0.93190135117802309</v>
+        <v>0.92938051448525039</v>
       </c>
       <c r="AD10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AD$9))</f>
-        <v>0.94843980488741186</v>
+        <v>0.94653117918081209</v>
       </c>
       <c r="AE10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AE$9))</f>
-        <v>0.96116949409196173</v>
+        <v>0.95973208871336446</v>
       </c>
       <c r="AF10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AF$9))</f>
-        <v>0.97087565957856936</v>
+        <v>0.96979755146251745</v>
       </c>
       <c r="AG10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AG$9))</f>
-        <v>0.97822339058775476</v>
+        <v>0.97741727656052824</v>
       </c>
       <c r="AH10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AH$9))</f>
-        <v>0.98375551028570629</v>
+        <v>0.98315418108996533</v>
       </c>
       <c r="AI10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AI$9))</f>
-        <v>0.98790358328663208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0.98745580507620323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>38</v>
       </c>
       <c r="D11">
-        <v>1.06995776452E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="E11" s="16">
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="F11" s="16">
         <f>E11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="G11" s="5" t="str">
         <f>IF(E11=F11,"n/a",IF(OR(C11="battery electric vehicle",C11="natural gas vehicle",C11="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -7297,114 +7401,114 @@
       </c>
       <c r="I11" s="16">
         <f>E11</f>
-        <v>1.06732008758E-4</v>
-      </c>
-      <c r="J11">
-        <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,J$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
+      </c>
+      <c r="J11" s="16">
+        <f>E11</f>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="K11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,K$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="L11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,L$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="M11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,M$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="N11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,N$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="O11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,O$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="P11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,P$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Q11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Q$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="R11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,R$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="S11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,S$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="T11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,T$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="U11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,U$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="V11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,V$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="W11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,W$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="X11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,X$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Y11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Y$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Z11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Z$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AA11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AA$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AB11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AB$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AC11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AC$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AD11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AD$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AE11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AE$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AF11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AF$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AG11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AG$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AH11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AH$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AI11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AI$9))</f>
-        <v>1.06732008758E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+        <v>1.0695408416000001E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>39</v>
       </c>
@@ -7426,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <f>IF($G12="s-curve",$E12+($F12-$E12)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E12:$F12,$E$9:$F$9,J$9))</f>
+        <f>E12</f>
         <v>1</v>
       </c>
       <c r="K12">
@@ -7530,19 +7634,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>40</v>
       </c>
       <c r="D13">
-        <v>6.8106756297200005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="E13" s="16">
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="F13" s="16">
         <f>E13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="G13" s="5" t="str">
         <f>IF(E13=F13,"n/a",IF(OR(C13="battery electric vehicle",C13="natural gas vehicle",C13="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -7550,126 +7654,125 @@
       </c>
       <c r="I13" s="16">
         <f>E13</f>
-        <v>6.7938858436000005E-2</v>
-      </c>
-      <c r="J13">
-        <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,J$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
+      </c>
+      <c r="J13" s="16">
+        <f>E13</f>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="K13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,K$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="L13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,L$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="M13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,M$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="N13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,N$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="O13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,O$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="P13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,P$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Q13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Q$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="R13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,R$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="S13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,S$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="T13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,T$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="U13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,U$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="V13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,V$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="W13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,W$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="X13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,X$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Y13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Y$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Z13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Z$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AA13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AA$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AB13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AB$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AC13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AC$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AD13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AD$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AE13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AE$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AF13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AF$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AG13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AG$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AH13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AH$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AI13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AI$9))</f>
-        <v>6.7938858436000005E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+        <v>6.7938939010499994E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>41</v>
       </c>
       <c r="D14">
-        <v>1.6603971957400002E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="E14" s="16">
-        <v>1.3970074369600001E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="F14" s="23">
-        <f>D14/D10*F10</f>
-        <v>9.1136971557240806E-2</v>
+        <v>9.1008967024832244E-2</v>
       </c>
       <c r="G14" s="5" t="str">
         <f>IF(E14=F14,"n/a",IF(OR(C14="battery electric vehicle",C14="natural gas vehicle",C14="plugin hybrid vehicle",C14="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -7677,114 +7780,114 @@
       </c>
       <c r="I14">
         <f>D14</f>
-        <v>1.6603971957400002E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="J14">
         <f>E14</f>
-        <v>1.3970074369600001E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="K14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:K$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,K$9))</f>
-        <v>1.6992371673937554E-2</v>
+        <v>1.4742630733106016E-2</v>
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:L$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>1.8393603157554242E-2</v>
+        <v>1.6183960131609255E-2</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:M$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>2.0388253288765361E-2</v>
+        <v>1.8235689562083126E-2</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:N$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>2.3168593997747108E-2</v>
+        <v>2.109559304595815E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:O$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>2.6932694373384324E-2</v>
+        <v>2.4967407656003776E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:P$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>3.18322986028182E-2</v>
+        <v>3.0007219920774209E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Q$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>3.7893781709970521E-2</v>
+        <v>3.6242159617047354E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:R$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>4.493810244183398E-2</v>
+        <v>4.3488062012213696E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:S$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
-        <v>5.2553522963420404E-2</v>
+        <v>5.1321406900666118E-2</v>
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:T$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>6.0168943485006829E-2</v>
+        <v>5.9154751789118533E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:U$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>6.721326421687028E-2</v>
+        <v>6.6400654184284882E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:V$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>7.3274747324022602E-2</v>
+        <v>7.2635593880558028E-2</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:W$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>7.8174351553456478E-2</v>
+        <v>7.7675406145328446E-2</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:X$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>8.1938451929093686E-2</v>
+        <v>8.1547220755374072E-2</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Y$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>8.4718792638075455E-2</v>
+        <v>8.4407124239249121E-2</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Z$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>8.6713442769286567E-2</v>
+        <v>8.6458853669722974E-2</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AA$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>8.8114674252903258E-2</v>
+        <v>8.7900183068226223E-2</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AB$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>8.908456408839445E-2</v>
+        <v>8.8897827461424384E-2</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AC$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>8.9749031542300767E-2</v>
+        <v>8.9581309446279456E-2</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AD$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>9.0201057861762329E-2</v>
+        <v>9.0046271039531389E-2</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AE$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>9.050709126827812E-2</v>
+        <v>9.0361061958014605E-2</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AF$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>9.0713610894126245E-2</v>
+        <v>9.0573491389970062E-2</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AG$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>9.0852670195706434E-2</v>
+        <v>9.0716530039790799E-2</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AH$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>9.0946166900329001E-2</v>
+        <v>9.0812702264445544E-2</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AI$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>9.1008967024832244E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+        <v>9.0877299489625335E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>42</v>
       </c>
@@ -7806,8 +7909,8 @@
         <f>E15</f>
         <v>0</v>
       </c>
-      <c r="J15">
-        <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,J$9))</f>
+      <c r="J15" s="16">
+        <f>E15</f>
         <v>0</v>
       </c>
       <c r="K15">
@@ -7911,7 +8014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
@@ -7935,8 +8038,8 @@
         <f>E16</f>
         <v>0</v>
       </c>
-      <c r="J16">
-        <f>IF($G16="s-curve",$E16+($F16-$E16)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E16:$F16,$E$9:$F$9,J$9))</f>
+      <c r="J16" s="16">
+        <f>E16</f>
         <v>0</v>
       </c>
       <c r="K16">
@@ -8040,7 +8143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -8068,8 +8171,8 @@
         <v>0.30732944248799998</v>
       </c>
       <c r="J17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:J$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,J$9))</f>
-        <v>0.30713450135322462</v>
+        <f>E17</f>
+        <v>0.30732944248799998</v>
       </c>
       <c r="K17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,K$9))</f>
@@ -8172,7 +8275,7 @@
         <v>0.30014541837982223</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>38</v>
       </c>
@@ -8298,7 +8401,7 @@
         <v>0.59353215226599998</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>39</v>
       </c>
@@ -8425,7 +8528,7 @@
         <v>0.97401567340499995</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>40</v>
       </c>
@@ -8551,7 +8654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>41</v>
       </c>
@@ -8562,8 +8665,7 @@
         <v>1.03300009982E-3</v>
       </c>
       <c r="F21" s="16">
-        <f>E21/E17*F17</f>
-        <v>1.0083642733256849E-3</v>
+        <v>1.0088530556553437E-3</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>74</v>
@@ -8578,106 +8680,106 @@
       </c>
       <c r="K21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,K$9))</f>
-        <v>1.0321237741728829E-3</v>
+        <v>1.0321411607416443E-3</v>
       </c>
       <c r="L21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,L$9))</f>
-        <v>1.0318317242370562E-3</v>
+        <v>1.0318549051658338E-3</v>
       </c>
       <c r="M21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,M$9))</f>
-        <v>1.0314486991464152E-3</v>
+        <v>1.031479479410095E-3</v>
       </c>
       <c r="N21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,N$9))</f>
-        <v>1.0309510717001113E-3</v>
+        <v>1.0309917250444676E-3</v>
       </c>
       <c r="O21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,O$9))</f>
-        <v>1.0303124094619435E-3</v>
+        <v>1.030365734060366E-3</v>
       </c>
       <c r="P21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,P$9))</f>
-        <v>1.0295054815970778E-3</v>
+        <v>1.0295748158910443E-3</v>
       </c>
       <c r="Q21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Q$9))</f>
-        <v>1.028505896267372E-3</v>
+        <v>1.0285950626398874E-3</v>
       </c>
       <c r="R21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,R$9))</f>
-        <v>1.0272975165485478E-3</v>
+        <v>1.0274106575441273E-3</v>
       </c>
       <c r="S21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,S$9))</f>
-        <v>1.025879101918574E-3</v>
+        <v>1.0260203846940701E-3</v>
       </c>
       <c r="T21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,T$9))</f>
-        <v>1.024270550060824E-3</v>
+        <v>1.0244437469969668E-3</v>
       </c>
       <c r="U21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,U$9))</f>
-        <v>1.0225161395008146E-3</v>
+        <v>1.0227241444788512E-3</v>
       </c>
       <c r="V21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,V$9))</f>
-        <v>1.0206821865728424E-3</v>
+        <v>1.0209265777376718E-3</v>
       </c>
       <c r="W21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,W$9))</f>
-        <v>1.0188482336448703E-3</v>
+        <v>1.0191290109964925E-3</v>
       </c>
       <c r="X21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,X$9))</f>
-        <v>1.0170938230848608E-3</v>
+        <v>1.0174094084783769E-3</v>
       </c>
       <c r="Y21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Y$9))</f>
-        <v>1.0154852712271109E-3</v>
+        <v>1.0158327707812736E-3</v>
       </c>
       <c r="Z21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Z$9))</f>
-        <v>1.0140668565971371E-3</v>
+        <v>1.0144424979312164E-3</v>
       </c>
       <c r="AA21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AA$9))</f>
-        <v>1.0128584768783128E-3</v>
+        <v>1.0132580928354563E-3</v>
       </c>
       <c r="AB21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AB$9))</f>
-        <v>1.0118588915486071E-3</v>
+        <v>1.0122783395842994E-3</v>
       </c>
       <c r="AC21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AC$9))</f>
-        <v>1.0110519636837413E-3</v>
+        <v>1.0114874214149777E-3</v>
       </c>
       <c r="AD21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AD$9))</f>
-        <v>1.0104133014455735E-3</v>
+        <v>1.0108614304308761E-3</v>
       </c>
       <c r="AE21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AE$9))</f>
-        <v>1.0099156739992697E-3</v>
+        <v>1.0103736760652487E-3</v>
       </c>
       <c r="AF21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AF$9))</f>
-        <v>1.0095326489086287E-3</v>
+        <v>1.0099982503095099E-3</v>
       </c>
       <c r="AG21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AG$9))</f>
-        <v>1.0092405989728019E-3</v>
+        <v>1.0097119947336994E-3</v>
       </c>
       <c r="AH21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AH$9))</f>
-        <v>1.0090195122447148E-3</v>
+        <v>1.0094952944338913E-3</v>
       </c>
       <c r="AI21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AI$9))</f>
-        <v>1.0088530556553437E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+        <v>1.0093321403941448E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>42</v>
       </c>
@@ -8804,7 +8906,7 @@
         <v>1.3472785756799999E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17" t="s">
@@ -8933,7 +9035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -9065,7 +9167,7 @@
         <v>0.73751575888521737</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>38</v>
       </c>
@@ -9192,7 +9294,7 @@
         <v>1.5317430015500001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>39</v>
       </c>
@@ -9319,7 +9421,7 @@
         <v>0.38138758163300002</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>40</v>
       </c>
@@ -9445,7 +9547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>41</v>
       </c>
@@ -9572,7 +9674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>42</v>
       </c>
@@ -9699,7 +9801,7 @@
         <v>5.5226931821800003E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17" t="s">
@@ -9828,7 +9930,7 @@
         <v>2.0026390066599999E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -9960,7 +10062,7 @@
         <v>0.24513810124032956</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>38</v>
       </c>
@@ -10087,7 +10189,7 @@
         <v>2.32516282526E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>39</v>
       </c>
@@ -10214,7 +10316,7 @@
         <v>7.3518745439599999E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>40</v>
       </c>
@@ -10340,7 +10442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
         <v>41</v>
       </c>
@@ -10467,7 +10569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>42</v>
       </c>
@@ -10594,7 +10696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17" t="s">
@@ -10723,7 +10825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -10852,7 +10954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>38</v>
       </c>
@@ -10975,7 +11077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>39</v>
       </c>
@@ -11098,7 +11200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
         <v>40</v>
       </c>
@@ -11221,7 +11323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
         <v>41</v>
       </c>
@@ -11344,7 +11446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
         <v>42</v>
       </c>
@@ -11467,7 +11569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17" t="s">
@@ -11593,7 +11695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -11722,7 +11824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
         <v>38</v>
       </c>
@@ -11845,7 +11947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
         <v>39</v>
       </c>
@@ -11968,7 +12070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>40</v>
       </c>
@@ -12091,7 +12193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
         <v>41</v>
       </c>
@@ -12214,7 +12316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>42</v>
       </c>
@@ -12337,7 +12439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17" t="s">
@@ -12463,7 +12565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -12593,7 +12695,7 @@
         <v>0.93664816810144857</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C53" t="s">
         <v>38</v>
       </c>
@@ -12716,7 +12818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
         <v>39</v>
       </c>
@@ -12839,7 +12941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C55" t="s">
         <v>40</v>
       </c>
@@ -12964,7 +13066,7 @@
         <v>6.3351831898551425E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
         <v>41</v>
       </c>
@@ -13087,7 +13189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>42</v>
       </c>
@@ -13210,7 +13312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17" t="s">
@@ -13336,7 +13438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -13465,7 +13567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
         <v>38</v>
       </c>
@@ -13588,7 +13690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C61" t="s">
         <v>39</v>
       </c>
@@ -13711,7 +13813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
         <v>40</v>
       </c>
@@ -13834,7 +13936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C63" t="s">
         <v>41</v>
       </c>
@@ -13957,7 +14059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
         <v>42</v>
       </c>
@@ -14080,7 +14182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17" t="s">
@@ -14206,7 +14308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>48</v>
       </c>
@@ -14335,7 +14437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
         <v>38</v>
       </c>
@@ -14458,7 +14560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
         <v>39</v>
       </c>
@@ -14581,7 +14683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C69" t="s">
         <v>40</v>
       </c>
@@ -14704,7 +14806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
         <v>41</v>
       </c>
@@ -14827,7 +14929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C71" t="s">
         <v>42</v>
       </c>
@@ -14950,7 +15052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17" t="s">
@@ -15076,7 +15178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>48</v>
       </c>
@@ -15205,7 +15307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C74" t="s">
         <v>38</v>
       </c>
@@ -15328,7 +15430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C75" t="s">
         <v>39</v>
       </c>
@@ -15451,7 +15553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
         <v>40</v>
       </c>
@@ -15574,7 +15676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C77" t="s">
         <v>41</v>
       </c>
@@ -15697,7 +15799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
         <v>42</v>
       </c>
@@ -15820,7 +15922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="17"/>
       <c r="B79" s="17"/>
       <c r="C79" s="17" t="s">
@@ -15946,7 +16048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>49</v>
       </c>
@@ -15958,11 +16060,11 @@
       </c>
       <c r="D80">
         <f t="shared" ref="D80:F86" si="5">D10</f>
-        <v>0.18218700570900001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="E80">
         <f t="shared" si="5"/>
-        <v>0.18123793393000001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="F80">
         <f t="shared" si="5"/>
@@ -15974,128 +16076,128 @@
       </c>
       <c r="I80" s="16">
         <f t="shared" si="4"/>
-        <v>0.18123793393000001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="J80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,J$9))</f>
-        <v>0.23279812904258823</v>
+        <v>0.20439829056518796</v>
       </c>
       <c r="K80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,K$9))</f>
-        <v>0.24933658275197695</v>
+        <v>0.22154895526074969</v>
       </c>
       <c r="L80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,L$9))</f>
-        <v>0.2705622726537894</v>
+        <v>0.24356036556758487</v>
       </c>
       <c r="M80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,M$9))</f>
-        <v>0.29738020490215311</v>
+        <v>0.27137102863815177</v>
       </c>
       <c r="N80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,N$9))</f>
-        <v>0.33060103270559432</v>
+        <v>0.30582160597612668</v>
       </c>
       <c r="O80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,O$9))</f>
-        <v>0.37076106043634494</v>
+        <v>0.34746825456114855</v>
       </c>
       <c r="P80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,P$9))</f>
-        <v>0.41790151635931294</v>
+        <v>0.39635372882237035</v>
       </c>
       <c r="Q80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Q$9))</f>
-        <v>0.47136110874344317</v>
+        <v>0.45179225771102483</v>
       </c>
       <c r="R80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,R$9))</f>
-        <v>0.52966825809683538</v>
+        <v>0.5122577876502824</v>
       </c>
       <c r="S80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,S$9))</f>
-        <v>0.59061896696500005</v>
+        <v>0.57546473487299998</v>
       </c>
       <c r="T80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,T$9))</f>
-        <v>0.65156967583316472</v>
+        <v>0.63867168209571767</v>
       </c>
       <c r="U80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,U$9))</f>
-        <v>0.70987682518655681</v>
+        <v>0.69913721203497514</v>
       </c>
       <c r="V80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,V$9))</f>
-        <v>0.76333641757068704</v>
+        <v>0.75457574092362967</v>
       </c>
       <c r="W80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,W$9))</f>
-        <v>0.81047687349365505</v>
+        <v>0.80346121518485136</v>
       </c>
       <c r="X80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,X$9))</f>
-        <v>0.85063690122440572</v>
+        <v>0.84510786376987324</v>
       </c>
       <c r="Y80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Y$9))</f>
-        <v>0.88385772902784698</v>
+        <v>0.87955844110784831</v>
       </c>
       <c r="Z80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Z$9))</f>
-        <v>0.91067566127621058</v>
+        <v>0.9073691041784151</v>
       </c>
       <c r="AA80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AA$9))</f>
-        <v>0.93190135117802309</v>
+        <v>0.92938051448525039</v>
       </c>
       <c r="AB80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AB$9))</f>
-        <v>0.94843980488741186</v>
+        <v>0.94653117918081209</v>
       </c>
       <c r="AC80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AC$9))</f>
-        <v>0.96116949409196173</v>
+        <v>0.95973208871336446</v>
       </c>
       <c r="AD80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AD$9))</f>
-        <v>0.97087565957856936</v>
+        <v>0.96979755146251745</v>
       </c>
       <c r="AE80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AE$9))</f>
-        <v>0.97822339058775476</v>
+        <v>0.97741727656052824</v>
       </c>
       <c r="AF80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AF$9))</f>
-        <v>0.98375551028570629</v>
+        <v>0.98315418108996533</v>
       </c>
       <c r="AG80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AG$9))</f>
-        <v>0.98790358328663208</v>
+        <v>0.98745580507620323</v>
       </c>
       <c r="AH80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AH$9))</f>
-        <v>0.99100430815198304</v>
+        <v>0.990671310794772</v>
       </c>
       <c r="AI80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AI$9))</f>
-        <v>0.99331679637819548</v>
-      </c>
-    </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
+        <v>0.99306940138275057</v>
+      </c>
+    </row>
+    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
         <v>38</v>
       </c>
       <c r="D81">
         <f t="shared" si="5"/>
-        <v>1.06995776452E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="E81">
         <f t="shared" si="5"/>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="F81">
         <f t="shared" si="5"/>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="G81" s="5" t="str">
         <f>IF(E81=F81,"n/a",IF(OR(C81="battery electric vehicle",C81="natural gas vehicle",C81="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16103,114 +16205,114 @@
       </c>
       <c r="I81" s="16">
         <f t="shared" si="4"/>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="J81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,J$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="K81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,K$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="L81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,L$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="M81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,M$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="N81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,N$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="O81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,O$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="P81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,P$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Q81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Q$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="R81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,R$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="S81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,S$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="T81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,T$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="U81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,U$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="V81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,V$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="W81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,W$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="X81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,X$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Y81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Y$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Z81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Z$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AA81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AA$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AB81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AB$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AC81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AC$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AD81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AD$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AE81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AE$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AF81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AF$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AG81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AG$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AH81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AH$9))</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AI81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AI$9))</f>
-        <v>1.06732008758E-4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
+        <v>1.0695408416000001E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
         <v>39</v>
       </c>
@@ -16339,21 +16441,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C83" t="s">
         <v>40</v>
       </c>
       <c r="D83">
         <f t="shared" si="5"/>
-        <v>6.8106756297200005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="E83">
         <f t="shared" si="5"/>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="F83">
         <f t="shared" si="5"/>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="G83" s="5" t="str">
         <f>IF(E83=F83,"n/a",IF(OR(C83="battery electric vehicle",C83="natural gas vehicle",C83="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16361,128 +16463,128 @@
       </c>
       <c r="I83" s="16">
         <f t="shared" si="4"/>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="J83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,J$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="K83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,K$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="L83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,L$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="M83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,M$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="N83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,N$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="O83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,O$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="P83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,P$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Q83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Q$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="R83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,R$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="S83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,S$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="T83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,T$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="U83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,U$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="V83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,V$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="W83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,W$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="X83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,X$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Y83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Y$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Z83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Z$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AA83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AA$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AB83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AB$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AC83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AC$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AD83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AD$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AE83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AE$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AF83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AF$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AG83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AG$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AH83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AH$9))</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AI83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AI$9))</f>
-        <v>6.7938858436000005E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
+        <v>6.7938939010499994E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C84" t="s">
         <v>41</v>
       </c>
       <c r="D84">
         <f t="shared" si="5"/>
-        <v>1.6603971957400002E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="E84">
         <f t="shared" si="5"/>
-        <v>1.3970074369600001E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="F84">
         <f t="shared" si="5"/>
-        <v>9.1136971557240806E-2</v>
+        <v>9.1008967024832244E-2</v>
       </c>
       <c r="G84" s="5" t="str">
         <f>IF(E84=F84,"n/a",IF(OR(C84="battery electric vehicle",C84="natural gas vehicle",C84="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16490,114 +16592,114 @@
       </c>
       <c r="I84" s="16">
         <f t="shared" si="4"/>
-        <v>1.3970074369600001E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="J84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,J$9))</f>
-        <v>1.5110140554321749E-2</v>
+        <v>1.2806537318706219E-2</v>
       </c>
       <c r="K84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,K$9))</f>
-        <v>1.550108920235292E-2</v>
+        <v>1.3208673429906077E-2</v>
       </c>
       <c r="L84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,L$9))</f>
-        <v>1.6022481838446352E-2</v>
+        <v>1.3744986339907847E-2</v>
       </c>
       <c r="M84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,M$9))</f>
-        <v>1.6714992675043627E-2</v>
+        <v>1.4457314202391682E-2</v>
       </c>
       <c r="N84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,N$9))</f>
-        <v>1.7629781849127387E-2</v>
+        <v>1.5398281162851517E-2</v>
       </c>
       <c r="O84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,O$9))</f>
-        <v>1.8829532862010948E-2</v>
+        <v>1.663236448596514E-2</v>
       </c>
       <c r="P84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,P$9))</f>
-        <v>2.0388253288765361E-2</v>
+        <v>1.8235689562083129E-2</v>
       </c>
       <c r="Q84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Q$9))</f>
-        <v>2.2388737554300295E-2</v>
+        <v>2.0293420077612576E-2</v>
       </c>
       <c r="R84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,R$9))</f>
-        <v>2.4916280910733307E-2</v>
+        <v>2.2893292110330199E-2</v>
       </c>
       <c r="S84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,S$9))</f>
-        <v>2.8047286009566623E-2</v>
+        <v>2.611389466499453E-2</v>
       </c>
       <c r="T84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,T$9))</f>
-        <v>3.18322986028182E-2</v>
+        <v>3.0007219920774212E-2</v>
       </c>
       <c r="U84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,U$9))</f>
-        <v>3.6275204382572757E-2</v>
+        <v>3.4577264763480553E-2</v>
       </c>
       <c r="V84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,V$9))</f>
-        <v>4.1313677756162917E-2</v>
+        <v>3.9759920079065703E-2</v>
       </c>
       <c r="W84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,W$9))</f>
-        <v>4.6809024922225891E-2</v>
+        <v>4.5412523177152192E-2</v>
       </c>
       <c r="X84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,X$9))</f>
-        <v>5.2553522963420404E-2</v>
+        <v>5.1321406900666118E-2</v>
       </c>
       <c r="Y84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Y$9))</f>
-        <v>5.8298021004614918E-2</v>
+        <v>5.7230290624180044E-2</v>
       </c>
       <c r="Z84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Z$9))</f>
-        <v>6.3793368170677878E-2</v>
+        <v>6.2882893722266534E-2</v>
       </c>
       <c r="AA84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AA$9))</f>
-        <v>6.8831841544268038E-2</v>
+        <v>6.8065549037851683E-2</v>
       </c>
       <c r="AB84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AB$9))</f>
-        <v>7.3274747324022602E-2</v>
+        <v>7.2635593880558014E-2</v>
       </c>
       <c r="AC84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AC$9))</f>
-        <v>7.7059759917274179E-2</v>
+        <v>7.6528919136337692E-2</v>
       </c>
       <c r="AD84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AD$9))</f>
-        <v>8.0190765016107501E-2</v>
+        <v>7.9749521691002051E-2</v>
       </c>
       <c r="AE84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AE$9))</f>
-        <v>8.2718308372540517E-2</v>
+        <v>8.234939372371966E-2</v>
       </c>
       <c r="AF84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AF$9))</f>
-        <v>8.4718792638075455E-2</v>
+        <v>8.4407124239249121E-2</v>
       </c>
       <c r="AG84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AG$9))</f>
-        <v>8.6277513064829864E-2</v>
+        <v>8.601044931536711E-2</v>
       </c>
       <c r="AH84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AH$9))</f>
-        <v>8.7477264077713432E-2</v>
+        <v>8.7244532638480726E-2</v>
       </c>
       <c r="AI84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AI$9))</f>
-        <v>8.8392053251797179E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
+        <v>8.8185499598940564E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C85" t="s">
         <v>42</v>
       </c>
@@ -16726,7 +16828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="17"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17" t="s">
@@ -16857,7 +16959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>49</v>
       </c>
@@ -16986,7 +17088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C88" t="s">
         <v>38</v>
       </c>
@@ -17109,7 +17211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C89" t="s">
         <v>39</v>
       </c>
@@ -17232,7 +17334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C90" t="s">
         <v>40</v>
       </c>
@@ -17355,7 +17457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C91" t="s">
         <v>41</v>
       </c>
@@ -17478,7 +17580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C92" t="s">
         <v>42</v>
       </c>
@@ -17601,7 +17703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="17"/>
       <c r="B93" s="17"/>
       <c r="C93" s="17" t="s">
@@ -17742,13 +17844,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -17861,233 +17963,233 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
       <c r="B2">
         <f>Data!I10</f>
-        <v>0.18218700570900001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="C2">
         <f>Data!J10</f>
-        <v>0.18123793393000001</v>
+        <v>0.15092946974599999</v>
       </c>
       <c r="D2">
         <f>Data!K10</f>
-        <v>0.22006843983803839</v>
+        <v>0.19119738103263559</v>
       </c>
       <c r="E2">
         <f>Data!L10</f>
-        <v>0.23279812904258823</v>
+        <v>0.20439829056518796</v>
       </c>
       <c r="F2">
         <f>Data!M10</f>
-        <v>0.24933658275197695</v>
+        <v>0.22154895526074969</v>
       </c>
       <c r="G2">
         <f>Data!N10</f>
-        <v>0.2705622726537894</v>
+        <v>0.24356036556758487</v>
       </c>
       <c r="H2">
         <f>Data!O10</f>
-        <v>0.29738020490215311</v>
+        <v>0.27137102863815177</v>
       </c>
       <c r="I2">
         <f>Data!P10</f>
-        <v>0.33060103270559432</v>
+        <v>0.30582160597612668</v>
       </c>
       <c r="J2">
         <f>Data!Q10</f>
-        <v>0.37076106043634494</v>
+        <v>0.34746825456114855</v>
       </c>
       <c r="K2">
         <f>Data!R10</f>
-        <v>0.41790151635931294</v>
+        <v>0.39635372882237035</v>
       </c>
       <c r="L2">
         <f>Data!S10</f>
-        <v>0.47136110874344317</v>
+        <v>0.45179225771102483</v>
       </c>
       <c r="M2">
         <f>Data!T10</f>
-        <v>0.52966825809683538</v>
+        <v>0.5122577876502824</v>
       </c>
       <c r="N2">
         <f>Data!U10</f>
-        <v>0.59061896696500005</v>
+        <v>0.57546473487299998</v>
       </c>
       <c r="O2">
         <f>Data!V10</f>
-        <v>0.65156967583316472</v>
+        <v>0.63867168209571767</v>
       </c>
       <c r="P2">
         <f>Data!W10</f>
-        <v>0.70987682518655681</v>
+        <v>0.69913721203497514</v>
       </c>
       <c r="Q2">
         <f>Data!X10</f>
-        <v>0.76333641757068704</v>
+        <v>0.75457574092362967</v>
       </c>
       <c r="R2">
         <f>Data!Y10</f>
-        <v>0.81047687349365505</v>
+        <v>0.80346121518485136</v>
       </c>
       <c r="S2">
         <f>Data!Z10</f>
-        <v>0.85063690122440572</v>
+        <v>0.84510786376987324</v>
       </c>
       <c r="T2">
         <f>Data!AA10</f>
-        <v>0.88385772902784698</v>
+        <v>0.87955844110784831</v>
       </c>
       <c r="U2">
         <f>Data!AB10</f>
-        <v>0.91067566127621058</v>
+        <v>0.9073691041784151</v>
       </c>
       <c r="V2">
         <f>Data!AC10</f>
-        <v>0.93190135117802309</v>
+        <v>0.92938051448525039</v>
       </c>
       <c r="W2">
         <f>Data!AD10</f>
-        <v>0.94843980488741186</v>
+        <v>0.94653117918081209</v>
       </c>
       <c r="X2">
         <f>Data!AE10</f>
-        <v>0.96116949409196173</v>
+        <v>0.95973208871336446</v>
       </c>
       <c r="Y2">
         <f>Data!AF10</f>
-        <v>0.97087565957856936</v>
+        <v>0.96979755146251745</v>
       </c>
       <c r="Z2">
         <f>Data!AG10</f>
-        <v>0.97822339058775476</v>
+        <v>0.97741727656052824</v>
       </c>
       <c r="AA2">
         <f>Data!AH10</f>
-        <v>0.98375551028570629</v>
+        <v>0.98315418108996533</v>
       </c>
       <c r="AB2">
         <f>Data!AI10</f>
-        <v>0.98790358328663208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <v>0.98745580507620323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
       <c r="B3">
         <f>Data!I11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="C3">
         <f>Data!J11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="D3">
         <f>Data!K11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="E3">
         <f>Data!L11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="F3">
         <f>Data!M11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="G3">
         <f>Data!N11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="H3">
         <f>Data!O11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="I3">
         <f>Data!P11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="J3">
         <f>Data!Q11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="K3">
         <f>Data!R11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="L3">
         <f>Data!S11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="M3">
         <f>Data!T11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="N3">
         <f>Data!U11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="O3">
         <f>Data!V11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="P3">
         <f>Data!W11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Q3">
         <f>Data!X11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="R3">
         <f>Data!Y11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="S3">
         <f>Data!Z11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="T3">
         <f>Data!AA11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="U3">
         <f>Data!AB11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="V3">
         <f>Data!AC11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="W3">
         <f>Data!AD11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="X3">
         <f>Data!AE11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Y3">
         <f>Data!AF11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="Z3">
         <f>Data!AG11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AA3">
         <f>Data!AH11</f>
-        <v>1.06732008758E-4</v>
+        <v>1.0695408416000001E-4</v>
       </c>
       <c r="AB3">
         <f>Data!AI11</f>
-        <v>1.06732008758E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+        <v>1.0695408416000001E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -18200,233 +18302,233 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
       <c r="B5">
         <f>Data!I13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="C5">
         <f>Data!J13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="D5">
         <f>Data!K13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="E5">
         <f>Data!L13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="F5">
         <f>Data!M13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="G5">
         <f>Data!N13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="H5">
         <f>Data!O13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="I5">
         <f>Data!P13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="K5">
         <f>Data!R13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="L5">
         <f>Data!S13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="M5">
         <f>Data!T13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="N5">
         <f>Data!U13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="O5">
         <f>Data!V13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="P5">
         <f>Data!W13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH13</f>
-        <v>6.7938858436000005E-2</v>
+        <v>6.7938939010499994E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI13</f>
-        <v>6.7938858436000005E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+        <v>6.7938939010499994E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
       <c r="B6">
         <f>Data!I14</f>
-        <v>1.6603971957400002E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="C6">
         <f>Data!J14</f>
-        <v>1.3970074369600001E-2</v>
+        <v>1.1633846776499999E-2</v>
       </c>
       <c r="D6">
         <f>Data!K14</f>
-        <v>1.6992371673937554E-2</v>
+        <v>1.4742630733106016E-2</v>
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>1.8393603157554242E-2</v>
+        <v>1.6183960131609255E-2</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>2.0388253288765361E-2</v>
+        <v>1.8235689562083126E-2</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>2.3168593997747108E-2</v>
+        <v>2.109559304595815E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>2.6932694373384324E-2</v>
+        <v>2.4967407656003776E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>3.18322986028182E-2</v>
+        <v>3.0007219920774209E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>3.7893781709970521E-2</v>
+        <v>3.6242159617047354E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>4.493810244183398E-2</v>
+        <v>4.3488062012213696E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
-        <v>5.2553522963420404E-2</v>
+        <v>5.1321406900666118E-2</v>
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>6.0168943485006829E-2</v>
+        <v>5.9154751789118533E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>6.721326421687028E-2</v>
+        <v>6.6400654184284882E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>7.3274747324022602E-2</v>
+        <v>7.2635593880558028E-2</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>7.8174351553456478E-2</v>
+        <v>7.7675406145328446E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>8.1938451929093686E-2</v>
+        <v>8.1547220755374072E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>8.4718792638075455E-2</v>
+        <v>8.4407124239249121E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>8.6713442769286567E-2</v>
+        <v>8.6458853669722974E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>8.8114674252903258E-2</v>
+        <v>8.7900183068226223E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>8.908456408839445E-2</v>
+        <v>8.8897827461424384E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>8.9749031542300767E-2</v>
+        <v>8.9581309446279456E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>9.0201057861762329E-2</v>
+        <v>9.0046271039531389E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>9.050709126827812E-2</v>
+        <v>9.0361061958014605E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>9.0713610894126245E-2</v>
+        <v>9.0573491389970062E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>9.0852670195706434E-2</v>
+        <v>9.0716530039790799E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>9.0946166900329001E-2</v>
+        <v>9.0812702264445544E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>9.1008967024832244E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+        <v>9.0877299489625335E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -18539,7 +18641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -18663,12 +18765,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -18781,7 +18883,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -18791,7 +18893,7 @@
       </c>
       <c r="C2">
         <f>Data!J17</f>
-        <v>0.30713450135322462</v>
+        <v>0.30732944248799998</v>
       </c>
       <c r="D2">
         <f>Data!K17</f>
@@ -18894,7 +18996,7 @@
         <v>0.30014541837982223</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -19007,7 +19109,7 @@
         <v>0.59353215226599998</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -19120,7 +19222,7 @@
         <v>0.97401567340499995</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -19233,7 +19335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -19247,106 +19349,106 @@
       </c>
       <c r="D6">
         <f>Data!K21</f>
-        <v>1.0321237741728829E-3</v>
+        <v>1.0321411607416443E-3</v>
       </c>
       <c r="E6">
         <f>Data!L21</f>
-        <v>1.0318317242370562E-3</v>
+        <v>1.0318549051658338E-3</v>
       </c>
       <c r="F6">
         <f>Data!M21</f>
-        <v>1.0314486991464152E-3</v>
+        <v>1.031479479410095E-3</v>
       </c>
       <c r="G6">
         <f>Data!N21</f>
-        <v>1.0309510717001113E-3</v>
+        <v>1.0309917250444676E-3</v>
       </c>
       <c r="H6">
         <f>Data!O21</f>
-        <v>1.0303124094619435E-3</v>
+        <v>1.030365734060366E-3</v>
       </c>
       <c r="I6">
         <f>Data!P21</f>
-        <v>1.0295054815970778E-3</v>
+        <v>1.0295748158910443E-3</v>
       </c>
       <c r="J6">
         <f>Data!Q21</f>
-        <v>1.028505896267372E-3</v>
+        <v>1.0285950626398874E-3</v>
       </c>
       <c r="K6">
         <f>Data!R21</f>
-        <v>1.0272975165485478E-3</v>
+        <v>1.0274106575441273E-3</v>
       </c>
       <c r="L6">
         <f>Data!S21</f>
-        <v>1.025879101918574E-3</v>
+        <v>1.0260203846940701E-3</v>
       </c>
       <c r="M6">
         <f>Data!T21</f>
-        <v>1.024270550060824E-3</v>
+        <v>1.0244437469969668E-3</v>
       </c>
       <c r="N6">
         <f>Data!U21</f>
-        <v>1.0225161395008146E-3</v>
+        <v>1.0227241444788512E-3</v>
       </c>
       <c r="O6">
         <f>Data!V21</f>
-        <v>1.0206821865728424E-3</v>
+        <v>1.0209265777376718E-3</v>
       </c>
       <c r="P6">
         <f>Data!W21</f>
-        <v>1.0188482336448703E-3</v>
+        <v>1.0191290109964925E-3</v>
       </c>
       <c r="Q6">
         <f>Data!X21</f>
-        <v>1.0170938230848608E-3</v>
+        <v>1.0174094084783769E-3</v>
       </c>
       <c r="R6">
         <f>Data!Y21</f>
-        <v>1.0154852712271109E-3</v>
+        <v>1.0158327707812736E-3</v>
       </c>
       <c r="S6">
         <f>Data!Z21</f>
-        <v>1.0140668565971371E-3</v>
+        <v>1.0144424979312164E-3</v>
       </c>
       <c r="T6">
         <f>Data!AA21</f>
-        <v>1.0128584768783128E-3</v>
+        <v>1.0132580928354563E-3</v>
       </c>
       <c r="U6">
         <f>Data!AB21</f>
-        <v>1.0118588915486071E-3</v>
+        <v>1.0122783395842994E-3</v>
       </c>
       <c r="V6">
         <f>Data!AC21</f>
-        <v>1.0110519636837413E-3</v>
+        <v>1.0114874214149777E-3</v>
       </c>
       <c r="W6">
         <f>Data!AD21</f>
-        <v>1.0104133014455735E-3</v>
+        <v>1.0108614304308761E-3</v>
       </c>
       <c r="X6">
         <f>Data!AE21</f>
-        <v>1.0099156739992697E-3</v>
+        <v>1.0103736760652487E-3</v>
       </c>
       <c r="Y6">
         <f>Data!AF21</f>
-        <v>1.0095326489086287E-3</v>
+        <v>1.0099982503095099E-3</v>
       </c>
       <c r="Z6">
         <f>Data!AG21</f>
-        <v>1.0092405989728019E-3</v>
+        <v>1.0097119947336994E-3</v>
       </c>
       <c r="AA6">
         <f>Data!AH21</f>
-        <v>1.0090195122447148E-3</v>
+        <v>1.0094952944338913E-3</v>
       </c>
       <c r="AB6">
         <f>Data!AI21</f>
-        <v>1.0088530556553437E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+        <v>1.0093321403941448E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -19459,7 +19561,7 @@
         <v>1.3472785756799999E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -19583,12 +19685,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -19701,7 +19803,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -19814,7 +19916,7 @@
         <v>0.73751575888521737</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -19927,7 +20029,7 @@
         <v>1.5317430015500001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -20040,7 +20142,7 @@
         <v>0.38138758163300002</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -20153,7 +20255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -20266,7 +20368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -20379,7 +20481,7 @@
         <v>5.5226931821800003E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -20503,12 +20605,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -20621,7 +20723,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -20734,7 +20836,7 @@
         <v>0.24513810124032956</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -20847,7 +20949,7 @@
         <v>2.32516282526E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -20960,7 +21062,7 @@
         <v>7.3518745439599999E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -21073,7 +21175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -21186,7 +21288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -21299,7 +21401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -21423,12 +21525,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -21541,7 +21643,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -21654,7 +21756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -21767,7 +21869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -21880,7 +21982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -21993,7 +22095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -22106,7 +22208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -22219,7 +22321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -22343,12 +22445,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>75</v>
       </c>
@@ -22461,7 +22563,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -22574,7 +22676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -22687,7 +22789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -22800,7 +22902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -22913,7 +23015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -23026,7 +23128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -23139,7 +23241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-tts-sync\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\.claude\worktrees\angry-germain-b7fbd2\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F16B4C-FA25-4DDE-8DA7-667025A8C726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80222AC-8B02-4792-810B-E20D95065644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="4680" windowWidth="43200" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="90">
   <si>
     <t>TTS Transportation Technology Shareweights</t>
   </si>
@@ -275,6 +275,48 @@
   </si>
   <si>
     <t>Max Fraction of Production (dimensionless)</t>
+  </si>
+  <si>
+    <t>Calibration record (2026-10-16)</t>
+  </si>
+  <si>
+    <t>On-road anchors (Data tab columns D-E) rewritten by calibration/steps/03-trans-shareweights/solve_base_year.py:</t>
+  </si>
+  <si>
+    <t>logit inversion at the start year from 'BAU New Vehicle Cost per Mile' in the BAU export and observed technology shares</t>
+  </si>
+  <si>
+    <t>(calibration/benchmarks/vehicle-technology-shares.csv), ZEV-mandate correction for passenger LDVs (3 passes), then the</t>
+  </si>
+  <si>
+    <t>existing s-curve formulas carry the trajectory to the unchanged 2050 targets. Confirmed by a headless run after the third pass.</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-frgt hydrogen vehicle: weight set to 0 - observed share unreachable at placeholder cost inputs (step 3a); provisional</t>
+  </si>
+  <si>
+    <t>TTS-HDVs-frgt hydrogen vehicle: weight set to 0 - observed share unreachable at placeholder cost inputs (step 3a); provisional</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr natural gas vehicle: IT-year cell set to =E11 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr gasoline vehicle: IT-year cell set to =E12 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr diesel vehicle: IT-year cell set to =E13 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr plugin hybrid vehicle: 2050 target pinned at its pre-calibration value 0.102391 (was =D14/D10*F10)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr LPG vehicle: IT-year cell set to =E15 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-psgr hydrogen vehicle: IT-year cell set to =E16 (was an s-curve formula)</t>
+  </si>
+  <si>
+    <t>TTS-LDVs-frgt plugin hybrid vehicle: 2050 target pinned at its pre-calibration value 0.00123571 (was =E21/E17*F17)</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="63.42578125" customWidth="1"/>
@@ -1248,8 +1290,78 @@
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" s="1"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5070,111 +5182,111 @@
       </c>
       <c r="B2">
         <f>Data!I80</f>
-        <v>0.14828894775500001</v>
+        <v>0.148288948</v>
       </c>
       <c r="C2">
         <f>Data!J80</f>
-        <v>0.20192405110570355</v>
+        <v>0.20192405133527508</v>
       </c>
       <c r="D2">
         <f>Data!K80</f>
-        <v>0.21912805260389268</v>
+        <v>0.21912805282851533</v>
       </c>
       <c r="E2">
         <f>Data!L80</f>
-        <v>0.2412079161321001</v>
+        <v>0.24120791635037137</v>
       </c>
       <c r="F2">
         <f>Data!M80</f>
-        <v>0.2691050675034683</v>
+        <v>0.26910506771371479</v>
       </c>
       <c r="G2">
         <f>Data!N80</f>
-        <v>0.30366278259245705</v>
+        <v>0.30366278279276282</v>
       </c>
       <c r="H2">
         <f>Data!O80</f>
-        <v>0.34543894796969088</v>
+        <v>0.34543894815797949</v>
       </c>
       <c r="I2">
         <f>Data!P80</f>
-        <v>0.39447645102619855</v>
+        <v>0.39447645120038111</v>
       </c>
       <c r="J2">
         <f>Data!Q80</f>
-        <v>0.45008738803580778</v>
+        <v>0.45008738819399363</v>
       </c>
       <c r="K2">
         <f>Data!R80</f>
-        <v>0.51074095955207577</v>
+        <v>0.51074095969281419</v>
       </c>
       <c r="L2">
         <f>Data!S80</f>
-        <v>0.57414447387750001</v>
+        <v>0.57414447400000002</v>
       </c>
       <c r="M2">
         <f>Data!T80</f>
-        <v>0.63754798820292424</v>
+        <v>0.63754798830718573</v>
       </c>
       <c r="N2">
         <f>Data!U80</f>
-        <v>0.69820155971919218</v>
+        <v>0.6982015598060064</v>
       </c>
       <c r="O2">
         <f>Data!V80</f>
-        <v>0.75381249672880146</v>
+        <v>0.75381249679961881</v>
       </c>
       <c r="P2">
         <f>Data!W80</f>
-        <v>0.80284999978530913</v>
+        <v>0.80284999984202055</v>
       </c>
       <c r="Q2">
         <f>Data!X80</f>
-        <v>0.84462616516254285</v>
+        <v>0.84462616520723721</v>
       </c>
       <c r="R2">
         <f>Data!Y80</f>
-        <v>0.87918388025153182</v>
+        <v>0.87918388028628536</v>
       </c>
       <c r="S2">
         <f>Data!Z80</f>
-        <v>0.90708103162289988</v>
+        <v>0.90708103164962861</v>
       </c>
       <c r="T2">
         <f>Data!AA80</f>
-        <v>0.92916089515110734</v>
+        <v>0.9291608951714847</v>
       </c>
       <c r="U2">
         <f>Data!AB80</f>
-        <v>0.94636489664929646</v>
+        <v>0.94636489666472501</v>
       </c>
       <c r="V2">
         <f>Data!AC80</f>
-        <v>0.95960685965229675</v>
+        <v>0.95960685966391612</v>
       </c>
       <c r="W2">
         <f>Data!AD80</f>
-        <v>0.96970362495499696</v>
+        <v>0.96970362496371199</v>
       </c>
       <c r="X2">
         <f>Data!AE80</f>
-        <v>0.97734704661409399</v>
+        <v>0.97734704662061023</v>
       </c>
       <c r="Y2">
         <f>Data!AF80</f>
-        <v>0.98310179232636641</v>
+        <v>0.9831017923312273</v>
       </c>
       <c r="Z2">
         <f>Data!AG80</f>
-        <v>0.98741679392062143</v>
+        <v>0.98741679392424109</v>
       </c>
       <c r="AA2">
         <f>Data!AH80</f>
-        <v>0.99064229953114202</v>
+        <v>0.99064229953383387</v>
       </c>
       <c r="AB2">
         <f>Data!AI80</f>
-        <v>0.99304784793411749</v>
+        <v>0.99304784793611733</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -5183,111 +5295,111 @@
       </c>
       <c r="B3">
         <f>Data!I81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="C3">
         <f>Data!J81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="D3">
         <f>Data!K81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="E3">
         <f>Data!L81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="F3">
         <f>Data!M81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="G3">
         <f>Data!N81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="H3">
         <f>Data!O81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="I3">
         <f>Data!P81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="J3">
         <f>Data!Q81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="K3">
         <f>Data!R81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="L3">
         <f>Data!S81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="M3">
         <f>Data!T81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="N3">
         <f>Data!U81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="O3">
         <f>Data!V81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="P3">
         <f>Data!W81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Q3">
         <f>Data!X81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="R3">
         <f>Data!Y81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="S3">
         <f>Data!Z81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="T3">
         <f>Data!AA81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="U3">
         <f>Data!AB81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="V3">
         <f>Data!AC81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="W3">
         <f>Data!AD81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="X3">
         <f>Data!AE81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Y3">
         <f>Data!AF81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Z3">
         <f>Data!AG81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AA3">
         <f>Data!AH81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AB3">
         <f>Data!AI81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -5409,111 +5521,111 @@
       </c>
       <c r="B5">
         <f>Data!I83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="C5">
         <f>Data!J83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="D5">
         <f>Data!K83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="E5">
         <f>Data!L83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="F5">
         <f>Data!M83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="G5">
         <f>Data!N83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="H5">
         <f>Data!O83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="I5">
         <f>Data!P83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="K5">
         <f>Data!R83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="L5">
         <f>Data!S83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="M5">
         <f>Data!T83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="N5">
         <f>Data!U83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="O5">
         <f>Data!V83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="P5">
         <f>Data!W83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -5522,111 +5634,111 @@
       </c>
       <c r="B6">
         <f>Data!I84</f>
-        <v>1.4073498597800001E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="C6">
         <f>Data!J84</f>
-        <v>1.5378299229133533E-2</v>
+        <v>1.5378299625391417E-2</v>
       </c>
       <c r="D6">
         <f>Data!K84</f>
-        <v>1.5825738202068743E-2</v>
+        <v>1.5825738596288972E-2</v>
       </c>
       <c r="E6">
         <f>Data!L84</f>
-        <v>1.6422469733855565E-2</v>
+        <v>1.6422470125358253E-2</v>
       </c>
       <c r="F6">
         <f>Data!M84</f>
-        <v>1.7215045278070985E-2</v>
+        <v>1.7215045665964251E-2</v>
       </c>
       <c r="G6">
         <f>Data!N84</f>
-        <v>1.8262017381864146E-2</v>
+        <v>1.8262017764989459E-2</v>
       </c>
       <c r="H6">
         <f>Data!O84</f>
-        <v>1.96351270311391E-2</v>
+        <v>1.9635127408011214E-2</v>
       </c>
       <c r="I6">
         <f>Data!P84</f>
-        <v>2.1419075563388585E-2</v>
+        <v>2.1419075932136523E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q84</f>
-        <v>2.3708620826306676E-2</v>
+        <v>2.370862118462793E-2</v>
       </c>
       <c r="K6">
         <f>Data!R84</f>
-        <v>2.6601382853102151E-2</v>
+        <v>2.6601383198249652E-2</v>
       </c>
       <c r="L6">
         <f>Data!S84</f>
-        <v>3.0184804135493147E-2</v>
+        <v>3.0184804464321601E-2</v>
       </c>
       <c r="M6">
         <f>Data!T84</f>
-        <v>3.4516734059794343E-2</v>
+        <v>3.4516734368895005E-2</v>
       </c>
       <c r="N6">
         <f>Data!U84</f>
-        <v>3.9601619783156121E-2</v>
+        <v>3.9601620069100008E-2</v>
       </c>
       <c r="O6">
         <f>Data!V84</f>
-        <v>4.5368129944513266E-2</v>
+        <v>4.5368130204196222E-2</v>
       </c>
       <c r="P6">
         <f>Data!W84</f>
-        <v>5.1657530110720232E-2</v>
+        <v>5.1657530341761002E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X84</f>
-        <v>5.8232082335224832E-2</v>
+        <v>5.8232082536324822E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y84</f>
-        <v>6.4806634559729431E-2</v>
+        <v>6.4806634730888643E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z84</f>
-        <v>7.1096034725936397E-2</v>
+        <v>7.1096034868453423E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA84</f>
-        <v>7.6862544887293549E-2</v>
+        <v>7.6862545003549651E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB84</f>
-        <v>8.194743061065532E-2</v>
+        <v>8.194743070375464E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC84</f>
-        <v>8.6279360534956523E-2</v>
+        <v>8.6279360608328054E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD84</f>
-        <v>8.9862781817347526E-2</v>
+        <v>8.9862781874400013E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE84</f>
-        <v>9.2755543844143001E-2</v>
+        <v>9.2755543888021721E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF84</f>
-        <v>9.5045089107061081E-2</v>
+        <v>9.5045089140513128E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG84</f>
-        <v>9.6829037639310556E-2</v>
+        <v>9.6829037664638448E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH84</f>
-        <v>9.8202147288585534E-2</v>
+        <v>9.8202147307660206E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI84</f>
-        <v>9.9249119392378682E-2</v>
+        <v>9.9249119406685404E-2</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -7156,10 +7268,10 @@
         <v>37</v>
       </c>
       <c r="D10">
-        <v>0.16449392895100001</v>
+        <v>0.148288948</v>
       </c>
       <c r="E10" s="16">
-        <v>0.14828894775500001</v>
+        <v>0.148288948</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -7170,111 +7282,111 @@
       </c>
       <c r="I10">
         <f>D10</f>
-        <v>0.16449392895100001</v>
+        <v>0.148288948</v>
       </c>
       <c r="J10" s="16">
         <f>E10</f>
-        <v>0.14828894775500001</v>
+        <v>0.148288948</v>
       </c>
       <c r="K10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,K$9))</f>
-        <v>0.18868208810270334</v>
+        <v>0.18868208833608399</v>
       </c>
       <c r="L10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,L$9))</f>
-        <v>0.20192405110570355</v>
+        <v>0.20192405133527508</v>
       </c>
       <c r="M10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,M$9))</f>
-        <v>0.21912805260389268</v>
+        <v>0.21912805282851533</v>
       </c>
       <c r="N10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,N$9))</f>
-        <v>0.2412079161321001</v>
+        <v>0.24120791635037137</v>
       </c>
       <c r="O10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,O$9))</f>
-        <v>0.2691050675034683</v>
+        <v>0.26910506771371479</v>
       </c>
       <c r="P10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,P$9))</f>
-        <v>0.30366278259245705</v>
+        <v>0.30366278279276282</v>
       </c>
       <c r="Q10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Q$9))</f>
-        <v>0.34543894796969088</v>
+        <v>0.34543894815797949</v>
       </c>
       <c r="R10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,R$9))</f>
-        <v>0.39447645102619855</v>
+        <v>0.39447645120038111</v>
       </c>
       <c r="S10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,S$9))</f>
-        <v>0.45008738803580778</v>
+        <v>0.45008738819399363</v>
       </c>
       <c r="T10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,T$9))</f>
-        <v>0.51074095955207577</v>
+        <v>0.51074095969281419</v>
       </c>
       <c r="U10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,U$9))</f>
-        <v>0.57414447387750001</v>
+        <v>0.57414447400000002</v>
       </c>
       <c r="V10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,V$9))</f>
-        <v>0.63754798820292424</v>
+        <v>0.63754798830718573</v>
       </c>
       <c r="W10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,W$9))</f>
-        <v>0.69820155971919218</v>
+        <v>0.6982015598060064</v>
       </c>
       <c r="X10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,X$9))</f>
-        <v>0.75381249672880146</v>
+        <v>0.75381249679961881</v>
       </c>
       <c r="Y10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Y$9))</f>
-        <v>0.80284999978530913</v>
+        <v>0.80284999984202055</v>
       </c>
       <c r="Z10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Z$9))</f>
-        <v>0.84462616516254285</v>
+        <v>0.84462616520723721</v>
       </c>
       <c r="AA10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AA$9))</f>
-        <v>0.87918388025153182</v>
+        <v>0.87918388028628536</v>
       </c>
       <c r="AB10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AB$9))</f>
-        <v>0.90708103162289988</v>
+        <v>0.90708103164962861</v>
       </c>
       <c r="AC10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AC$9))</f>
-        <v>0.92916089515110734</v>
+        <v>0.9291608951714847</v>
       </c>
       <c r="AD10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AD$9))</f>
-        <v>0.94636489664929646</v>
+        <v>0.94636489666472501</v>
       </c>
       <c r="AE10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AE$9))</f>
-        <v>0.95960685965229675</v>
+        <v>0.95960685966391612</v>
       </c>
       <c r="AF10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AF$9))</f>
-        <v>0.96970362495499696</v>
+        <v>0.96970362496371199</v>
       </c>
       <c r="AG10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AG$9))</f>
-        <v>0.97734704661409399</v>
+        <v>0.97734704662061023</v>
       </c>
       <c r="AH10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AH$9))</f>
-        <v>0.98310179232636641</v>
+        <v>0.9831017923312273</v>
       </c>
       <c r="AI10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AI$9))</f>
-        <v>0.98741679392062143</v>
+        <v>0.98741679392424109</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
@@ -7282,14 +7394,14 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>1.0004432735E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="E11" s="16">
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="F11" s="16">
         <f>E11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="G11" s="5" t="str">
         <f>IF(E11=F11,"n/a",IF(OR(C11="battery electric vehicle",C11="natural gas vehicle",C11="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -7297,111 +7409,111 @@
       </c>
       <c r="I11" s="16">
         <f>E11</f>
-        <v>1.00970167475E-4</v>
-      </c>
-      <c r="J11">
-        <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,J$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
+      </c>
+      <c r="J11" s="16">
+        <f>E11</f>
+        <v>1.0097E-4</v>
       </c>
       <c r="K11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,K$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="L11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,L$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="M11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,M$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="N11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,N$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="O11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,O$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="P11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,P$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Q11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Q$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="R11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,R$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="S11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,S$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="T11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,T$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="U11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,U$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="V11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,V$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="W11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,W$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="X11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,X$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Y11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Y$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Z11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Z$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AA11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AA$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AB11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AB$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AC11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AC$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AD11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AD$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AE11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AE$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AF11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AF$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AG11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AG$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AH11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AH$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AI11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AI$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
@@ -7426,7 +7538,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <f>IF($G12="s-curve",$E12+($F12-$E12)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E12:$F12,$E$9:$F$9,J$9))</f>
+        <f>E12</f>
         <v>1</v>
       </c>
       <c r="K12">
@@ -7535,14 +7647,14 @@
         <v>40</v>
       </c>
       <c r="D13">
-        <v>6.6777915503600002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="E13" s="16">
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="F13" s="16">
         <f>E13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="G13" s="5" t="str">
         <f>IF(E13=F13,"n/a",IF(OR(C13="battery electric vehicle",C13="natural gas vehicle",C13="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -7550,111 +7662,111 @@
       </c>
       <c r="I13" s="16">
         <f>E13</f>
-        <v>6.7382959534800002E-2</v>
-      </c>
-      <c r="J13">
-        <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,J$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
+      </c>
+      <c r="J13" s="16">
+        <f>E13</f>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="K13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,K$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="L13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,L$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="M13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,M$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="N13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,N$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="O13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,O$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="P13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,P$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Q13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Q$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="R13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,R$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="S13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,S$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="T13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,T$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="U13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,U$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="V13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,V$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="W13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,W$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="X13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,X$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Y13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Y$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Z13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Z$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AA13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AA$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AB13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AB$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AC13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AC$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AD13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AD$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AE13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AE$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AF13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AF$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AG13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AG$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AH13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AH$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AI13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AI$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.25">
@@ -7662,13 +7774,12 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>1.68426429502E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="E14" s="16">
-        <v>1.4073498597800001E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="F14" s="23">
-        <f>D14/D10*F10</f>
         <v>0.10239066607264966</v>
       </c>
       <c r="G14" s="5" t="str">
@@ -7677,111 +7788,111 @@
       </c>
       <c r="I14">
         <f>D14</f>
-        <v>1.68426429502E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="J14">
         <f>E14</f>
-        <v>1.4073498597800001E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="K14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:K$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,K$9))</f>
-        <v>1.7532504297315375E-2</v>
+        <v>1.7532504683762919E-2</v>
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:L$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>1.9136207441018131E-2</v>
+        <v>1.9136207820162347E-2</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:M$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>2.1419075563388582E-2</v>
+        <v>2.1419075932136523E-2</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:N$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>2.4601163025518801E-2</v>
+        <v>2.4601163379775384E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:O$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>2.8909159010622888E-2</v>
+        <v>2.8909159345260678E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:P$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>3.4516734059794343E-2</v>
+        <v>3.4516734368895005E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Q$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>4.1454074269529816E-2</v>
+        <v>4.1454074547037548E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:R$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>4.9516267729372364E-2</v>
+        <v>4.9516267970164535E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:S$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
-        <v>5.8232082335224832E-2</v>
+        <v>5.8232082536324822E-2</v>
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:T$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>6.6947896941077292E-2</v>
+        <v>6.694789710248511E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:U$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>7.5010090400919854E-2</v>
+        <v>7.5010090525612097E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:V$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>8.194743061065532E-2</v>
+        <v>8.1947430703754653E-2</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:W$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>8.7555005659826768E-2</v>
+        <v>8.7555005727388974E-2</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:X$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>9.1863001644930858E-2</v>
+        <v>9.1863001692874258E-2</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Y$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>9.5045089107061081E-2</v>
+        <v>9.5045089140513128E-2</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Z$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>9.7327957229431522E-2</v>
+        <v>9.7327957252487315E-2</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AA$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>9.8931660373134278E-2</v>
+        <v>9.8931660388886733E-2</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AB$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>0.10004169493659409</v>
+        <v>0.1000416949472914</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AC$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>0.10080217495518981</v>
+        <v>0.10080217496242386</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AD$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>0.10131951704893569</v>
+        <v>0.10131951705381374</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AE$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>0.10166977090909066</v>
+        <v>0.10166977091237364</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AF$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>0.10190613169392981</v>
+        <v>0.1019061316961364</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AG$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>0.10206528444043367</v>
+        <v>0.10206528444191545</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AH$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>0.10217229099922295</v>
+        <v>0.10217229100021745</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AI$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>0.10224416545984444</v>
+        <v>0.1022441654605116</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
@@ -7806,8 +7917,8 @@
         <f>E15</f>
         <v>0</v>
       </c>
-      <c r="J15">
-        <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,J$9))</f>
+      <c r="J15" s="16">
+        <f>E15</f>
         <v>0</v>
       </c>
       <c r="K15">
@@ -7935,8 +8046,8 @@
         <f>E16</f>
         <v>0</v>
       </c>
-      <c r="J16">
-        <f>IF($G16="s-curve",$E16+($F16-$E16)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E16:$F16,$E$9:$F$9,J$9))</f>
+      <c r="J16" s="16">
+        <f>E16</f>
         <v>0</v>
       </c>
       <c r="K16">
@@ -8051,10 +8162,10 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.464269858905</v>
+        <v>0.328639128</v>
       </c>
       <c r="E17">
-        <v>0.21897752724899999</v>
+        <v>0.328639128</v>
       </c>
       <c r="F17">
         <v>0.3</v>
@@ -8065,111 +8176,111 @@
       </c>
       <c r="I17" s="16">
         <f t="shared" ref="I17:I37" si="1">D17</f>
-        <v>0.464269858905</v>
+        <v>0.328639128</v>
       </c>
       <c r="J17">
         <f>E17</f>
-        <v>0.21897752724899999</v>
+        <v>0.328639128</v>
       </c>
       <c r="K17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,K$9))</f>
-        <v>0.22185959296256283</v>
+        <v>0.32762040015730876</v>
       </c>
       <c r="L17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,L$9))</f>
-        <v>0.22282008876622178</v>
+        <v>0.32728089234755592</v>
       </c>
       <c r="M17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,M$9))</f>
-        <v>0.22407978427416703</v>
+        <v>0.32683562599529409</v>
       </c>
       <c r="N17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,N$9))</f>
-        <v>0.225716384784306</v>
+        <v>0.3262571344990054</v>
       </c>
       <c r="O17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,O$9))</f>
-        <v>0.22781682147154225</v>
+        <v>0.32551469017338575</v>
       </c>
       <c r="P17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,P$9))</f>
-        <v>0.23047065128960009</v>
+        <v>0.3245766371953786</v>
       </c>
       <c r="Q17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Q$9))</f>
-        <v>0.23375809428068739</v>
+        <v>0.32341462007324273</v>
       </c>
       <c r="R17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,R$9))</f>
-        <v>0.23773222167048266</v>
+        <v>0.32200987964580063</v>
       </c>
       <c r="S17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,S$9))</f>
-        <v>0.24239711329622859</v>
+        <v>0.32036097380721384</v>
       </c>
       <c r="T17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,T$9))</f>
-        <v>0.24768732952230915</v>
+        <v>0.31849103359800773</v>
       </c>
       <c r="U17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,U$9))</f>
-        <v>0.25345724683461146</v>
+        <v>0.31645153276761123</v>
       </c>
       <c r="V17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,V$9))</f>
-        <v>0.25948876362450002</v>
+        <v>0.314319564</v>
       </c>
       <c r="W17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,W$9))</f>
-        <v>0.26552028041438847</v>
+        <v>0.31218759523238876</v>
       </c>
       <c r="X17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,X$9))</f>
-        <v>0.27129019772669083</v>
+        <v>0.31014809440199226</v>
       </c>
       <c r="Y17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Y$9))</f>
-        <v>0.27658041395277139</v>
+        <v>0.30827815419278615</v>
       </c>
       <c r="Z17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Z$9))</f>
-        <v>0.28124530557851735</v>
+        <v>0.30662924835419936</v>
       </c>
       <c r="AA17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AA$9))</f>
-        <v>0.28521943296831259</v>
+        <v>0.30522450792675726</v>
       </c>
       <c r="AB17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AB$9))</f>
-        <v>0.28850687595939989</v>
+        <v>0.30406249080462139</v>
       </c>
       <c r="AC17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AC$9))</f>
-        <v>0.29116070577745773</v>
+        <v>0.30312443782661425</v>
       </c>
       <c r="AD17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AD$9))</f>
-        <v>0.29326114246469398</v>
+        <v>0.30238199350099459</v>
       </c>
       <c r="AE17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AE$9))</f>
-        <v>0.29489774297483295</v>
+        <v>0.3018035020047059</v>
       </c>
       <c r="AF17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AF$9))</f>
-        <v>0.2961574384827782</v>
+        <v>0.30135823565244407</v>
       </c>
       <c r="AG17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AG$9))</f>
-        <v>0.29711793428643718</v>
+        <v>0.30101872784269124</v>
       </c>
       <c r="AH17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AH$9))</f>
-        <v>0.29784504581265986</v>
+        <v>0.30076171470346302</v>
       </c>
       <c r="AI17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AI$9))</f>
-        <v>0.29839248936928919</v>
+        <v>0.30056820905547738</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
@@ -8177,125 +8288,125 @@
         <v>38</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="F18" s="16">
         <f>E18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="J18" s="16">
         <f t="shared" ref="J18:J37" si="2">E18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="K18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="L18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="M18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="N18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="O18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="P18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="Q18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="R18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="S18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="T18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="U18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="V18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="W18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="X18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="Y18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="Z18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AA18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AB18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AC18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AD18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AE18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AF18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AG18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AH18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AI18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
@@ -8303,14 +8414,14 @@
         <v>39</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="E19">
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="F19" s="16">
         <f>E19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="G19" s="5" t="str">
         <f>IF(E19=F19,"n/a",IF(OR(C19="battery electric vehicle",C19="natural gas vehicle",C19="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -8318,111 +8429,111 @@
       </c>
       <c r="I19" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="J19" s="16">
         <f t="shared" si="2"/>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="K19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,K$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="L19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,L$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="M19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,M$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="N19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,N$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="O19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,O$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="P19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,P$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="Q19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Q$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="R19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,R$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="S19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,S$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="T19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,T$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="U19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,U$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="V19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,V$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="W19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,W$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="X19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,X$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="Y19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Y$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="Z19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Z$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AA19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AA$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AB19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AB$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AC19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AC$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AD19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AD$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AE19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AE$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AF19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AF$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AG19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AG$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AH19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AH$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AI19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AI$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
@@ -8430,7 +8541,7 @@
         <v>40</v>
       </c>
       <c r="D20">
-        <v>0.97299803336400004</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -8444,7 +8555,7 @@
       </c>
       <c r="I20" s="16">
         <f t="shared" si="1"/>
-        <v>0.97299803336400004</v>
+        <v>1</v>
       </c>
       <c r="J20" s="16">
         <f t="shared" si="2"/>
@@ -8556,13 +8667,12 @@
         <v>41</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1.003192E-3</v>
       </c>
       <c r="E21">
-        <v>9.0197447039299999E-4</v>
+        <v>1.003192E-3</v>
       </c>
       <c r="F21" s="16">
-        <f>E21/E17*F17</f>
         <v>1.235708268868196E-3</v>
       </c>
       <c r="G21" s="5" t="s">
@@ -8570,111 +8680,111 @@
       </c>
       <c r="I21" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.003192E-3</v>
       </c>
       <c r="J21" s="16">
         <f t="shared" si="2"/>
-        <v>9.0197447039299999E-4</v>
+        <v>1.003192E-3</v>
       </c>
       <c r="K21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,K$9))</f>
-        <v>9.1384577850523699E-4</v>
+        <v>1.0114628802088777E-3</v>
       </c>
       <c r="L21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,L$9))</f>
-        <v>9.1780208719455226E-4</v>
+        <v>1.0142192870790641E-3</v>
       </c>
       <c r="M21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,M$9))</f>
-        <v>9.229908077126324E-4</v>
+        <v>1.0178343297884813E-3</v>
       </c>
       <c r="N21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,N$9))</f>
-        <v>9.2973201032334131E-4</v>
+        <v>1.0225310050604737E-3</v>
       </c>
       <c r="O21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,O$9))</f>
-        <v>9.3838376693218116E-4</v>
+        <v>1.0285587858097846E-3</v>
       </c>
       <c r="P21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,P$9))</f>
-        <v>9.4931496509999139E-4</v>
+        <v>1.0361746803456418E-3</v>
       </c>
       <c r="Q21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Q$9))</f>
-        <v>9.6285603339172255E-4</v>
+        <v>1.0456089021417803E-3</v>
       </c>
       <c r="R21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,R$9))</f>
-        <v>9.7922557364874116E-4</v>
+        <v>1.0570137536762662E-3</v>
       </c>
       <c r="S21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,S$9))</f>
-        <v>9.9844039083310217E-4</v>
+        <v>1.0704009431641303E-3</v>
       </c>
       <c r="T21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,T$9))</f>
-        <v>1.020230937281997E-3</v>
+        <v>1.0855826735733526E-3</v>
       </c>
       <c r="U21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,U$9))</f>
-        <v>1.0439973857269895E-3</v>
+        <v>1.1021410381798931E-3</v>
       </c>
       <c r="V21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,V$9))</f>
-        <v>1.0688413696305979E-3</v>
+        <v>1.1194501344340981E-3</v>
       </c>
       <c r="W21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,W$9))</f>
-        <v>1.0936853535342065E-3</v>
+        <v>1.1367592306883029E-3</v>
       </c>
       <c r="X21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,X$9))</f>
-        <v>1.117451801979199E-3</v>
+        <v>1.1533175952948434E-3</v>
       </c>
       <c r="Y21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Y$9))</f>
-        <v>1.1392423484280938E-3</v>
+        <v>1.1684993257040656E-3</v>
       </c>
       <c r="Z21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Z$9))</f>
-        <v>1.1584571656124548E-3</v>
+        <v>1.1818865151919297E-3</v>
       </c>
       <c r="AA21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AA$9))</f>
-        <v>1.1748267058694735E-3</v>
+        <v>1.1932913667264157E-3</v>
       </c>
       <c r="AB21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AB$9))</f>
-        <v>1.1883677741612046E-3</v>
+        <v>1.2027255885225542E-3</v>
       </c>
       <c r="AC21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AC$9))</f>
-        <v>1.1992989723290147E-3</v>
+        <v>1.2103414830584114E-3</v>
       </c>
       <c r="AD21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AD$9))</f>
-        <v>1.2079507289378547E-3</v>
+        <v>1.2163692638077223E-3</v>
       </c>
       <c r="AE21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AE$9))</f>
-        <v>1.2146919315485635E-3</v>
+        <v>1.2210659390797147E-3</v>
       </c>
       <c r="AF21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AF$9))</f>
-        <v>1.2198806520666437E-3</v>
+        <v>1.2246809817891319E-3</v>
       </c>
       <c r="AG21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AG$9))</f>
-        <v>1.223836960755959E-3</v>
+        <v>1.2274373886593183E-3</v>
       </c>
       <c r="AH21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AH$9))</f>
-        <v>1.2268319531737681E-3</v>
+        <v>1.2295240351585918E-3</v>
       </c>
       <c r="AI21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AI$9))</f>
-        <v>1.2290868882726532E-3</v>
+        <v>1.2310950750057041E-3</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
@@ -8682,14 +8792,14 @@
         <v>42</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="F22" s="16">
         <f>E22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="G22" s="5" t="str">
         <f>IF(E22=F22,"n/a",IF(OR(C22="battery electric vehicle",C22="natural gas vehicle",C22="plugin hybrid vehicle",C22="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -8697,111 +8807,111 @@
       </c>
       <c r="I22" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="J22" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="K22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="L22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="M22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="N22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="O22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="P22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="Q22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="R22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="S22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="T22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="U22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="V22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="W22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="X22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="Y22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="Z22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AA22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AB22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AC22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AD22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AE22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AF22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AG22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AH22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AI22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
     </row>
     <row r="23" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8814,11 +8924,11 @@
         <v>0</v>
       </c>
       <c r="E23" s="6">
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="F23" s="20">
         <f>E23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="str">
         <f>IF(E23=F23,"n/a",IF(OR(C23="battery electric vehicle",C23="natural gas vehicle",C23="plugin hybrid vehicle",C23="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -8830,107 +8940,107 @@
       </c>
       <c r="J23" s="16">
         <f t="shared" si="2"/>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,K$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,L$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,M$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="N23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,N$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,O$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,P$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,Q$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="R23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,R$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,S$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="T23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,T$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="U23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,U$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,V$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="W23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,W$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="X23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,X$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Y23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,Y$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Z23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,Z$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AA23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AA$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AB23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AB$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AC23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AC$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AD23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AD$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AE$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AF23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AF$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AG23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AG$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AH23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AH$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AI23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AI$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
@@ -8944,10 +9054,10 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>3.1162890650799999E-2</v>
+        <v>0.12184009799999999</v>
       </c>
       <c r="E24">
-        <v>3.0635270769200001E-2</v>
+        <v>0.12184009799999999</v>
       </c>
       <c r="F24" s="26">
         <v>0.75</v>
@@ -8958,111 +9068,111 @@
       </c>
       <c r="I24" s="16">
         <f t="shared" si="1"/>
-        <v>3.1162890650799999E-2</v>
+        <v>0.12184009799999999</v>
       </c>
       <c r="J24" s="16">
         <f t="shared" si="2"/>
-        <v>3.0635270769200001E-2</v>
+        <v>0.12184009799999999</v>
       </c>
       <c r="K24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
-        <v>5.6223929708727458E-2</v>
+        <v>0.1441844927675226</v>
       </c>
       <c r="L24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
-        <v>6.4751771186114582E-2</v>
+        <v>0.15163112984748478</v>
       </c>
       <c r="M24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
-        <v>7.593608199789606E-2</v>
+        <v>0.16139743516937402</v>
       </c>
       <c r="N24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
-        <v>9.0466775061945975E-2</v>
+        <v>0.17408585087869802</v>
       </c>
       <c r="O24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
-        <v>0.10911567600852309</v>
+        <v>0.19037034651074775</v>
       </c>
       <c r="P24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
-        <v>0.13267792366244005</v>
+        <v>0.21094524902648606</v>
       </c>
       <c r="Q24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
-        <v>0.16186575830694638</v>
+        <v>0.23643249715649947</v>
       </c>
       <c r="R24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
-        <v>0.19715037721106998</v>
+        <v>0.26724354731268585</v>
       </c>
       <c r="S24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
-        <v>0.2385680035473921</v>
+        <v>0.30341003010412881</v>
       </c>
       <c r="T24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
-        <v>0.2855376260957222</v>
+        <v>0.34442459795552233</v>
       </c>
       <c r="U24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
-        <v>0.33676631443512162</v>
+        <v>0.38915824493495493</v>
       </c>
       <c r="V24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
-        <v>0.39031763538459996</v>
+        <v>0.43592004900000003</v>
       </c>
       <c r="W24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
-        <v>0.4438689563340783</v>
+        <v>0.48268185306504513</v>
       </c>
       <c r="X24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
-        <v>0.49509764467347783</v>
+        <v>0.52741550004447768</v>
       </c>
       <c r="Y24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
-        <v>0.54206726722180787</v>
+        <v>0.56843006789587125</v>
       </c>
       <c r="Z24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
-        <v>0.58348489355812994</v>
+        <v>0.6045965506873141</v>
       </c>
       <c r="AA24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
-        <v>0.61876951246225353</v>
+        <v>0.63540760084350045</v>
       </c>
       <c r="AB24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
-        <v>0.64795734710676001</v>
+        <v>0.66089484897351403</v>
       </c>
       <c r="AC24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
-        <v>0.67151959476067691</v>
+        <v>0.68146975148925226</v>
       </c>
       <c r="AD24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
-        <v>0.69016849570725403</v>
+        <v>0.69775424712130196</v>
       </c>
       <c r="AE24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
-        <v>0.704699188771304</v>
+        <v>0.71044266283062596</v>
       </c>
       <c r="AF24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
-        <v>0.7158834995830855</v>
+        <v>0.72020896815251523</v>
       </c>
       <c r="AG24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
-        <v>0.72441134106047256</v>
+        <v>0.72765560523247741</v>
       </c>
       <c r="AH24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
-        <v>0.73086706091722453</v>
+        <v>0.73329283512126131</v>
       </c>
       <c r="AI24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
-        <v>0.73572758383774906</v>
+        <v>0.73753711549443191</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
@@ -9070,14 +9180,14 @@
         <v>38</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="F25" s="16">
         <f>E25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="G25" s="5" t="str">
         <f>IF(E25=F25,"n/a",IF(OR(C25="battery electric vehicle",C25="natural gas vehicle",C25="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -9085,111 +9195,111 @@
       </c>
       <c r="I25" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="J25" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="K25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="L25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="M25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="N25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="O25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="P25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="Q25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="R25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="S25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="T25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="U25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="V25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="W25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="X25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="Y25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="Z25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AA25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AB25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AC25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AD25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AE25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AF25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AG25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AH25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AI25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
@@ -9197,14 +9307,14 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="F26" s="16">
         <f>E26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="G26" s="5" t="str">
         <f>IF(E26=F26,"n/a",IF(OR(C26="battery electric vehicle",C26="natural gas vehicle",C26="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -9212,111 +9322,111 @@
       </c>
       <c r="I26" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="J26" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="K26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="L26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="M26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="N26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="O26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="P26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="Q26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="R26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="S26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="T26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="U26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="V26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="W26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="X26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="Y26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="Z26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AA26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AB26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AC26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AD26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AE26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AF26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AG26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AH26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AI26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
@@ -9577,14 +9687,14 @@
         <v>42</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="F29" s="16">
         <f>E29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="G29" s="5" t="str">
         <f>IF(E29=F29,"n/a",IF(OR(C29="battery electric vehicle",C29="natural gas vehicle",C29="plugin hybrid vehicle",C29="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -9592,111 +9702,111 @@
       </c>
       <c r="I29" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="J29" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="K29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="L29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="M29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="N29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="O29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="P29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="Q29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="R29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="S29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="T29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="U29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="V29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="W29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="X29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="Y29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="Z29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AA29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AB29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AC29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AD29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AE29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AF29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AG29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AH29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AI29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
     </row>
     <row r="30" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9706,14 +9816,14 @@
         <v>43</v>
       </c>
       <c r="D30" s="20">
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="E30" s="6">
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="F30" s="20">
         <f>E30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="G30" s="6" t="str">
         <f>IF(E30=F30,"n/a",IF(OR(C30="battery electric vehicle",C30="natural gas vehicle",C30="plugin hybrid vehicle",C30="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -9721,111 +9831,111 @@
       </c>
       <c r="I30" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="J30" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="K30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="L30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="M30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="N30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="O30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="P30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="Q30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="R30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="S30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="T30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="U30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="V30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="W30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="X30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="Y30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="Z30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AA30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AB30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AC30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AD30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AE30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AF30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AG30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AH30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AI30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
@@ -9839,10 +9949,10 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>4.7973229575300003E-3</v>
+        <v>4.8089680000000003E-3</v>
       </c>
       <c r="E31">
-        <v>6.1405058414400002E-3</v>
+        <v>4.8089680000000003E-3</v>
       </c>
       <c r="F31" s="16">
         <v>0.25</v>
@@ -9853,111 +9963,111 @@
       </c>
       <c r="I31" s="16">
         <f t="shared" si="1"/>
-        <v>4.7973229575300003E-3</v>
+        <v>4.8089680000000003E-3</v>
       </c>
       <c r="J31" s="16">
         <f t="shared" si="2"/>
-        <v>6.1405058414400002E-3</v>
+        <v>4.8089680000000003E-3</v>
       </c>
       <c r="K31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:K$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,K$9))</f>
-        <v>1.4814878064083456E-2</v>
+        <v>1.3530704607224994E-2</v>
       </c>
       <c r="L31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:L$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,L$9))</f>
-        <v>1.7705755284549454E-2</v>
+        <v>1.6437366787908719E-2</v>
       </c>
       <c r="M31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:M$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,M$9))</f>
-        <v>2.1497156594966059E-2</v>
+        <v>2.0249470160118424E-2</v>
       </c>
       <c r="N31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:N$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,N$9))</f>
-        <v>2.6422957536251346E-2</v>
+        <v>2.520216728756761E-2</v>
       </c>
       <c r="O31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:O$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,O$9))</f>
-        <v>3.2744801472509036E-2</v>
+        <v>3.155853017687181E-2</v>
       </c>
       <c r="P31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:P$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,P$9))</f>
-        <v>4.0732234773926027E-2</v>
+        <v>3.9589576993249581E-2</v>
       </c>
       <c r="Q31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Q$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Q$9))</f>
-        <v>5.0626701798468406E-2</v>
+        <v>4.9538070445221086E-2</v>
       </c>
       <c r="R31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:R$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,R$9))</f>
-        <v>6.2587935047612731E-2</v>
+        <v>6.1564615216299301E-2</v>
       </c>
       <c r="S31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:S$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,S$9))</f>
-        <v>7.6628213917586716E-2</v>
+        <v>7.5681557751488576E-2</v>
       </c>
       <c r="T31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:T$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,T$9))</f>
-        <v>9.2550579763493207E-2</v>
+        <v>9.1690863959189184E-2</v>
       </c>
       <c r="U31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:U$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,U$9))</f>
-        <v>0.10991673842713874</v>
+        <v>0.10915184647827197</v>
       </c>
       <c r="V31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:V$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,V$9))</f>
-        <v>0.12807025292072</v>
+        <v>0.12740448400000001</v>
       </c>
       <c r="W31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:W$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,W$9))</f>
-        <v>0.14622376741430126</v>
+        <v>0.14565712152172802</v>
       </c>
       <c r="X31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:X$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,X$9))</f>
-        <v>0.16358992607794678</v>
+        <v>0.16311810404081081</v>
       </c>
       <c r="Y31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Y$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Y$9))</f>
-        <v>0.17951229192385326</v>
+        <v>0.17912741024851142</v>
       </c>
       <c r="Z31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Z$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Z$9))</f>
-        <v>0.19355257079382726</v>
+        <v>0.1932443527837007</v>
       </c>
       <c r="AA31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AA$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AA$9))</f>
-        <v>0.20551380404297159</v>
+        <v>0.2052708975547789</v>
       </c>
       <c r="AB31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AB$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AB$9))</f>
-        <v>0.21540827106751401</v>
+        <v>0.21521939100675044</v>
       </c>
       <c r="AC31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AC$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AC$9))</f>
-        <v>0.22339570436893097</v>
+        <v>0.2232504378231282</v>
       </c>
       <c r="AD31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AD$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AD$9))</f>
-        <v>0.22971754830518867</v>
+        <v>0.22960680071243239</v>
       </c>
       <c r="AE31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AE$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AE$9))</f>
-        <v>0.23464334924647395</v>
+        <v>0.23455949783988159</v>
       </c>
       <c r="AF31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AF$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AF$9))</f>
-        <v>0.23843475055689056</v>
+        <v>0.23837160121209131</v>
       </c>
       <c r="AG31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AG$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AG$9))</f>
-        <v>0.24132562777735656</v>
+        <v>0.241278263392775</v>
       </c>
       <c r="AH31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AH$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AH$9))</f>
-        <v>0.24351407060020699</v>
+        <v>0.24347865569679086</v>
       </c>
       <c r="AI31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AI$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AI$9))</f>
-        <v>0.2451617530797367</v>
+        <v>0.24513533496186604</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
@@ -9965,14 +10075,14 @@
         <v>38</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="F32" s="16">
         <f>E32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="G32" s="5" t="str">
         <f>IF(E32=F32,"n/a",IF(OR(C32="battery electric vehicle",C32="natural gas vehicle",C32="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -9980,111 +10090,111 @@
       </c>
       <c r="I32" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="J32" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="K32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="L32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="M32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="N32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="O32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="P32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="Q32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="R32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="S32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="T32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="U32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="V32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="W32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="X32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="Y32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="Z32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AA32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AB32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AC32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AD32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AE32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AF32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AG32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AH32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AI32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.25">
@@ -10092,14 +10202,14 @@
         <v>39</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="F33" s="16">
         <f>E33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="G33" s="5" t="str">
         <f>IF(E33=F33,"n/a",IF(OR(C33="battery electric vehicle",C33="natural gas vehicle",C33="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -10107,111 +10217,111 @@
       </c>
       <c r="I33" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="J33" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="K33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="L33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="M33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="N33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="O33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="P33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="Q33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="R33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="S33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="T33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="U33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="V33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="W33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="X33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="Y33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="Z33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AA33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AB33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AC33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AD33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AE33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AF33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AG33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AH33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AI33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.25">
@@ -10601,14 +10711,14 @@
         <v>43</v>
       </c>
       <c r="D37" s="20">
-        <v>6.2247642917999998E-4</v>
+        <v>0</v>
       </c>
       <c r="E37" s="6">
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="F37" s="20">
         <f>E37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="G37" s="6" t="str">
         <f>IF(E37=F37,"n/a",IF(OR(C37="battery electric vehicle",C37="natural gas vehicle",C37="plugin hybrid vehicle",C37="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -10616,111 +10726,111 @@
       </c>
       <c r="I37" s="16">
         <f t="shared" si="1"/>
-        <v>6.2247642917999998E-4</v>
+        <v>0</v>
       </c>
       <c r="J37" s="16">
         <f t="shared" si="2"/>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,K$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="L37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,L$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,M$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="N37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,N$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,O$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="P37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,P$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,Q$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="R37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,R$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,S$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="T37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,T$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="U37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,U$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="V37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,V$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="W37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,W$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="X37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,X$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Y37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,Y$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Z37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,Z$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AA37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AA$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AB37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AB$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AC37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AC$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AD37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AD$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AE$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AF37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AF$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AG$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AH37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AH$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AI37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AI$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.25">
@@ -15958,11 +16068,11 @@
       </c>
       <c r="D80">
         <f t="shared" ref="D80:F86" si="5">D10</f>
-        <v>0.16449392895100001</v>
+        <v>0.148288948</v>
       </c>
       <c r="E80">
         <f t="shared" si="5"/>
-        <v>0.14828894775500001</v>
+        <v>0.148288948</v>
       </c>
       <c r="F80">
         <f t="shared" si="5"/>
@@ -15974,111 +16084,111 @@
       </c>
       <c r="I80" s="16">
         <f t="shared" si="4"/>
-        <v>0.14828894775500001</v>
+        <v>0.148288948</v>
       </c>
       <c r="J80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,J$9))</f>
-        <v>0.20192405110570355</v>
+        <v>0.20192405133527508</v>
       </c>
       <c r="K80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,K$9))</f>
-        <v>0.21912805260389268</v>
+        <v>0.21912805282851533</v>
       </c>
       <c r="L80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,L$9))</f>
-        <v>0.2412079161321001</v>
+        <v>0.24120791635037137</v>
       </c>
       <c r="M80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,M$9))</f>
-        <v>0.2691050675034683</v>
+        <v>0.26910506771371479</v>
       </c>
       <c r="N80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,N$9))</f>
-        <v>0.30366278259245705</v>
+        <v>0.30366278279276282</v>
       </c>
       <c r="O80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,O$9))</f>
-        <v>0.34543894796969088</v>
+        <v>0.34543894815797949</v>
       </c>
       <c r="P80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,P$9))</f>
-        <v>0.39447645102619855</v>
+        <v>0.39447645120038111</v>
       </c>
       <c r="Q80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Q$9))</f>
-        <v>0.45008738803580778</v>
+        <v>0.45008738819399363</v>
       </c>
       <c r="R80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,R$9))</f>
-        <v>0.51074095955207577</v>
+        <v>0.51074095969281419</v>
       </c>
       <c r="S80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,S$9))</f>
-        <v>0.57414447387750001</v>
+        <v>0.57414447400000002</v>
       </c>
       <c r="T80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,T$9))</f>
-        <v>0.63754798820292424</v>
+        <v>0.63754798830718573</v>
       </c>
       <c r="U80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,U$9))</f>
-        <v>0.69820155971919218</v>
+        <v>0.6982015598060064</v>
       </c>
       <c r="V80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,V$9))</f>
-        <v>0.75381249672880146</v>
+        <v>0.75381249679961881</v>
       </c>
       <c r="W80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,W$9))</f>
-        <v>0.80284999978530913</v>
+        <v>0.80284999984202055</v>
       </c>
       <c r="X80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,X$9))</f>
-        <v>0.84462616516254285</v>
+        <v>0.84462616520723721</v>
       </c>
       <c r="Y80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Y$9))</f>
-        <v>0.87918388025153182</v>
+        <v>0.87918388028628536</v>
       </c>
       <c r="Z80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Z$9))</f>
-        <v>0.90708103162289988</v>
+        <v>0.90708103164962861</v>
       </c>
       <c r="AA80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AA$9))</f>
-        <v>0.92916089515110734</v>
+        <v>0.9291608951714847</v>
       </c>
       <c r="AB80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AB$9))</f>
-        <v>0.94636489664929646</v>
+        <v>0.94636489666472501</v>
       </c>
       <c r="AC80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AC$9))</f>
-        <v>0.95960685965229675</v>
+        <v>0.95960685966391612</v>
       </c>
       <c r="AD80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AD$9))</f>
-        <v>0.96970362495499696</v>
+        <v>0.96970362496371199</v>
       </c>
       <c r="AE80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AE$9))</f>
-        <v>0.97734704661409399</v>
+        <v>0.97734704662061023</v>
       </c>
       <c r="AF80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AF$9))</f>
-        <v>0.98310179232636641</v>
+        <v>0.9831017923312273</v>
       </c>
       <c r="AG80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AG$9))</f>
-        <v>0.98741679392062143</v>
+        <v>0.98741679392424109</v>
       </c>
       <c r="AH80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AH$9))</f>
-        <v>0.99064229953114202</v>
+        <v>0.99064229953383387</v>
       </c>
       <c r="AI80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AI$9))</f>
-        <v>0.99304784793411749</v>
+        <v>0.99304784793611733</v>
       </c>
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.25">
@@ -16087,15 +16197,15 @@
       </c>
       <c r="D81">
         <f t="shared" si="5"/>
-        <v>1.0004432735E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="E81">
         <f t="shared" si="5"/>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="F81">
         <f t="shared" si="5"/>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="G81" s="5" t="str">
         <f>IF(E81=F81,"n/a",IF(OR(C81="battery electric vehicle",C81="natural gas vehicle",C81="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16103,111 +16213,111 @@
       </c>
       <c r="I81" s="16">
         <f t="shared" si="4"/>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="J81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,J$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="K81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,K$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="L81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,L$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="M81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,M$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="N81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,N$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="O81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,O$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="P81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,P$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Q81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Q$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="R81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,R$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="S81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,S$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="T81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,T$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="U81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,U$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="V81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,V$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="W81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,W$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="X81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,X$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Y81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Y$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Z81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Z$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AA81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AA$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AB81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AB$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AC81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AC$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AD81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AD$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AE81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AE$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AF81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AF$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AG81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AG$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AH81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AH$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AI81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AI$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.25">
@@ -16345,15 +16455,15 @@
       </c>
       <c r="D83">
         <f t="shared" si="5"/>
-        <v>6.6777915503600002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="E83">
         <f t="shared" si="5"/>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="F83">
         <f t="shared" si="5"/>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="G83" s="5" t="str">
         <f>IF(E83=F83,"n/a",IF(OR(C83="battery electric vehicle",C83="natural gas vehicle",C83="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16361,111 +16471,111 @@
       </c>
       <c r="I83" s="16">
         <f t="shared" si="4"/>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="J83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,J$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="K83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,K$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="L83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,L$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="M83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,M$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="N83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,N$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="O83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,O$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="P83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,P$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Q83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Q$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="R83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,R$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="S83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,S$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="T83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,T$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="U83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,U$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="V83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,V$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="W83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,W$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="X83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,X$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Y83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Y$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Z83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Z$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AA83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AA$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AB83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AB$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AC83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AC$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AD83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AD$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AE83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AE$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AF83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AF$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AG83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AG$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AH83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AH$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AI83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AI$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.25">
@@ -16474,11 +16584,11 @@
       </c>
       <c r="D84">
         <f t="shared" si="5"/>
-        <v>1.68426429502E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="E84">
         <f t="shared" si="5"/>
-        <v>1.4073498597800001E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="F84">
         <f t="shared" si="5"/>
@@ -16490,111 +16600,111 @@
       </c>
       <c r="I84" s="16">
         <f t="shared" si="4"/>
-        <v>1.4073498597800001E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="J84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,J$9))</f>
-        <v>1.5378299229133533E-2</v>
+        <v>1.5378299625391417E-2</v>
       </c>
       <c r="K84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,K$9))</f>
-        <v>1.5825738202068743E-2</v>
+        <v>1.5825738596288972E-2</v>
       </c>
       <c r="L84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,L$9))</f>
-        <v>1.6422469733855565E-2</v>
+        <v>1.6422470125358253E-2</v>
       </c>
       <c r="M84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,M$9))</f>
-        <v>1.7215045278070985E-2</v>
+        <v>1.7215045665964251E-2</v>
       </c>
       <c r="N84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,N$9))</f>
-        <v>1.8262017381864146E-2</v>
+        <v>1.8262017764989459E-2</v>
       </c>
       <c r="O84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,O$9))</f>
-        <v>1.96351270311391E-2</v>
+        <v>1.9635127408011214E-2</v>
       </c>
       <c r="P84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,P$9))</f>
-        <v>2.1419075563388585E-2</v>
+        <v>2.1419075932136523E-2</v>
       </c>
       <c r="Q84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Q$9))</f>
-        <v>2.3708620826306676E-2</v>
+        <v>2.370862118462793E-2</v>
       </c>
       <c r="R84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,R$9))</f>
-        <v>2.6601382853102151E-2</v>
+        <v>2.6601383198249652E-2</v>
       </c>
       <c r="S84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,S$9))</f>
-        <v>3.0184804135493147E-2</v>
+        <v>3.0184804464321601E-2</v>
       </c>
       <c r="T84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,T$9))</f>
-        <v>3.4516734059794343E-2</v>
+        <v>3.4516734368895005E-2</v>
       </c>
       <c r="U84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,U$9))</f>
-        <v>3.9601619783156121E-2</v>
+        <v>3.9601620069100008E-2</v>
       </c>
       <c r="V84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,V$9))</f>
-        <v>4.5368129944513266E-2</v>
+        <v>4.5368130204196222E-2</v>
       </c>
       <c r="W84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,W$9))</f>
-        <v>5.1657530110720232E-2</v>
+        <v>5.1657530341761002E-2</v>
       </c>
       <c r="X84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,X$9))</f>
-        <v>5.8232082335224832E-2</v>
+        <v>5.8232082536324822E-2</v>
       </c>
       <c r="Y84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Y$9))</f>
-        <v>6.4806634559729431E-2</v>
+        <v>6.4806634730888643E-2</v>
       </c>
       <c r="Z84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Z$9))</f>
-        <v>7.1096034725936397E-2</v>
+        <v>7.1096034868453423E-2</v>
       </c>
       <c r="AA84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AA$9))</f>
-        <v>7.6862544887293549E-2</v>
+        <v>7.6862545003549651E-2</v>
       </c>
       <c r="AB84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AB$9))</f>
-        <v>8.194743061065532E-2</v>
+        <v>8.194743070375464E-2</v>
       </c>
       <c r="AC84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AC$9))</f>
-        <v>8.6279360534956523E-2</v>
+        <v>8.6279360608328054E-2</v>
       </c>
       <c r="AD84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AD$9))</f>
-        <v>8.9862781817347526E-2</v>
+        <v>8.9862781874400013E-2</v>
       </c>
       <c r="AE84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AE$9))</f>
-        <v>9.2755543844143001E-2</v>
+        <v>9.2755543888021721E-2</v>
       </c>
       <c r="AF84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AF$9))</f>
-        <v>9.5045089107061081E-2</v>
+        <v>9.5045089140513128E-2</v>
       </c>
       <c r="AG84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AG$9))</f>
-        <v>9.6829037639310556E-2</v>
+        <v>9.6829037664638448E-2</v>
       </c>
       <c r="AH84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AH$9))</f>
-        <v>9.8202147288585534E-2</v>
+        <v>9.8202147307660206E-2</v>
       </c>
       <c r="AI84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AI$9))</f>
-        <v>9.9249119392378682E-2</v>
+        <v>9.9249119406685404E-2</v>
       </c>
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.25">
@@ -17867,111 +17977,111 @@
       </c>
       <c r="B2">
         <f>Data!I10</f>
-        <v>0.16449392895100001</v>
+        <v>0.148288948</v>
       </c>
       <c r="C2">
         <f>Data!J10</f>
-        <v>0.14828894775500001</v>
+        <v>0.148288948</v>
       </c>
       <c r="D2">
         <f>Data!K10</f>
-        <v>0.18868208810270334</v>
+        <v>0.18868208833608399</v>
       </c>
       <c r="E2">
         <f>Data!L10</f>
-        <v>0.20192405110570355</v>
+        <v>0.20192405133527508</v>
       </c>
       <c r="F2">
         <f>Data!M10</f>
-        <v>0.21912805260389268</v>
+        <v>0.21912805282851533</v>
       </c>
       <c r="G2">
         <f>Data!N10</f>
-        <v>0.2412079161321001</v>
+        <v>0.24120791635037137</v>
       </c>
       <c r="H2">
         <f>Data!O10</f>
-        <v>0.2691050675034683</v>
+        <v>0.26910506771371479</v>
       </c>
       <c r="I2">
         <f>Data!P10</f>
-        <v>0.30366278259245705</v>
+        <v>0.30366278279276282</v>
       </c>
       <c r="J2">
         <f>Data!Q10</f>
-        <v>0.34543894796969088</v>
+        <v>0.34543894815797949</v>
       </c>
       <c r="K2">
         <f>Data!R10</f>
-        <v>0.39447645102619855</v>
+        <v>0.39447645120038111</v>
       </c>
       <c r="L2">
         <f>Data!S10</f>
-        <v>0.45008738803580778</v>
+        <v>0.45008738819399363</v>
       </c>
       <c r="M2">
         <f>Data!T10</f>
-        <v>0.51074095955207577</v>
+        <v>0.51074095969281419</v>
       </c>
       <c r="N2">
         <f>Data!U10</f>
-        <v>0.57414447387750001</v>
+        <v>0.57414447400000002</v>
       </c>
       <c r="O2">
         <f>Data!V10</f>
-        <v>0.63754798820292424</v>
+        <v>0.63754798830718573</v>
       </c>
       <c r="P2">
         <f>Data!W10</f>
-        <v>0.69820155971919218</v>
+        <v>0.6982015598060064</v>
       </c>
       <c r="Q2">
         <f>Data!X10</f>
-        <v>0.75381249672880146</v>
+        <v>0.75381249679961881</v>
       </c>
       <c r="R2">
         <f>Data!Y10</f>
-        <v>0.80284999978530913</v>
+        <v>0.80284999984202055</v>
       </c>
       <c r="S2">
         <f>Data!Z10</f>
-        <v>0.84462616516254285</v>
+        <v>0.84462616520723721</v>
       </c>
       <c r="T2">
         <f>Data!AA10</f>
-        <v>0.87918388025153182</v>
+        <v>0.87918388028628536</v>
       </c>
       <c r="U2">
         <f>Data!AB10</f>
-        <v>0.90708103162289988</v>
+        <v>0.90708103164962861</v>
       </c>
       <c r="V2">
         <f>Data!AC10</f>
-        <v>0.92916089515110734</v>
+        <v>0.9291608951714847</v>
       </c>
       <c r="W2">
         <f>Data!AD10</f>
-        <v>0.94636489664929646</v>
+        <v>0.94636489666472501</v>
       </c>
       <c r="X2">
         <f>Data!AE10</f>
-        <v>0.95960685965229675</v>
+        <v>0.95960685966391612</v>
       </c>
       <c r="Y2">
         <f>Data!AF10</f>
-        <v>0.96970362495499696</v>
+        <v>0.96970362496371199</v>
       </c>
       <c r="Z2">
         <f>Data!AG10</f>
-        <v>0.97734704661409399</v>
+        <v>0.97734704662061023</v>
       </c>
       <c r="AA2">
         <f>Data!AH10</f>
-        <v>0.98310179232636641</v>
+        <v>0.9831017923312273</v>
       </c>
       <c r="AB2">
         <f>Data!AI10</f>
-        <v>0.98741679392062143</v>
+        <v>0.98741679392424109</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -17980,111 +18090,111 @@
       </c>
       <c r="B3">
         <f>Data!I11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="C3">
         <f>Data!J11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="D3">
         <f>Data!K11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="E3">
         <f>Data!L11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="F3">
         <f>Data!M11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="G3">
         <f>Data!N11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="H3">
         <f>Data!O11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="I3">
         <f>Data!P11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="J3">
         <f>Data!Q11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="K3">
         <f>Data!R11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="L3">
         <f>Data!S11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="M3">
         <f>Data!T11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="N3">
         <f>Data!U11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="O3">
         <f>Data!V11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="P3">
         <f>Data!W11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Q3">
         <f>Data!X11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="R3">
         <f>Data!Y11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="S3">
         <f>Data!Z11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="T3">
         <f>Data!AA11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="U3">
         <f>Data!AB11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="V3">
         <f>Data!AC11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="W3">
         <f>Data!AD11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="X3">
         <f>Data!AE11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Y3">
         <f>Data!AF11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="Z3">
         <f>Data!AG11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AA3">
         <f>Data!AH11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
       <c r="AB3">
         <f>Data!AI11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.0097E-4</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -18206,111 +18316,111 @@
       </c>
       <c r="B5">
         <f>Data!I13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="C5">
         <f>Data!J13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="D5">
         <f>Data!K13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="E5">
         <f>Data!L13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="F5">
         <f>Data!M13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="G5">
         <f>Data!N13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="H5">
         <f>Data!O13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="I5">
         <f>Data!P13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="K5">
         <f>Data!R13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="L5">
         <f>Data!S13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="M5">
         <f>Data!T13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="N5">
         <f>Data!U13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="O5">
         <f>Data!V13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="P5">
         <f>Data!W13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7382960000000006E-2</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -18319,111 +18429,111 @@
       </c>
       <c r="B6">
         <f>Data!I14</f>
-        <v>1.68426429502E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="C6">
         <f>Data!J14</f>
-        <v>1.4073498597800001E-2</v>
+        <v>1.4073499E-2</v>
       </c>
       <c r="D6">
         <f>Data!K14</f>
-        <v>1.7532504297315375E-2</v>
+        <v>1.7532504683762919E-2</v>
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>1.9136207441018131E-2</v>
+        <v>1.9136207820162347E-2</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>2.1419075563388582E-2</v>
+        <v>2.1419075932136523E-2</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>2.4601163025518801E-2</v>
+        <v>2.4601163379775384E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>2.8909159010622888E-2</v>
+        <v>2.8909159345260678E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>3.4516734059794343E-2</v>
+        <v>3.4516734368895005E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>4.1454074269529816E-2</v>
+        <v>4.1454074547037548E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>4.9516267729372364E-2</v>
+        <v>4.9516267970164535E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
-        <v>5.8232082335224832E-2</v>
+        <v>5.8232082536324822E-2</v>
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>6.6947896941077292E-2</v>
+        <v>6.694789710248511E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>7.5010090400919854E-2</v>
+        <v>7.5010090525612097E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>8.194743061065532E-2</v>
+        <v>8.1947430703754653E-2</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>8.7555005659826768E-2</v>
+        <v>8.7555005727388974E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>9.1863001644930858E-2</v>
+        <v>9.1863001692874258E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>9.5045089107061081E-2</v>
+        <v>9.5045089140513128E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>9.7327957229431522E-2</v>
+        <v>9.7327957252487315E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>9.8931660373134278E-2</v>
+        <v>9.8931660388886733E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>0.10004169493659409</v>
+        <v>0.1000416949472914</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>0.10080217495518981</v>
+        <v>0.10080217496242386</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>0.10131951704893569</v>
+        <v>0.10131951705381374</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>0.10166977090909066</v>
+        <v>0.10166977091237364</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>0.10190613169392981</v>
+        <v>0.1019061316961364</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>0.10206528444043367</v>
+        <v>0.10206528444191545</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>0.10217229099922295</v>
+        <v>0.10217229100021745</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>0.10224416545984444</v>
+        <v>0.1022441654605116</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -18787,111 +18897,111 @@
       </c>
       <c r="B2">
         <f>Data!I17</f>
-        <v>0.464269858905</v>
+        <v>0.328639128</v>
       </c>
       <c r="C2">
         <f>Data!J17</f>
-        <v>0.21897752724899999</v>
+        <v>0.328639128</v>
       </c>
       <c r="D2">
         <f>Data!K17</f>
-        <v>0.22185959296256283</v>
+        <v>0.32762040015730876</v>
       </c>
       <c r="E2">
         <f>Data!L17</f>
-        <v>0.22282008876622178</v>
+        <v>0.32728089234755592</v>
       </c>
       <c r="F2">
         <f>Data!M17</f>
-        <v>0.22407978427416703</v>
+        <v>0.32683562599529409</v>
       </c>
       <c r="G2">
         <f>Data!N17</f>
-        <v>0.225716384784306</v>
+        <v>0.3262571344990054</v>
       </c>
       <c r="H2">
         <f>Data!O17</f>
-        <v>0.22781682147154225</v>
+        <v>0.32551469017338575</v>
       </c>
       <c r="I2">
         <f>Data!P17</f>
-        <v>0.23047065128960009</v>
+        <v>0.3245766371953786</v>
       </c>
       <c r="J2">
         <f>Data!Q17</f>
-        <v>0.23375809428068739</v>
+        <v>0.32341462007324273</v>
       </c>
       <c r="K2">
         <f>Data!R17</f>
-        <v>0.23773222167048266</v>
+        <v>0.32200987964580063</v>
       </c>
       <c r="L2">
         <f>Data!S17</f>
-        <v>0.24239711329622859</v>
+        <v>0.32036097380721384</v>
       </c>
       <c r="M2">
         <f>Data!T17</f>
-        <v>0.24768732952230915</v>
+        <v>0.31849103359800773</v>
       </c>
       <c r="N2">
         <f>Data!U17</f>
-        <v>0.25345724683461146</v>
+        <v>0.31645153276761123</v>
       </c>
       <c r="O2">
         <f>Data!V17</f>
-        <v>0.25948876362450002</v>
+        <v>0.314319564</v>
       </c>
       <c r="P2">
         <f>Data!W17</f>
-        <v>0.26552028041438847</v>
+        <v>0.31218759523238876</v>
       </c>
       <c r="Q2">
         <f>Data!X17</f>
-        <v>0.27129019772669083</v>
+        <v>0.31014809440199226</v>
       </c>
       <c r="R2">
         <f>Data!Y17</f>
-        <v>0.27658041395277139</v>
+        <v>0.30827815419278615</v>
       </c>
       <c r="S2">
         <f>Data!Z17</f>
-        <v>0.28124530557851735</v>
+        <v>0.30662924835419936</v>
       </c>
       <c r="T2">
         <f>Data!AA17</f>
-        <v>0.28521943296831259</v>
+        <v>0.30522450792675726</v>
       </c>
       <c r="U2">
         <f>Data!AB17</f>
-        <v>0.28850687595939989</v>
+        <v>0.30406249080462139</v>
       </c>
       <c r="V2">
         <f>Data!AC17</f>
-        <v>0.29116070577745773</v>
+        <v>0.30312443782661425</v>
       </c>
       <c r="W2">
         <f>Data!AD17</f>
-        <v>0.29326114246469398</v>
+        <v>0.30238199350099459</v>
       </c>
       <c r="X2">
         <f>Data!AE17</f>
-        <v>0.29489774297483295</v>
+        <v>0.3018035020047059</v>
       </c>
       <c r="Y2">
         <f>Data!AF17</f>
-        <v>0.2961574384827782</v>
+        <v>0.30135823565244407</v>
       </c>
       <c r="Z2">
         <f>Data!AG17</f>
-        <v>0.29711793428643718</v>
+        <v>0.30101872784269124</v>
       </c>
       <c r="AA2">
         <f>Data!AH17</f>
-        <v>0.29784504581265986</v>
+        <v>0.30076171470346302</v>
       </c>
       <c r="AB2">
         <f>Data!AI17</f>
-        <v>0.29839248936928919</v>
+        <v>0.30056820905547738</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -18900,111 +19010,111 @@
       </c>
       <c r="B3">
         <f>Data!I18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="C3">
         <f>Data!J18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="D3">
         <f>Data!K18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="E3">
         <f>Data!L18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="F3">
         <f>Data!M18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="G3">
         <f>Data!N18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="H3">
         <f>Data!O18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="I3">
         <f>Data!P18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="J3">
         <f>Data!Q18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="K3">
         <f>Data!R18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="L3">
         <f>Data!S18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="M3">
         <f>Data!T18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="N3">
         <f>Data!U18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="O3">
         <f>Data!V18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="P3">
         <f>Data!W18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="Q3">
         <f>Data!X18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="R3">
         <f>Data!Y18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="S3">
         <f>Data!Z18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="T3">
         <f>Data!AA18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="U3">
         <f>Data!AB18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="V3">
         <f>Data!AC18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="W3">
         <f>Data!AD18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="X3">
         <f>Data!AE18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="Y3">
         <f>Data!AF18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="Z3">
         <f>Data!AG18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AA3">
         <f>Data!AH18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
       <c r="AB3">
         <f>Data!AI18</f>
-        <v>0</v>
+        <v>0.250478074</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -19013,111 +19123,111 @@
       </c>
       <c r="B4">
         <f>Data!I19</f>
-        <v>1</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="C4">
         <f>Data!J19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="D4">
         <f>Data!K19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="E4">
         <f>Data!L19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="F4">
         <f>Data!M19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="G4">
         <f>Data!N19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="H4">
         <f>Data!O19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="I4">
         <f>Data!P19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="J4">
         <f>Data!Q19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="K4">
         <f>Data!R19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="L4">
         <f>Data!S19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="M4">
         <f>Data!T19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="N4">
         <f>Data!U19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="O4">
         <f>Data!V19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="P4">
         <f>Data!W19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="Q4">
         <f>Data!X19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="R4">
         <f>Data!Y19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="S4">
         <f>Data!Z19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="T4">
         <f>Data!AA19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="U4">
         <f>Data!AB19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="V4">
         <f>Data!AC19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="W4">
         <f>Data!AD19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="X4">
         <f>Data!AE19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="Y4">
         <f>Data!AF19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="Z4">
         <f>Data!AG19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AA4">
         <f>Data!AH19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
       <c r="AB4">
         <f>Data!AI19</f>
-        <v>0.95569574619999997</v>
+        <v>0.76148265500000001</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -19126,7 +19236,7 @@
       </c>
       <c r="B5">
         <f>Data!I20</f>
-        <v>0.97299803336400004</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <f>Data!J20</f>
@@ -19239,111 +19349,111 @@
       </c>
       <c r="B6">
         <f>Data!I21</f>
-        <v>0</v>
+        <v>1.003192E-3</v>
       </c>
       <c r="C6">
         <f>Data!J21</f>
-        <v>9.0197447039299999E-4</v>
+        <v>1.003192E-3</v>
       </c>
       <c r="D6">
         <f>Data!K21</f>
-        <v>9.1384577850523699E-4</v>
+        <v>1.0114628802088777E-3</v>
       </c>
       <c r="E6">
         <f>Data!L21</f>
-        <v>9.1780208719455226E-4</v>
+        <v>1.0142192870790641E-3</v>
       </c>
       <c r="F6">
         <f>Data!M21</f>
-        <v>9.229908077126324E-4</v>
+        <v>1.0178343297884813E-3</v>
       </c>
       <c r="G6">
         <f>Data!N21</f>
-        <v>9.2973201032334131E-4</v>
+        <v>1.0225310050604737E-3</v>
       </c>
       <c r="H6">
         <f>Data!O21</f>
-        <v>9.3838376693218116E-4</v>
+        <v>1.0285587858097846E-3</v>
       </c>
       <c r="I6">
         <f>Data!P21</f>
-        <v>9.4931496509999139E-4</v>
+        <v>1.0361746803456418E-3</v>
       </c>
       <c r="J6">
         <f>Data!Q21</f>
-        <v>9.6285603339172255E-4</v>
+        <v>1.0456089021417803E-3</v>
       </c>
       <c r="K6">
         <f>Data!R21</f>
-        <v>9.7922557364874116E-4</v>
+        <v>1.0570137536762662E-3</v>
       </c>
       <c r="L6">
         <f>Data!S21</f>
-        <v>9.9844039083310217E-4</v>
+        <v>1.0704009431641303E-3</v>
       </c>
       <c r="M6">
         <f>Data!T21</f>
-        <v>1.020230937281997E-3</v>
+        <v>1.0855826735733526E-3</v>
       </c>
       <c r="N6">
         <f>Data!U21</f>
-        <v>1.0439973857269895E-3</v>
+        <v>1.1021410381798931E-3</v>
       </c>
       <c r="O6">
         <f>Data!V21</f>
-        <v>1.0688413696305979E-3</v>
+        <v>1.1194501344340981E-3</v>
       </c>
       <c r="P6">
         <f>Data!W21</f>
-        <v>1.0936853535342065E-3</v>
+        <v>1.1367592306883029E-3</v>
       </c>
       <c r="Q6">
         <f>Data!X21</f>
-        <v>1.117451801979199E-3</v>
+        <v>1.1533175952948434E-3</v>
       </c>
       <c r="R6">
         <f>Data!Y21</f>
-        <v>1.1392423484280938E-3</v>
+        <v>1.1684993257040656E-3</v>
       </c>
       <c r="S6">
         <f>Data!Z21</f>
-        <v>1.1584571656124548E-3</v>
+        <v>1.1818865151919297E-3</v>
       </c>
       <c r="T6">
         <f>Data!AA21</f>
-        <v>1.1748267058694735E-3</v>
+        <v>1.1932913667264157E-3</v>
       </c>
       <c r="U6">
         <f>Data!AB21</f>
-        <v>1.1883677741612046E-3</v>
+        <v>1.2027255885225542E-3</v>
       </c>
       <c r="V6">
         <f>Data!AC21</f>
-        <v>1.1992989723290147E-3</v>
+        <v>1.2103414830584114E-3</v>
       </c>
       <c r="W6">
         <f>Data!AD21</f>
-        <v>1.2079507289378547E-3</v>
+        <v>1.2163692638077223E-3</v>
       </c>
       <c r="X6">
         <f>Data!AE21</f>
-        <v>1.2146919315485635E-3</v>
+        <v>1.2210659390797147E-3</v>
       </c>
       <c r="Y6">
         <f>Data!AF21</f>
-        <v>1.2198806520666437E-3</v>
+        <v>1.2246809817891319E-3</v>
       </c>
       <c r="Z6">
         <f>Data!AG21</f>
-        <v>1.223836960755959E-3</v>
+        <v>1.2274373886593183E-3</v>
       </c>
       <c r="AA6">
         <f>Data!AH21</f>
-        <v>1.2268319531737681E-3</v>
+        <v>1.2295240351585918E-3</v>
       </c>
       <c r="AB6">
         <f>Data!AI21</f>
-        <v>1.2290868882726532E-3</v>
+        <v>1.2310950750057041E-3</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -19352,111 +19462,111 @@
       </c>
       <c r="B7">
         <f>Data!I22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="C7">
         <f>Data!J22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="D7">
         <f>Data!K22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="E7">
         <f>Data!L22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="F7">
         <f>Data!M22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="G7">
         <f>Data!N22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="H7">
         <f>Data!O22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="I7">
         <f>Data!P22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="J7">
         <f>Data!Q22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="K7">
         <f>Data!R22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="L7">
         <f>Data!S22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="M7">
         <f>Data!T22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="N7">
         <f>Data!U22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="O7">
         <f>Data!V22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="P7">
         <f>Data!W22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="Q7">
         <f>Data!X22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="R7">
         <f>Data!Y22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="S7">
         <f>Data!Z22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="T7">
         <f>Data!AA22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="U7">
         <f>Data!AB22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="V7">
         <f>Data!AC22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="W7">
         <f>Data!AD22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="X7">
         <f>Data!AE22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="Y7">
         <f>Data!AF22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="Z7">
         <f>Data!AG22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AA7">
         <f>Data!AH22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
       <c r="AB7">
         <f>Data!AI22</f>
-        <v>0</v>
+        <v>6.0223199999999996E-4</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -19469,107 +19579,107 @@
       </c>
       <c r="C8">
         <f>Data!J23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f>Data!K23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f>Data!L23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>Data!M23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>Data!N23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f>Data!O23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f>Data!P23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f>Data!Q23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f>Data!R23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f>Data!S23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f>Data!T23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f>Data!U23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f>Data!V23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f>Data!W23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f>Data!X23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f>Data!Y23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f>Data!Z23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f>Data!AA23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f>Data!AB23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f>Data!AC23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f>Data!AD23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f>Data!AE23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f>Data!AF23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f>Data!AG23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f>Data!AH23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f>Data!AI23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19707,111 +19817,111 @@
       </c>
       <c r="B2">
         <f>Data!I24</f>
-        <v>3.1162890650799999E-2</v>
+        <v>0.12184009799999999</v>
       </c>
       <c r="C2">
         <f>Data!J24</f>
-        <v>3.0635270769200001E-2</v>
+        <v>0.12184009799999999</v>
       </c>
       <c r="D2">
         <f>Data!K24</f>
-        <v>5.6223929708727458E-2</v>
+        <v>0.1441844927675226</v>
       </c>
       <c r="E2">
         <f>Data!L24</f>
-        <v>6.4751771186114582E-2</v>
+        <v>0.15163112984748478</v>
       </c>
       <c r="F2">
         <f>Data!M24</f>
-        <v>7.593608199789606E-2</v>
+        <v>0.16139743516937402</v>
       </c>
       <c r="G2">
         <f>Data!N24</f>
-        <v>9.0466775061945975E-2</v>
+        <v>0.17408585087869802</v>
       </c>
       <c r="H2">
         <f>Data!O24</f>
-        <v>0.10911567600852309</v>
+        <v>0.19037034651074775</v>
       </c>
       <c r="I2">
         <f>Data!P24</f>
-        <v>0.13267792366244005</v>
+        <v>0.21094524902648606</v>
       </c>
       <c r="J2">
         <f>Data!Q24</f>
-        <v>0.16186575830694638</v>
+        <v>0.23643249715649947</v>
       </c>
       <c r="K2">
         <f>Data!R24</f>
-        <v>0.19715037721106998</v>
+        <v>0.26724354731268585</v>
       </c>
       <c r="L2">
         <f>Data!S24</f>
-        <v>0.2385680035473921</v>
+        <v>0.30341003010412881</v>
       </c>
       <c r="M2">
         <f>Data!T24</f>
-        <v>0.2855376260957222</v>
+        <v>0.34442459795552233</v>
       </c>
       <c r="N2">
         <f>Data!U24</f>
-        <v>0.33676631443512162</v>
+        <v>0.38915824493495493</v>
       </c>
       <c r="O2">
         <f>Data!V24</f>
-        <v>0.39031763538459996</v>
+        <v>0.43592004900000003</v>
       </c>
       <c r="P2">
         <f>Data!W24</f>
-        <v>0.4438689563340783</v>
+        <v>0.48268185306504513</v>
       </c>
       <c r="Q2">
         <f>Data!X24</f>
-        <v>0.49509764467347783</v>
+        <v>0.52741550004447768</v>
       </c>
       <c r="R2">
         <f>Data!Y24</f>
-        <v>0.54206726722180787</v>
+        <v>0.56843006789587125</v>
       </c>
       <c r="S2">
         <f>Data!Z24</f>
-        <v>0.58348489355812994</v>
+        <v>0.6045965506873141</v>
       </c>
       <c r="T2">
         <f>Data!AA24</f>
-        <v>0.61876951246225353</v>
+        <v>0.63540760084350045</v>
       </c>
       <c r="U2">
         <f>Data!AB24</f>
-        <v>0.64795734710676001</v>
+        <v>0.66089484897351403</v>
       </c>
       <c r="V2">
         <f>Data!AC24</f>
-        <v>0.67151959476067691</v>
+        <v>0.68146975148925226</v>
       </c>
       <c r="W2">
         <f>Data!AD24</f>
-        <v>0.69016849570725403</v>
+        <v>0.69775424712130196</v>
       </c>
       <c r="X2">
         <f>Data!AE24</f>
-        <v>0.704699188771304</v>
+        <v>0.71044266283062596</v>
       </c>
       <c r="Y2">
         <f>Data!AF24</f>
-        <v>0.7158834995830855</v>
+        <v>0.72020896815251523</v>
       </c>
       <c r="Z2">
         <f>Data!AG24</f>
-        <v>0.72441134106047256</v>
+        <v>0.72765560523247741</v>
       </c>
       <c r="AA2">
         <f>Data!AH24</f>
-        <v>0.73086706091722453</v>
+        <v>0.73329283512126131</v>
       </c>
       <c r="AB2">
         <f>Data!AI24</f>
-        <v>0.73572758383774906</v>
+        <v>0.73753711549443191</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -19820,111 +19930,111 @@
       </c>
       <c r="B3">
         <f>Data!I25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="C3">
         <f>Data!J25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="D3">
         <f>Data!K25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="E3">
         <f>Data!L25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="F3">
         <f>Data!M25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="G3">
         <f>Data!N25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="H3">
         <f>Data!O25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="I3">
         <f>Data!P25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="J3">
         <f>Data!Q25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="K3">
         <f>Data!R25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="L3">
         <f>Data!S25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="M3">
         <f>Data!T25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="N3">
         <f>Data!U25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="O3">
         <f>Data!V25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="P3">
         <f>Data!W25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="Q3">
         <f>Data!X25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="R3">
         <f>Data!Y25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="S3">
         <f>Data!Z25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="T3">
         <f>Data!AA25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="U3">
         <f>Data!AB25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="V3">
         <f>Data!AC25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="W3">
         <f>Data!AD25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="X3">
         <f>Data!AE25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="Y3">
         <f>Data!AF25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="Z3">
         <f>Data!AG25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AA3">
         <f>Data!AH25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
       <c r="AB3">
         <f>Data!AI25</f>
-        <v>0</v>
+        <v>1.5737247999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -19933,111 +20043,111 @@
       </c>
       <c r="B4">
         <f>Data!I26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="C4">
         <f>Data!J26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="D4">
         <f>Data!K26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="E4">
         <f>Data!L26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="F4">
         <f>Data!M26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="G4">
         <f>Data!N26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="H4">
         <f>Data!O26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="I4">
         <f>Data!P26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="J4">
         <f>Data!Q26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="K4">
         <f>Data!R26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="L4">
         <f>Data!S26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="M4">
         <f>Data!T26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="N4">
         <f>Data!U26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="O4">
         <f>Data!V26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="P4">
         <f>Data!W26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="Q4">
         <f>Data!X26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="R4">
         <f>Data!Y26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="S4">
         <f>Data!Z26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="T4">
         <f>Data!AA26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="U4">
         <f>Data!AB26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="V4">
         <f>Data!AC26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="W4">
         <f>Data!AD26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="X4">
         <f>Data!AE26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="Y4">
         <f>Data!AF26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="Z4">
         <f>Data!AG26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AA4">
         <f>Data!AH26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
       <c r="AB4">
         <f>Data!AI26</f>
-        <v>0</v>
+        <v>0.37956814</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -20272,111 +20382,111 @@
       </c>
       <c r="B7">
         <f>Data!I29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="C7">
         <f>Data!J29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="D7">
         <f>Data!K29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="E7">
         <f>Data!L29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="F7">
         <f>Data!M29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="G7">
         <f>Data!N29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="H7">
         <f>Data!O29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="I7">
         <f>Data!P29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="J7">
         <f>Data!Q29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="K7">
         <f>Data!R29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="L7">
         <f>Data!S29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="M7">
         <f>Data!T29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="N7">
         <f>Data!U29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="O7">
         <f>Data!V29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="P7">
         <f>Data!W29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="Q7">
         <f>Data!X29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="R7">
         <f>Data!Y29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="S7">
         <f>Data!Z29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="T7">
         <f>Data!AA29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="U7">
         <f>Data!AB29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="V7">
         <f>Data!AC29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="W7">
         <f>Data!AD29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="X7">
         <f>Data!AE29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="Y7">
         <f>Data!AF29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="Z7">
         <f>Data!AG29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AA7">
         <f>Data!AH29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
       <c r="AB7">
         <f>Data!AI29</f>
-        <v>0</v>
+        <v>5.5449391000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -20385,111 +20495,111 @@
       </c>
       <c r="B8">
         <f>Data!I30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="C8">
         <f>Data!J30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="D8">
         <f>Data!K30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="E8">
         <f>Data!L30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="F8">
         <f>Data!M30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="G8">
         <f>Data!N30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="H8">
         <f>Data!O30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="I8">
         <f>Data!P30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="J8">
         <f>Data!Q30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="K8">
         <f>Data!R30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="L8">
         <f>Data!S30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="M8">
         <f>Data!T30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="N8">
         <f>Data!U30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="O8">
         <f>Data!V30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="P8">
         <f>Data!W30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="Q8">
         <f>Data!X30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="R8">
         <f>Data!Y30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="S8">
         <f>Data!Z30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="T8">
         <f>Data!AA30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="U8">
         <f>Data!AB30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="V8">
         <f>Data!AC30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="W8">
         <f>Data!AD30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="X8">
         <f>Data!AE30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="Y8">
         <f>Data!AF30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="Z8">
         <f>Data!AG30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AA8">
         <f>Data!AH30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
       <c r="AB8">
         <f>Data!AI30</f>
-        <v>0</v>
+        <v>2.0286950000000001E-3</v>
       </c>
     </row>
   </sheetData>
@@ -20627,111 +20737,111 @@
       </c>
       <c r="B2">
         <f>Data!I31</f>
-        <v>4.7973229575300003E-3</v>
+        <v>4.8089680000000003E-3</v>
       </c>
       <c r="C2">
         <f>Data!J31</f>
-        <v>6.1405058414400002E-3</v>
+        <v>4.8089680000000003E-3</v>
       </c>
       <c r="D2">
         <f>Data!K31</f>
-        <v>1.4814878064083456E-2</v>
+        <v>1.3530704607224994E-2</v>
       </c>
       <c r="E2">
         <f>Data!L31</f>
-        <v>1.7705755284549454E-2</v>
+        <v>1.6437366787908719E-2</v>
       </c>
       <c r="F2">
         <f>Data!M31</f>
-        <v>2.1497156594966059E-2</v>
+        <v>2.0249470160118424E-2</v>
       </c>
       <c r="G2">
         <f>Data!N31</f>
-        <v>2.6422957536251346E-2</v>
+        <v>2.520216728756761E-2</v>
       </c>
       <c r="H2">
         <f>Data!O31</f>
-        <v>3.2744801472509036E-2</v>
+        <v>3.155853017687181E-2</v>
       </c>
       <c r="I2">
         <f>Data!P31</f>
-        <v>4.0732234773926027E-2</v>
+        <v>3.9589576993249581E-2</v>
       </c>
       <c r="J2">
         <f>Data!Q31</f>
-        <v>5.0626701798468406E-2</v>
+        <v>4.9538070445221086E-2</v>
       </c>
       <c r="K2">
         <f>Data!R31</f>
-        <v>6.2587935047612731E-2</v>
+        <v>6.1564615216299301E-2</v>
       </c>
       <c r="L2">
         <f>Data!S31</f>
-        <v>7.6628213917586716E-2</v>
+        <v>7.5681557751488576E-2</v>
       </c>
       <c r="M2">
         <f>Data!T31</f>
-        <v>9.2550579763493207E-2</v>
+        <v>9.1690863959189184E-2</v>
       </c>
       <c r="N2">
         <f>Data!U31</f>
-        <v>0.10991673842713874</v>
+        <v>0.10915184647827197</v>
       </c>
       <c r="O2">
         <f>Data!V31</f>
-        <v>0.12807025292072</v>
+        <v>0.12740448400000001</v>
       </c>
       <c r="P2">
         <f>Data!W31</f>
-        <v>0.14622376741430126</v>
+        <v>0.14565712152172802</v>
       </c>
       <c r="Q2">
         <f>Data!X31</f>
-        <v>0.16358992607794678</v>
+        <v>0.16311810404081081</v>
       </c>
       <c r="R2">
         <f>Data!Y31</f>
-        <v>0.17951229192385326</v>
+        <v>0.17912741024851142</v>
       </c>
       <c r="S2">
         <f>Data!Z31</f>
-        <v>0.19355257079382726</v>
+        <v>0.1932443527837007</v>
       </c>
       <c r="T2">
         <f>Data!AA31</f>
-        <v>0.20551380404297159</v>
+        <v>0.2052708975547789</v>
       </c>
       <c r="U2">
         <f>Data!AB31</f>
-        <v>0.21540827106751401</v>
+        <v>0.21521939100675044</v>
       </c>
       <c r="V2">
         <f>Data!AC31</f>
-        <v>0.22339570436893097</v>
+        <v>0.2232504378231282</v>
       </c>
       <c r="W2">
         <f>Data!AD31</f>
-        <v>0.22971754830518867</v>
+        <v>0.22960680071243239</v>
       </c>
       <c r="X2">
         <f>Data!AE31</f>
-        <v>0.23464334924647395</v>
+        <v>0.23455949783988159</v>
       </c>
       <c r="Y2">
         <f>Data!AF31</f>
-        <v>0.23843475055689056</v>
+        <v>0.23837160121209131</v>
       </c>
       <c r="Z2">
         <f>Data!AG31</f>
-        <v>0.24132562777735656</v>
+        <v>0.241278263392775</v>
       </c>
       <c r="AA2">
         <f>Data!AH31</f>
-        <v>0.24351407060020699</v>
+        <v>0.24347865569679086</v>
       </c>
       <c r="AB2">
         <f>Data!AI31</f>
-        <v>0.2451617530797367</v>
+        <v>0.24513533496186604</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -20740,111 +20850,111 @@
       </c>
       <c r="B3">
         <f>Data!I32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="C3">
         <f>Data!J32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="D3">
         <f>Data!K32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="E3">
         <f>Data!L32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="F3">
         <f>Data!M32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="G3">
         <f>Data!N32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="H3">
         <f>Data!O32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="I3">
         <f>Data!P32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="J3">
         <f>Data!Q32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="K3">
         <f>Data!R32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="L3">
         <f>Data!S32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="M3">
         <f>Data!T32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="N3">
         <f>Data!U32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="O3">
         <f>Data!V32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="P3">
         <f>Data!W32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="Q3">
         <f>Data!X32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="R3">
         <f>Data!Y32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="S3">
         <f>Data!Z32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="T3">
         <f>Data!AA32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="U3">
         <f>Data!AB32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="V3">
         <f>Data!AC32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="W3">
         <f>Data!AD32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="X3">
         <f>Data!AE32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="Y3">
         <f>Data!AF32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="Z3">
         <f>Data!AG32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AA3">
         <f>Data!AH32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
       <c r="AB3">
         <f>Data!AI32</f>
-        <v>0</v>
+        <v>2.2159679000000002E-2</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -20853,111 +20963,111 @@
       </c>
       <c r="B4">
         <f>Data!I33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="C4">
         <f>Data!J33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="D4">
         <f>Data!K33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="E4">
         <f>Data!L33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="F4">
         <f>Data!M33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="G4">
         <f>Data!N33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="H4">
         <f>Data!O33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="I4">
         <f>Data!P33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="J4">
         <f>Data!Q33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="K4">
         <f>Data!R33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="L4">
         <f>Data!S33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="M4">
         <f>Data!T33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="N4">
         <f>Data!U33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="O4">
         <f>Data!V33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="P4">
         <f>Data!W33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="Q4">
         <f>Data!X33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="R4">
         <f>Data!Y33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="S4">
         <f>Data!Z33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="T4">
         <f>Data!AA33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="U4">
         <f>Data!AB33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="V4">
         <f>Data!AC33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="W4">
         <f>Data!AD33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="X4">
         <f>Data!AE33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="Y4">
         <f>Data!AF33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="Z4">
         <f>Data!AG33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AA4">
         <f>Data!AH33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
       <c r="AB4">
         <f>Data!AI33</f>
-        <v>0</v>
+        <v>7.5358100000000002E-4</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -21305,111 +21415,111 @@
       </c>
       <c r="B8">
         <f>Data!I37</f>
-        <v>6.2247642917999998E-4</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f>Data!J37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f>Data!K37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f>Data!L37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>Data!M37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>Data!N37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f>Data!O37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f>Data!P37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f>Data!Q37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f>Data!R37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f>Data!S37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f>Data!T37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f>Data!U37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f>Data!V37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f>Data!W37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f>Data!X37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f>Data!Y37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f>Data!Z37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f>Data!AA37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f>Data!AB37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f>Data!AC37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f>Data!AD37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f>Data!AE37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f>Data!AF37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f>Data!AG37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f>Data!AH37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f>Data!AI37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -5,29 +5,30 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\.claude\worktrees\angry-germain-b7fbd2\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-rail-vintaging\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80222AC-8B02-4792-810B-E20D95065644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80EA775-6AC6-443E-9E62-5458D18CC890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="43200" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="43200" windowHeight="17145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="SYVbT-passenger" sheetId="2" r:id="rId2"/>
-    <sheet name="Data" sheetId="3" r:id="rId3"/>
-    <sheet name="TTS-LDVs-psgr" sheetId="4" r:id="rId4"/>
-    <sheet name="TTS-LDVs-frgt" sheetId="5" r:id="rId5"/>
-    <sheet name="TTS-HDVs-psgr" sheetId="6" r:id="rId6"/>
-    <sheet name="TTS-HDVs-frgt" sheetId="7" r:id="rId7"/>
-    <sheet name="TTS-aircraft-psgr" sheetId="8" r:id="rId8"/>
-    <sheet name="TTS-aircraft-frgt" sheetId="9" r:id="rId9"/>
-    <sheet name="TTS-rail-psgr" sheetId="10" r:id="rId10"/>
-    <sheet name="TTS-rail-frgt" sheetId="11" r:id="rId11"/>
-    <sheet name="TTS-ships-psgr" sheetId="12" r:id="rId12"/>
-    <sheet name="TTS-ships-frgt" sheetId="13" r:id="rId13"/>
-    <sheet name="TTS-motorbikes-psgr" sheetId="14" r:id="rId14"/>
-    <sheet name="TTS-motorbikes-frgt" sheetId="15" r:id="rId15"/>
+    <sheet name="Calibration rail" sheetId="16" r:id="rId2"/>
+    <sheet name="SYVbT-passenger" sheetId="2" r:id="rId3"/>
+    <sheet name="Data" sheetId="3" r:id="rId4"/>
+    <sheet name="TTS-LDVs-psgr" sheetId="4" r:id="rId5"/>
+    <sheet name="TTS-LDVs-frgt" sheetId="5" r:id="rId6"/>
+    <sheet name="TTS-HDVs-psgr" sheetId="6" r:id="rId7"/>
+    <sheet name="TTS-HDVs-frgt" sheetId="7" r:id="rId8"/>
+    <sheet name="TTS-aircraft-psgr" sheetId="8" r:id="rId9"/>
+    <sheet name="TTS-aircraft-frgt" sheetId="9" r:id="rId10"/>
+    <sheet name="TTS-rail-psgr" sheetId="10" r:id="rId11"/>
+    <sheet name="TTS-rail-frgt" sheetId="11" r:id="rId12"/>
+    <sheet name="TTS-ships-psgr" sheetId="12" r:id="rId13"/>
+    <sheet name="TTS-ships-frgt" sheetId="13" r:id="rId14"/>
+    <sheet name="TTS-motorbikes-psgr" sheetId="14" r:id="rId15"/>
+    <sheet name="TTS-motorbikes-frgt" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="95">
   <si>
     <t>TTS Transportation Technology Shareweights</t>
   </si>
@@ -317,6 +318,21 @@
   </si>
   <si>
     <t>TTS-LDVs-frgt plugin hybrid vehicle: 2050 target pinned at its pre-calibration value 0.00123571 (was =E21/E17*F17)</t>
+  </si>
+  <si>
+    <t>Passenger-rail shareweights at the start year, solved by eps-calibrate step 3a (solve_base_year.py: logit inversion from 'BAU New Vehicle Cost per Mile' in a BAU export and the observed new-vehicle shares), 2026-10-19. Observed shares: vehicles delivered 2015-2024, NTD transit + Amtrak, 376 diesel of 4,528 (vehicle-vintaging-4.0.7/data/fleet-utilization/ntd-energy/rail_purchase_share.py). Held flat through 2050.</t>
+  </si>
+  <si>
+    <t>technology</t>
+  </si>
+  <si>
+    <t>observed share of new vehicles</t>
+  </si>
+  <si>
+    <t>shareweight (solved)</t>
+  </si>
+  <si>
+    <t>Passenger rail (2026-10-19): Data!E52 and E55 now read the solved shareweights on 'Calibration rail' (step 3a, observed 2015-2024 deliveries, 8.3% diesel) instead of the start-year fleet shares; pasted SYVbT-passenger refreshed.</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="63.42578125" customWidth="1"/>
@@ -1361,6 +1377,11 @@
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1373,6 +1394,926 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1">
+        <f>Data!I9</f>
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <f>Data!J9</f>
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <f>Data!K9</f>
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <f>Data!L9</f>
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <f>Data!M9</f>
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <f>Data!N9</f>
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <f>Data!O9</f>
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <f>Data!P9</f>
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <f>Data!Q9</f>
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <f>Data!R9</f>
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <f>Data!S9</f>
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <f>Data!T9</f>
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <f>Data!U9</f>
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <f>Data!V9</f>
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <f>Data!W9</f>
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <f>Data!X9</f>
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <f>Data!Y9</f>
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <f>Data!Z9</f>
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <f>Data!AA9</f>
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <f>Data!AB9</f>
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <f>Data!AC9</f>
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <f>Data!AD9</f>
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <f>Data!AE9</f>
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <f>Data!AF9</f>
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <f>Data!AG9</f>
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <f>Data!AH9</f>
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <f>Data!AI9</f>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <f>Data!I45</f>
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <f>Data!J45</f>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>Data!K45</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>Data!L45</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>Data!M45</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>Data!N45</f>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <f>Data!O45</f>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>Data!P45</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>Data!Q45</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>Data!R45</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>Data!S45</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>Data!T45</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>Data!U45</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>Data!V45</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>Data!W45</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>Data!X45</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>Data!Y45</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>Data!Z45</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>Data!AA45</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>Data!AB45</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f>Data!AC45</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f>Data!AD45</f>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f>Data!AE45</f>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f>Data!AF45</f>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f>Data!AG45</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>Data!AH45</f>
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <f>Data!AI45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <f>Data!I46</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>Data!J46</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>Data!K46</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>Data!L46</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>Data!M46</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>Data!N46</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>Data!O46</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>Data!P46</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>Data!Q46</f>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f>Data!R46</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>Data!S46</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>Data!T46</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>Data!U46</f>
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f>Data!V46</f>
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <f>Data!W46</f>
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <f>Data!X46</f>
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <f>Data!Y46</f>
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <f>Data!Z46</f>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <f>Data!AA46</f>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f>Data!AB46</f>
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <f>Data!AC46</f>
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <f>Data!AD46</f>
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <f>Data!AE46</f>
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <f>Data!AF46</f>
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <f>Data!AG46</f>
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f>Data!AH46</f>
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <f>Data!AI46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <f>Data!I47</f>
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <f>Data!J47</f>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f>Data!K47</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>Data!L47</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>Data!M47</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>Data!N47</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>Data!O47</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f>Data!P47</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>Data!Q47</f>
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f>Data!R47</f>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f>Data!S47</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f>Data!T47</f>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>Data!U47</f>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f>Data!V47</f>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f>Data!W47</f>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f>Data!X47</f>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f>Data!Y47</f>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f>Data!Z47</f>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f>Data!AA47</f>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f>Data!AB47</f>
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <f>Data!AC47</f>
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <f>Data!AD47</f>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f>Data!AE47</f>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <f>Data!AF47</f>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f>Data!AG47</f>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f>Data!AH47</f>
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <f>Data!AI47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <f>Data!I48</f>
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <f>Data!J48</f>
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <f>Data!K48</f>
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <f>Data!L48</f>
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <f>Data!M48</f>
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <f>Data!N48</f>
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <f>Data!O48</f>
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <f>Data!P48</f>
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <f>Data!Q48</f>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <f>Data!R48</f>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <f>Data!S48</f>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <f>Data!T48</f>
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <f>Data!U48</f>
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <f>Data!V48</f>
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <f>Data!W48</f>
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <f>Data!X48</f>
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <f>Data!Y48</f>
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <f>Data!Z48</f>
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <f>Data!AA48</f>
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <f>Data!AB48</f>
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <f>Data!AC48</f>
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <f>Data!AD48</f>
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <f>Data!AE48</f>
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <f>Data!AF48</f>
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <f>Data!AG48</f>
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <f>Data!AH48</f>
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <f>Data!AI48</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6">
+        <f>Data!I49</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f>Data!J49</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>Data!K49</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>Data!L49</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>Data!M49</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f>Data!N49</f>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>Data!O49</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>Data!P49</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>Data!Q49</f>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>Data!R49</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f>Data!S49</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>Data!T49</f>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>Data!U49</f>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f>Data!V49</f>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f>Data!W49</f>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f>Data!X49</f>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f>Data!Y49</f>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f>Data!Z49</f>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f>Data!AA49</f>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f>Data!AB49</f>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f>Data!AC49</f>
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <f>Data!AD49</f>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f>Data!AE49</f>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f>Data!AF49</f>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f>Data!AG49</f>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f>Data!AH49</f>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f>Data!AI49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7">
+        <f>Data!I50</f>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f>Data!J50</f>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f>Data!K50</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>Data!L50</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>Data!M50</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>Data!N50</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>Data!O50</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f>Data!P50</f>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f>Data!Q50</f>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f>Data!R50</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f>Data!S50</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f>Data!T50</f>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f>Data!U50</f>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f>Data!V50</f>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f>Data!W50</f>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f>Data!X50</f>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f>Data!Y50</f>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f>Data!Z50</f>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f>Data!AA50</f>
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f>Data!AB50</f>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <f>Data!AC50</f>
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <f>Data!AD50</f>
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <f>Data!AE50</f>
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <f>Data!AF50</f>
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <f>Data!AG50</f>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f>Data!AH50</f>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f>Data!AI50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8">
+        <f>Data!I51</f>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f>Data!J51</f>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f>Data!K51</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>Data!L51</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f>Data!M51</f>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f>Data!N51</f>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f>Data!O51</f>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f>Data!P51</f>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f>Data!Q51</f>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f>Data!R51</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>Data!S51</f>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f>Data!T51</f>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f>Data!U51</f>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f>Data!V51</f>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f>Data!W51</f>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f>Data!X51</f>
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f>Data!Y51</f>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <f>Data!Z51</f>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f>Data!AA51</f>
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f>Data!AB51</f>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f>Data!AC51</f>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <f>Data!AD51</f>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f>Data!AE51</f>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f>Data!AF51</f>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f>Data!AG51</f>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f>Data!AH51</f>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f>Data!AI51</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -1502,111 +2443,111 @@
       </c>
       <c r="B2">
         <f>Data!I52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <f>Data!J52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <f>Data!K52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <f>Data!L52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <f>Data!M52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <f>Data!N52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <f>Data!O52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <f>Data!P52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <f>Data!Q52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f>Data!R52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <f>Data!S52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <f>Data!T52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="N2">
         <f>Data!U52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <f>Data!V52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <f>Data!W52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="Q2">
         <f>Data!X52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <f>Data!Y52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="S2">
         <f>Data!Z52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <f>Data!AA52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="U2">
         <f>Data!AB52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="V2">
         <f>Data!AC52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="W2">
         <f>Data!AD52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="X2">
         <f>Data!AE52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="Y2">
         <f>Data!AF52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="Z2">
         <f>Data!AG52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AA2">
         <f>Data!AH52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AB2">
         <f>Data!AI52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -1841,111 +2782,111 @@
       </c>
       <c r="B5">
         <f>Data!I55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="C5">
         <f>Data!J55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="D5">
         <f>Data!K55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="E5">
         <f>Data!L55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="F5">
         <f>Data!M55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="G5">
         <f>Data!N55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="H5">
         <f>Data!O55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="I5">
         <f>Data!P55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="J5">
         <f>Data!Q55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="K5">
         <f>Data!R55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="L5">
         <f>Data!S55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="M5">
         <f>Data!T55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="N5">
         <f>Data!U55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="O5">
         <f>Data!V55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="P5">
         <f>Data!W55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="Q5">
         <f>Data!X55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="R5">
         <f>Data!Y55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="S5">
         <f>Data!Z55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="T5">
         <f>Data!AA55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="U5">
         <f>Data!AB55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="V5">
         <f>Data!AC55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="W5">
         <f>Data!AD55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="X5">
         <f>Data!AE55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="Y5">
         <f>Data!AF55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="Z5">
         <f>Data!AG55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AA5">
         <f>Data!AH55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AB5">
         <f>Data!AI55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -2292,7 +3233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -3212,7 +4153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -4132,7 +5073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -5052,7 +5993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -5972,7 +6913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -6704,6 +7645,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DBCC89-6371-46BB-B5C9-7335B7F17874}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="C5">
+        <v>0.10755844933173792</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6748,25 +7737,25 @@
         <v>44</v>
       </c>
       <c r="B2">
-        <v>2799214</v>
+        <v>4769953</v>
       </c>
       <c r="C2">
-        <v>16648</v>
+        <v>14506</v>
       </c>
       <c r="D2">
-        <v>256819978</v>
+        <v>257649823</v>
       </c>
       <c r="E2">
-        <v>1348635</v>
+        <v>1553093</v>
       </c>
       <c r="F2">
-        <v>1130472</v>
+        <v>1417825</v>
       </c>
       <c r="G2">
-        <v>16384</v>
+        <v>13525</v>
       </c>
       <c r="H2">
-        <v>15809</v>
+        <v>17094</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -6775,25 +7764,25 @@
         <v>45</v>
       </c>
       <c r="B3">
-        <v>300</v>
+        <v>2445</v>
       </c>
       <c r="C3">
-        <v>123405.86320000001</v>
+        <v>67549</v>
       </c>
       <c r="D3">
-        <v>98369.804889999999</v>
+        <v>53161</v>
       </c>
       <c r="E3">
-        <v>703911.92879999999</v>
+        <v>422350</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>41837.429479999999</v>
+        <v>24746</v>
       </c>
       <c r="H3">
-        <v>105.315567</v>
+        <v>91</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="18"/>
@@ -6812,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6767</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6829,7 +7818,7 @@
         <v>47</v>
       </c>
       <c r="B5">
-        <v>2563.6060360000001</v>
+        <v>18776</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -6838,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>173.39396389999999</v>
+        <v>6889</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -6861,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>10231405.02</v>
+        <v>9385963</v>
       </c>
       <c r="E6">
-        <v>2473594.5350000001</v>
+        <v>2288110</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6887,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>9516910</v>
+        <v>9261249</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6916,7 +7905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -7151,107 +8140,107 @@
         <v>2024</v>
       </c>
       <c r="J9" s="15">
-        <f>E9</f>
+        <f t="shared" ref="J9:J17" si="0">E9</f>
         <v>2025</v>
       </c>
       <c r="K9" s="15">
-        <f t="shared" ref="K9:AI9" si="0">J9+1</f>
+        <f t="shared" ref="K9:AI9" si="1">J9+1</f>
         <v>2026</v>
       </c>
       <c r="L9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2027</v>
       </c>
       <c r="M9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2028</v>
       </c>
       <c r="N9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2029</v>
       </c>
       <c r="O9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2030</v>
       </c>
       <c r="P9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2031</v>
       </c>
       <c r="Q9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2032</v>
       </c>
       <c r="R9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2033</v>
       </c>
       <c r="S9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2034</v>
       </c>
       <c r="T9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2035</v>
       </c>
       <c r="U9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2036</v>
       </c>
       <c r="V9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2037</v>
       </c>
       <c r="W9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2038</v>
       </c>
       <c r="X9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2039</v>
       </c>
       <c r="Y9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2040</v>
       </c>
       <c r="Z9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2041</v>
       </c>
       <c r="AA9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2042</v>
       </c>
       <c r="AB9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2043</v>
       </c>
       <c r="AC9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2044</v>
       </c>
       <c r="AD9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2045</v>
       </c>
       <c r="AE9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2046</v>
       </c>
       <c r="AF9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2047</v>
       </c>
       <c r="AG9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2048</v>
       </c>
       <c r="AH9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2049</v>
       </c>
       <c r="AI9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2050</v>
       </c>
       <c r="AJ9" s="15"/>
@@ -7285,7 +8274,7 @@
         <v>0.148288948</v>
       </c>
       <c r="J10" s="16">
-        <f>E10</f>
+        <f t="shared" si="0"/>
         <v>0.148288948</v>
       </c>
       <c r="K10">
@@ -7412,7 +8401,7 @@
         <v>1.0097E-4</v>
       </c>
       <c r="J11" s="16">
-        <f>E11</f>
+        <f t="shared" si="0"/>
         <v>1.0097E-4</v>
       </c>
       <c r="K11">
@@ -7538,7 +8527,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <f>E12</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K12">
@@ -7665,7 +8654,7 @@
         <v>6.7382960000000006E-2</v>
       </c>
       <c r="J13" s="16">
-        <f>E13</f>
+        <f t="shared" si="0"/>
         <v>6.7382960000000006E-2</v>
       </c>
       <c r="K13">
@@ -7791,7 +8780,7 @@
         <v>1.4073499E-2</v>
       </c>
       <c r="J14">
-        <f>E14</f>
+        <f t="shared" si="0"/>
         <v>1.4073499E-2</v>
       </c>
       <c r="K14">
@@ -7918,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="16">
-        <f>E15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K15">
@@ -8047,7 +9036,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="16">
-        <f>E16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K16">
@@ -8175,11 +9164,11 @@
         <v>s-curve</v>
       </c>
       <c r="I17" s="16">
-        <f t="shared" ref="I17:I37" si="1">D17</f>
+        <f t="shared" ref="I17:I37" si="2">D17</f>
         <v>0.328639128</v>
       </c>
       <c r="J17">
-        <f>E17</f>
+        <f t="shared" si="0"/>
         <v>0.328639128</v>
       </c>
       <c r="K17" s="25">
@@ -8301,11 +9290,11 @@
         <v>73</v>
       </c>
       <c r="I18" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.250478074</v>
       </c>
       <c r="J18" s="16">
-        <f t="shared" ref="J18:J37" si="2">E18</f>
+        <f t="shared" ref="J18:J37" si="3">E18</f>
         <v>0.250478074</v>
       </c>
       <c r="K18">
@@ -8428,11 +9417,11 @@
         <v>n/a</v>
       </c>
       <c r="I19" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.76148265500000001</v>
       </c>
       <c r="J19" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.76148265500000001</v>
       </c>
       <c r="K19">
@@ -8554,11 +9543,11 @@
         <v>n/a</v>
       </c>
       <c r="I20" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J20" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K20">
@@ -8679,11 +9668,11 @@
         <v>74</v>
       </c>
       <c r="I21" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.003192E-3</v>
       </c>
       <c r="J21" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.003192E-3</v>
       </c>
       <c r="K21">
@@ -8806,11 +9795,11 @@
         <v>n/a</v>
       </c>
       <c r="I22" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.0223199999999996E-4</v>
       </c>
       <c r="J22" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.0223199999999996E-4</v>
       </c>
       <c r="K22">
@@ -8935,11 +9924,11 @@
         <v>n/a</v>
       </c>
       <c r="I23" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J23" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K23">
@@ -9067,11 +10056,11 @@
         <v>s-curve</v>
       </c>
       <c r="I24" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.12184009799999999</v>
       </c>
       <c r="J24" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12184009799999999</v>
       </c>
       <c r="K24">
@@ -9194,11 +10183,11 @@
         <v>n/a</v>
       </c>
       <c r="I25" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5737247999999999E-2</v>
       </c>
       <c r="J25" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.5737247999999999E-2</v>
       </c>
       <c r="K25">
@@ -9321,11 +10310,11 @@
         <v>n/a</v>
       </c>
       <c r="I26" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.37956814</v>
       </c>
       <c r="J26" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.37956814</v>
       </c>
       <c r="K26">
@@ -9447,11 +10436,11 @@
         <v>n/a</v>
       </c>
       <c r="I27" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J27" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K27">
@@ -9574,11 +10563,11 @@
         <v>n/a</v>
       </c>
       <c r="I28" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J28" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K28">
@@ -9701,11 +10690,11 @@
         <v>n/a</v>
       </c>
       <c r="I29" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.5449391000000001E-2</v>
       </c>
       <c r="J29" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5449391000000001E-2</v>
       </c>
       <c r="K29">
@@ -9830,11 +10819,11 @@
         <v>n/a</v>
       </c>
       <c r="I30" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.0286950000000001E-3</v>
       </c>
       <c r="J30" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.0286950000000001E-3</v>
       </c>
       <c r="K30">
@@ -9962,11 +10951,11 @@
         <v>s-curve</v>
       </c>
       <c r="I31" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8089680000000003E-3</v>
       </c>
       <c r="J31" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8089680000000003E-3</v>
       </c>
       <c r="K31">
@@ -10089,11 +11078,11 @@
         <v>n/a</v>
       </c>
       <c r="I32" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2159679000000002E-2</v>
       </c>
       <c r="J32" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.2159679000000002E-2</v>
       </c>
       <c r="K32">
@@ -10216,11 +11205,11 @@
         <v>n/a</v>
       </c>
       <c r="I33" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.5358100000000002E-4</v>
       </c>
       <c r="J33" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.5358100000000002E-4</v>
       </c>
       <c r="K33">
@@ -10342,11 +11331,11 @@
         <v>n/a</v>
       </c>
       <c r="I34" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J34" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K34">
@@ -10469,11 +11458,11 @@
         <v>n/a</v>
       </c>
       <c r="I35" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J35" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K35">
@@ -10596,11 +11585,11 @@
         <v>n/a</v>
       </c>
       <c r="I36" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J36" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K36">
@@ -10725,11 +11714,11 @@
         <v>n/a</v>
       </c>
       <c r="I37" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J37" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K37">
@@ -10854,7 +11843,7 @@
         <v>n/a</v>
       </c>
       <c r="I38" s="16">
-        <f t="shared" ref="I38:I69" si="3">E38</f>
+        <f t="shared" ref="I38:I69" si="4">E38</f>
         <v>0</v>
       </c>
       <c r="J38">
@@ -10977,7 +11966,7 @@
         <v>n/a</v>
       </c>
       <c r="I39" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J39">
@@ -11100,7 +12089,7 @@
         <v>n/a</v>
       </c>
       <c r="I40" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J40">
@@ -11223,7 +12212,7 @@
         <v>n/a</v>
       </c>
       <c r="I41" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J41">
@@ -11346,7 +12335,7 @@
         <v>n/a</v>
       </c>
       <c r="I42" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J42">
@@ -11469,7 +12458,7 @@
         <v>n/a</v>
       </c>
       <c r="I43" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J43">
@@ -11595,7 +12584,7 @@
         <v>n/a</v>
       </c>
       <c r="I44" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J44">
@@ -11724,7 +12713,7 @@
         <v>n/a</v>
       </c>
       <c r="I45" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J45">
@@ -11847,7 +12836,7 @@
         <v>n/a</v>
       </c>
       <c r="I46" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J46">
@@ -11970,7 +12959,7 @@
         <v>n/a</v>
       </c>
       <c r="I47" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J47">
@@ -12093,7 +13082,7 @@
         <v>n/a</v>
       </c>
       <c r="I48" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J48">
@@ -12216,7 +13205,7 @@
         <v>n/a</v>
       </c>
       <c r="I49" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J49">
@@ -12339,7 +13328,7 @@
         <v>n/a</v>
       </c>
       <c r="I50" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J50">
@@ -12465,7 +13454,7 @@
         <v>n/a</v>
       </c>
       <c r="I51" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J51">
@@ -12584,123 +13573,123 @@
         <v>37</v>
       </c>
       <c r="E52" s="16">
-        <f>'SYVbT-passenger'!B5/SUM('SYVbT-passenger'!B5:H5)</f>
-        <v>0.93664816810144857</v>
+        <f>'Calibration rail'!C4</f>
+        <v>1</v>
       </c>
       <c r="F52" s="16">
         <f>E52</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I52" s="16">
-        <f t="shared" si="3"/>
-        <v>0.93664816810144857</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="J52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,J$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,K$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="L52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,L$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="M52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,M$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="N52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,N$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="O52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,O$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="P52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,P$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="Q52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Q$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="R52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,R$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="S52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,S$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="T52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,T$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="U52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,U$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="V52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,V$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="W52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,W$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="X52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,X$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="Y52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Y$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="Z52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Z$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AA52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AA$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AB52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AB$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AC52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AC$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AD52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AD$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AE52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AE$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AF52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AF$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AG52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AG$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AH52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AH$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
       <c r="AI52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AI$9))</f>
-        <v>0.93664816810144857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
@@ -12718,7 +13707,7 @@
         <v>n/a</v>
       </c>
       <c r="I53" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J53">
@@ -12841,7 +13830,7 @@
         <v>n/a</v>
       </c>
       <c r="I54" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J54">
@@ -12954,124 +13943,124 @@
         <v>40</v>
       </c>
       <c r="E55" s="16">
-        <f>1-E52</f>
-        <v>6.3351831898551425E-2</v>
+        <f>'Calibration rail'!C5</f>
+        <v>0.10755844933173792</v>
       </c>
       <c r="F55" s="16">
         <f>E55</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="G55" s="5" t="str">
         <f>IF(E55=F55,"n/a",IF(OR(C55="battery electric vehicle",C55="natural gas vehicle",C55="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
       <c r="I55" s="16">
-        <f t="shared" si="3"/>
-        <v>6.3351831898551425E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.10755844933173792</v>
       </c>
       <c r="J55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,J$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="K55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,K$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="L55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,L$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="M55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,M$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="N55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,N$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="O55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,O$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="P55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,P$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="Q55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Q$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="R55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,R$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="S55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,S$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="T55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,T$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="U55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,U$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="V55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,V$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="W55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,W$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="X55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,X$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="Y55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Y$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="Z55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Z$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AA55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AA$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AB55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AB$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AC55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AC$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AD55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AD$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AE55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AE$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AF55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AF$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AG55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AG$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AH55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AH$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
       <c r="AI55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AI$9))</f>
-        <v>6.3351831898551425E-2</v>
+        <v>0.10755844933173792</v>
       </c>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
@@ -13089,7 +14078,7 @@
         <v>n/a</v>
       </c>
       <c r="I56" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J56">
@@ -13212,7 +14201,7 @@
         <v>n/a</v>
       </c>
       <c r="I57" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J57">
@@ -13338,7 +14327,7 @@
         <v>n/a</v>
       </c>
       <c r="I58" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J58">
@@ -13467,7 +14456,7 @@
         <v>n/a</v>
       </c>
       <c r="I59" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J59">
@@ -13590,7 +14579,7 @@
         <v>n/a</v>
       </c>
       <c r="I60" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J60">
@@ -13713,7 +14702,7 @@
         <v>n/a</v>
       </c>
       <c r="I61" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J61">
@@ -13836,7 +14825,7 @@
         <v>n/a</v>
       </c>
       <c r="I62" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J62">
@@ -13959,7 +14948,7 @@
         <v>n/a</v>
       </c>
       <c r="I63" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J63">
@@ -14082,7 +15071,7 @@
         <v>n/a</v>
       </c>
       <c r="I64" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J64">
@@ -14208,7 +15197,7 @@
         <v>n/a</v>
       </c>
       <c r="I65" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J65">
@@ -14337,7 +15326,7 @@
         <v>n/a</v>
       </c>
       <c r="I66" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J66">
@@ -14460,7 +15449,7 @@
         <v>n/a</v>
       </c>
       <c r="I67" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J67">
@@ -14583,7 +15572,7 @@
         <v>n/a</v>
       </c>
       <c r="I68" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J68">
@@ -14706,7 +15695,7 @@
         <v>n/a</v>
       </c>
       <c r="I69" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J69">
@@ -14829,7 +15818,7 @@
         <v>n/a</v>
       </c>
       <c r="I70" s="16">
-        <f t="shared" ref="I70:I93" si="4">E70</f>
+        <f t="shared" ref="I70:I93" si="5">E70</f>
         <v>0</v>
       </c>
       <c r="J70">
@@ -14952,7 +15941,7 @@
         <v>n/a</v>
       </c>
       <c r="I71" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J71">
@@ -15078,7 +16067,7 @@
         <v>n/a</v>
       </c>
       <c r="I72" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J72">
@@ -15207,7 +16196,7 @@
         <v>n/a</v>
       </c>
       <c r="I73" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J73">
@@ -15330,7 +16319,7 @@
         <v>n/a</v>
       </c>
       <c r="I74" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J74">
@@ -15453,7 +16442,7 @@
         <v>n/a</v>
       </c>
       <c r="I75" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J75">
@@ -15576,7 +16565,7 @@
         <v>n/a</v>
       </c>
       <c r="I76" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J76">
@@ -15699,7 +16688,7 @@
         <v>n/a</v>
       </c>
       <c r="I77" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J77">
@@ -15822,7 +16811,7 @@
         <v>n/a</v>
       </c>
       <c r="I78" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J78">
@@ -15948,7 +16937,7 @@
         <v>n/a</v>
       </c>
       <c r="I79" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J79">
@@ -16067,15 +17056,15 @@
         <v>37</v>
       </c>
       <c r="D80">
-        <f t="shared" ref="D80:F86" si="5">D10</f>
+        <f t="shared" ref="D80:F86" si="6">D10</f>
         <v>0.148288948</v>
       </c>
       <c r="E80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.148288948</v>
       </c>
       <c r="F80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G80" s="5" t="str">
@@ -16083,7 +17072,7 @@
         <v>s-curve</v>
       </c>
       <c r="I80" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.148288948</v>
       </c>
       <c r="J80">
@@ -16196,15 +17185,15 @@
         <v>38</v>
       </c>
       <c r="D81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0097E-4</v>
       </c>
       <c r="E81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0097E-4</v>
       </c>
       <c r="F81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0097E-4</v>
       </c>
       <c r="G81" s="5" t="str">
@@ -16212,7 +17201,7 @@
         <v>n/a</v>
       </c>
       <c r="I81" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0097E-4</v>
       </c>
       <c r="J81">
@@ -16325,15 +17314,15 @@
         <v>39</v>
       </c>
       <c r="D82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G82" s="5" t="str">
@@ -16341,7 +17330,7 @@
         <v>n/a</v>
       </c>
       <c r="I82" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J82">
@@ -16454,15 +17443,15 @@
         <v>40</v>
       </c>
       <c r="D83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.7382960000000006E-2</v>
       </c>
       <c r="E83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.7382960000000006E-2</v>
       </c>
       <c r="F83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.7382960000000006E-2</v>
       </c>
       <c r="G83" s="5" t="str">
@@ -16470,7 +17459,7 @@
         <v>n/a</v>
       </c>
       <c r="I83" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.7382960000000006E-2</v>
       </c>
       <c r="J83">
@@ -16583,15 +17572,15 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4073499E-2</v>
       </c>
       <c r="E84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4073499E-2</v>
       </c>
       <c r="F84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.10239066607264966</v>
       </c>
       <c r="G84" s="5" t="str">
@@ -16599,7 +17588,7 @@
         <v>s-curve</v>
       </c>
       <c r="I84" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.4073499E-2</v>
       </c>
       <c r="J84">
@@ -16712,15 +17701,15 @@
         <v>42</v>
       </c>
       <c r="D85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G85" s="5" t="str">
@@ -16728,7 +17717,7 @@
         <v>n/a</v>
       </c>
       <c r="I85" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J85">
@@ -16843,15 +17832,15 @@
         <v>43</v>
       </c>
       <c r="D86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G86" s="6" t="str">
@@ -16859,7 +17848,7 @@
         <v>n/a</v>
       </c>
       <c r="I86" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J86">
@@ -16988,7 +17977,7 @@
         <v>n/a</v>
       </c>
       <c r="I87" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J87">
@@ -17111,7 +18100,7 @@
         <v>n/a</v>
       </c>
       <c r="I88" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J88">
@@ -17234,7 +18223,7 @@
         <v>n/a</v>
       </c>
       <c r="I89" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J89">
@@ -17357,7 +18346,7 @@
         <v>n/a</v>
       </c>
       <c r="I90" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J90">
@@ -17480,7 +18469,7 @@
         <v>n/a</v>
       </c>
       <c r="I91" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J91">
@@ -17603,7 +18592,7 @@
         <v>n/a</v>
       </c>
       <c r="I92" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J92">
@@ -17729,7 +18718,7 @@
         <v>n/a</v>
       </c>
       <c r="I93" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J93">
@@ -17846,7 +18835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -18767,7 +19756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -19687,7 +20676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -20607,7 +21596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -21527,7 +22516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -22445,924 +23434,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1">
-        <f>Data!I9</f>
-        <v>2024</v>
-      </c>
-      <c r="C1">
-        <f>Data!J9</f>
-        <v>2025</v>
-      </c>
-      <c r="D1">
-        <f>Data!K9</f>
-        <v>2026</v>
-      </c>
-      <c r="E1">
-        <f>Data!L9</f>
-        <v>2027</v>
-      </c>
-      <c r="F1">
-        <f>Data!M9</f>
-        <v>2028</v>
-      </c>
-      <c r="G1">
-        <f>Data!N9</f>
-        <v>2029</v>
-      </c>
-      <c r="H1">
-        <f>Data!O9</f>
-        <v>2030</v>
-      </c>
-      <c r="I1">
-        <f>Data!P9</f>
-        <v>2031</v>
-      </c>
-      <c r="J1">
-        <f>Data!Q9</f>
-        <v>2032</v>
-      </c>
-      <c r="K1">
-        <f>Data!R9</f>
-        <v>2033</v>
-      </c>
-      <c r="L1">
-        <f>Data!S9</f>
-        <v>2034</v>
-      </c>
-      <c r="M1">
-        <f>Data!T9</f>
-        <v>2035</v>
-      </c>
-      <c r="N1">
-        <f>Data!U9</f>
-        <v>2036</v>
-      </c>
-      <c r="O1">
-        <f>Data!V9</f>
-        <v>2037</v>
-      </c>
-      <c r="P1">
-        <f>Data!W9</f>
-        <v>2038</v>
-      </c>
-      <c r="Q1">
-        <f>Data!X9</f>
-        <v>2039</v>
-      </c>
-      <c r="R1">
-        <f>Data!Y9</f>
-        <v>2040</v>
-      </c>
-      <c r="S1">
-        <f>Data!Z9</f>
-        <v>2041</v>
-      </c>
-      <c r="T1">
-        <f>Data!AA9</f>
-        <v>2042</v>
-      </c>
-      <c r="U1">
-        <f>Data!AB9</f>
-        <v>2043</v>
-      </c>
-      <c r="V1">
-        <f>Data!AC9</f>
-        <v>2044</v>
-      </c>
-      <c r="W1">
-        <f>Data!AD9</f>
-        <v>2045</v>
-      </c>
-      <c r="X1">
-        <f>Data!AE9</f>
-        <v>2046</v>
-      </c>
-      <c r="Y1">
-        <f>Data!AF9</f>
-        <v>2047</v>
-      </c>
-      <c r="Z1">
-        <f>Data!AG9</f>
-        <v>2048</v>
-      </c>
-      <c r="AA1">
-        <f>Data!AH9</f>
-        <v>2049</v>
-      </c>
-      <c r="AB1">
-        <f>Data!AI9</f>
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2">
-        <f>Data!I45</f>
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <f>Data!J45</f>
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>Data!K45</f>
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <f>Data!L45</f>
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <f>Data!M45</f>
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <f>Data!N45</f>
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <f>Data!O45</f>
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <f>Data!P45</f>
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <f>Data!Q45</f>
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <f>Data!R45</f>
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <f>Data!S45</f>
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <f>Data!T45</f>
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <f>Data!U45</f>
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <f>Data!V45</f>
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <f>Data!W45</f>
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <f>Data!X45</f>
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <f>Data!Y45</f>
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <f>Data!Z45</f>
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <f>Data!AA45</f>
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <f>Data!AB45</f>
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <f>Data!AC45</f>
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <f>Data!AD45</f>
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <f>Data!AE45</f>
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <f>Data!AF45</f>
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <f>Data!AG45</f>
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <f>Data!AH45</f>
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <f>Data!AI45</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3">
-        <f>Data!I46</f>
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <f>Data!J46</f>
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <f>Data!K46</f>
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <f>Data!L46</f>
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <f>Data!M46</f>
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <f>Data!N46</f>
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <f>Data!O46</f>
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <f>Data!P46</f>
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <f>Data!Q46</f>
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <f>Data!R46</f>
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <f>Data!S46</f>
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <f>Data!T46</f>
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <f>Data!U46</f>
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <f>Data!V46</f>
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <f>Data!W46</f>
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <f>Data!X46</f>
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <f>Data!Y46</f>
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <f>Data!Z46</f>
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <f>Data!AA46</f>
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <f>Data!AB46</f>
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <f>Data!AC46</f>
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <f>Data!AD46</f>
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <f>Data!AE46</f>
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <f>Data!AF46</f>
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <f>Data!AG46</f>
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <f>Data!AH46</f>
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <f>Data!AI46</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4">
-        <f>Data!I47</f>
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <f>Data!J47</f>
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f>Data!K47</f>
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <f>Data!L47</f>
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <f>Data!M47</f>
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <f>Data!N47</f>
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <f>Data!O47</f>
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <f>Data!P47</f>
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <f>Data!Q47</f>
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <f>Data!R47</f>
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <f>Data!S47</f>
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <f>Data!T47</f>
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <f>Data!U47</f>
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <f>Data!V47</f>
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <f>Data!W47</f>
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <f>Data!X47</f>
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <f>Data!Y47</f>
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <f>Data!Z47</f>
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <f>Data!AA47</f>
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <f>Data!AB47</f>
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <f>Data!AC47</f>
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <f>Data!AD47</f>
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <f>Data!AE47</f>
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <f>Data!AF47</f>
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <f>Data!AG47</f>
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <f>Data!AH47</f>
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <f>Data!AI47</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5">
-        <f>Data!I48</f>
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <f>Data!J48</f>
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <f>Data!K48</f>
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <f>Data!L48</f>
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <f>Data!M48</f>
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <f>Data!N48</f>
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <f>Data!O48</f>
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <f>Data!P48</f>
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <f>Data!Q48</f>
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <f>Data!R48</f>
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <f>Data!S48</f>
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <f>Data!T48</f>
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <f>Data!U48</f>
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <f>Data!V48</f>
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <f>Data!W48</f>
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <f>Data!X48</f>
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <f>Data!Y48</f>
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <f>Data!Z48</f>
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <f>Data!AA48</f>
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <f>Data!AB48</f>
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <f>Data!AC48</f>
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <f>Data!AD48</f>
-        <v>1</v>
-      </c>
-      <c r="X5">
-        <f>Data!AE48</f>
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <f>Data!AF48</f>
-        <v>1</v>
-      </c>
-      <c r="Z5">
-        <f>Data!AG48</f>
-        <v>1</v>
-      </c>
-      <c r="AA5">
-        <f>Data!AH48</f>
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <f>Data!AI48</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6">
-        <f>Data!I49</f>
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <f>Data!J49</f>
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <f>Data!K49</f>
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <f>Data!L49</f>
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <f>Data!M49</f>
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <f>Data!N49</f>
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <f>Data!O49</f>
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <f>Data!P49</f>
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <f>Data!Q49</f>
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <f>Data!R49</f>
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <f>Data!S49</f>
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <f>Data!T49</f>
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <f>Data!U49</f>
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <f>Data!V49</f>
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <f>Data!W49</f>
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <f>Data!X49</f>
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f>Data!Y49</f>
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <f>Data!Z49</f>
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <f>Data!AA49</f>
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <f>Data!AB49</f>
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <f>Data!AC49</f>
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <f>Data!AD49</f>
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <f>Data!AE49</f>
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <f>Data!AF49</f>
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <f>Data!AG49</f>
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <f>Data!AH49</f>
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <f>Data!AI49</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7">
-        <f>Data!I50</f>
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <f>Data!J50</f>
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <f>Data!K50</f>
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <f>Data!L50</f>
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <f>Data!M50</f>
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <f>Data!N50</f>
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <f>Data!O50</f>
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <f>Data!P50</f>
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <f>Data!Q50</f>
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <f>Data!R50</f>
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <f>Data!S50</f>
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <f>Data!T50</f>
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <f>Data!U50</f>
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <f>Data!V50</f>
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <f>Data!W50</f>
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <f>Data!X50</f>
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <f>Data!Y50</f>
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <f>Data!Z50</f>
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <f>Data!AA50</f>
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <f>Data!AB50</f>
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <f>Data!AC50</f>
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <f>Data!AD50</f>
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <f>Data!AE50</f>
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <f>Data!AF50</f>
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <f>Data!AG50</f>
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <f>Data!AH50</f>
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <f>Data!AI50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8">
-        <f>Data!I51</f>
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <f>Data!J51</f>
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <f>Data!K51</f>
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <f>Data!L51</f>
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <f>Data!M51</f>
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <f>Data!N51</f>
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <f>Data!O51</f>
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <f>Data!P51</f>
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <f>Data!Q51</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>Data!R51</f>
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <f>Data!S51</f>
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <f>Data!T51</f>
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <f>Data!U51</f>
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <f>Data!V51</f>
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <f>Data!W51</f>
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <f>Data!X51</f>
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <f>Data!Y51</f>
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <f>Data!Z51</f>
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <f>Data!AA51</f>
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <f>Data!AB51</f>
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <f>Data!AC51</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>Data!AD51</f>
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <f>Data!AE51</f>
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <f>Data!AF51</f>
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <f>Data!AG51</f>
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <f>Data!AH51</f>
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <f>Data!AI51</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-rail-vintaging\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-port-main-trans-v2\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80EA775-6AC6-443E-9E62-5458D18CC890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966BDD85-8A56-4A33-AA83-2E2093A92799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="43200" windowHeight="17145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="96">
   <si>
     <t>TTS Transportation Technology Shareweights</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>Passenger rail (2026-10-19): Data!E52 and E55 now read the solved shareweights on 'Calibration rail' (step 3a, observed 2015-2024 deliveries, 8.3% diesel) instead of the start-year fleet shares; pasted SYVbT-passenger refreshed.</t>
+  </si>
+  <si>
+    <t>Calibration record (2026-10-22)</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="63.42578125" customWidth="1"/>
@@ -1382,6 +1385,31 @@
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -6123,111 +6151,111 @@
       </c>
       <c r="B2">
         <f>Data!I80</f>
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="C2">
         <f>Data!J80</f>
-        <v>0.20192405133527508</v>
+        <v>0.19899617946551834</v>
       </c>
       <c r="D2">
         <f>Data!K80</f>
-        <v>0.21912805282851533</v>
+        <v>0.21626329664606081</v>
       </c>
       <c r="E2">
         <f>Data!L80</f>
-        <v>0.24120791635037137</v>
+        <v>0.23842416375084885</v>
       </c>
       <c r="F2">
         <f>Data!M80</f>
-        <v>0.26910506771371479</v>
+        <v>0.2664236603669965</v>
       </c>
       <c r="G2">
         <f>Data!N80</f>
-        <v>0.30366278279276282</v>
+        <v>0.30110815606389463</v>
       </c>
       <c r="H2">
         <f>Data!O80</f>
-        <v>0.34543894815797949</v>
+        <v>0.34303758410994234</v>
       </c>
       <c r="I2">
         <f>Data!P80</f>
-        <v>0.39447645120038111</v>
+        <v>0.39225498923554947</v>
       </c>
       <c r="J2">
         <f>Data!Q80</f>
-        <v>0.45008738819399363</v>
+        <v>0.44806994402765193</v>
       </c>
       <c r="K2">
         <f>Data!R80</f>
-        <v>0.51074095969281419</v>
+        <v>0.50894603305264141</v>
       </c>
       <c r="L2">
         <f>Data!S80</f>
-        <v>0.57414447400000002</v>
+        <v>0.57258215349999997</v>
       </c>
       <c r="M2">
         <f>Data!T80</f>
-        <v>0.63754798830718573</v>
+        <v>0.63621827394735875</v>
       </c>
       <c r="N2">
         <f>Data!U80</f>
-        <v>0.6982015598060064</v>
+        <v>0.69709436297234806</v>
       </c>
       <c r="O2">
         <f>Data!V80</f>
-        <v>0.75381249679961881</v>
+        <v>0.75290931776445058</v>
       </c>
       <c r="P2">
         <f>Data!W80</f>
-        <v>0.80284999984202055</v>
+        <v>0.80212672289005771</v>
       </c>
       <c r="Q2">
         <f>Data!X80</f>
-        <v>0.84462616520723721</v>
+        <v>0.84405615093610531</v>
       </c>
       <c r="R2">
         <f>Data!Y80</f>
-        <v>0.87918388028628536</v>
+        <v>0.87874064663300366</v>
       </c>
       <c r="S2">
         <f>Data!Z80</f>
-        <v>0.90708103164962861</v>
+        <v>0.90674014324915131</v>
       </c>
       <c r="T2">
         <f>Data!AA80</f>
-        <v>0.9291608951714847</v>
+        <v>0.92890101035393924</v>
       </c>
       <c r="U2">
         <f>Data!AB80</f>
-        <v>0.94636489666472501</v>
+        <v>0.94616812753448176</v>
       </c>
       <c r="V2">
         <f>Data!AC80</f>
-        <v>0.95960685966391612</v>
+        <v>0.95945867083612479</v>
       </c>
       <c r="W2">
         <f>Data!AD80</f>
-        <v>0.96970362496371199</v>
+        <v>0.96959247776729196</v>
       </c>
       <c r="X2">
         <f>Data!AE80</f>
-        <v>0.97734704662061023</v>
+        <v>0.97726394056400334</v>
       </c>
       <c r="Y2">
         <f>Data!AF80</f>
-        <v>0.9831017923312273</v>
+        <v>0.983039798498478</v>
       </c>
       <c r="Z2">
         <f>Data!AG80</f>
-        <v>0.98741679392424109</v>
+        <v>0.98737063037907702</v>
       </c>
       <c r="AA2">
         <f>Data!AH80</f>
-        <v>0.99064229953383387</v>
+        <v>0.99060796928242567</v>
       </c>
       <c r="AB2">
         <f>Data!AI80</f>
-        <v>0.99304784793611733</v>
+        <v>0.99302234283162671</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -6236,111 +6264,111 @@
       </c>
       <c r="B3">
         <f>Data!I81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="C3">
         <f>Data!J81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="D3">
         <f>Data!K81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="E3">
         <f>Data!L81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="F3">
         <f>Data!M81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="G3">
         <f>Data!N81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="H3">
         <f>Data!O81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="I3">
         <f>Data!P81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="J3">
         <f>Data!Q81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="K3">
         <f>Data!R81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="L3">
         <f>Data!S81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="M3">
         <f>Data!T81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="N3">
         <f>Data!U81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="O3">
         <f>Data!V81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="P3">
         <f>Data!W81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Q3">
         <f>Data!X81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="R3">
         <f>Data!Y81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="S3">
         <f>Data!Z81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="T3">
         <f>Data!AA81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="U3">
         <f>Data!AB81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="V3">
         <f>Data!AC81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="W3">
         <f>Data!AD81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="X3">
         <f>Data!AE81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Y3">
         <f>Data!AF81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Z3">
         <f>Data!AG81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AA3">
         <f>Data!AH81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AB3">
         <f>Data!AI81</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -6462,111 +6490,111 @@
       </c>
       <c r="B5">
         <f>Data!I83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="C5">
         <f>Data!J83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="D5">
         <f>Data!K83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="E5">
         <f>Data!L83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="F5">
         <f>Data!M83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="G5">
         <f>Data!N83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="H5">
         <f>Data!O83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="I5">
         <f>Data!P83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="K5">
         <f>Data!R83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="L5">
         <f>Data!S83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="M5">
         <f>Data!T83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="N5">
         <f>Data!U83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="O5">
         <f>Data!V83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="P5">
         <f>Data!W83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI83</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -6575,111 +6603,111 @@
       </c>
       <c r="B6">
         <f>Data!I84</f>
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="C6">
         <f>Data!J84</f>
-        <v>1.5378299625391417E-2</v>
+        <v>1.2452844371960014E-2</v>
       </c>
       <c r="D6">
         <f>Data!K84</f>
-        <v>1.5825738596288972E-2</v>
+        <v>1.2856799259209385E-2</v>
       </c>
       <c r="E6">
         <f>Data!L84</f>
-        <v>1.6422470125358253E-2</v>
+        <v>1.3395537798366533E-2</v>
       </c>
       <c r="F6">
         <f>Data!M84</f>
-        <v>1.7215045665964251E-2</v>
+        <v>1.4111087368176831E-2</v>
       </c>
       <c r="G6">
         <f>Data!N84</f>
-        <v>1.8262017764989459E-2</v>
+        <v>1.5056310121944961E-2</v>
       </c>
       <c r="H6">
         <f>Data!O84</f>
-        <v>1.9635127408011214E-2</v>
+        <v>1.6295974941294988E-2</v>
       </c>
       <c r="I6">
         <f>Data!P84</f>
-        <v>2.1419075932136523E-2</v>
+        <v>1.7906551515517261E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q84</f>
-        <v>2.370862118462793E-2</v>
+        <v>1.9973588708248197E-2</v>
       </c>
       <c r="K6">
         <f>Data!R84</f>
-        <v>2.6601383198249652E-2</v>
+        <v>2.2585219408872568E-2</v>
       </c>
       <c r="L6">
         <f>Data!S84</f>
-        <v>3.0184804464321601E-2</v>
+        <v>2.5820388063492336E-2</v>
       </c>
       <c r="M6">
         <f>Data!T84</f>
-        <v>3.4516734368895005E-2</v>
+        <v>2.9731322000837706E-2</v>
       </c>
       <c r="N6">
         <f>Data!U84</f>
-        <v>3.9601620069100008E-2</v>
+        <v>3.4322036183783898E-2</v>
       </c>
       <c r="O6">
         <f>Data!V84</f>
-        <v>4.5368130204196222E-2</v>
+        <v>3.9528131546403743E-2</v>
       </c>
       <c r="P6">
         <f>Data!W84</f>
-        <v>5.1657530341761002E-2</v>
+        <v>4.5206300165332253E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X84</f>
-        <v>5.8232082536324822E-2</v>
+        <v>5.1141908512416123E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y84</f>
-        <v>6.4806634730888643E-2</v>
+        <v>5.707751685949998E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z84</f>
-        <v>7.1096034868453423E-2</v>
+        <v>6.2755685478428497E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA84</f>
-        <v>7.6862545003549651E-2</v>
+        <v>6.7961780841048341E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB84</f>
-        <v>8.194743070375464E-2</v>
+        <v>7.2552495023994523E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC84</f>
-        <v>8.6279360608328054E-2</v>
+        <v>7.6463428961339897E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD84</f>
-        <v>8.9862781874400013E-2</v>
+        <v>7.9698597615959682E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE84</f>
-        <v>9.2755543888021721E-2</v>
+        <v>8.231022831658405E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF84</f>
-        <v>9.5045089140513128E-2</v>
+        <v>8.4377265509314986E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG84</f>
-        <v>9.6829037664638448E-2</v>
+        <v>8.5987842083537255E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH84</f>
-        <v>9.8202147307660206E-2</v>
+        <v>8.7227506902887289E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI84</f>
-        <v>9.9249119406685404E-2</v>
+        <v>8.8172729656655416E-2</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -8257,10 +8285,10 @@
         <v>37</v>
       </c>
       <c r="D10">
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="E10" s="16">
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -8271,111 +8299,111 @@
       </c>
       <c r="I10">
         <f>D10</f>
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="J10" s="16">
         <f t="shared" si="0"/>
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="K10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,K$9))</f>
-        <v>0.18868208833608399</v>
+        <v>0.18570563616387542</v>
       </c>
       <c r="L10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,L$9))</f>
-        <v>0.20192405133527508</v>
+        <v>0.19899617946551834</v>
       </c>
       <c r="M10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,M$9))</f>
-        <v>0.21912805282851533</v>
+        <v>0.21626329664606081</v>
       </c>
       <c r="N10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,N$9))</f>
-        <v>0.24120791635037137</v>
+        <v>0.23842416375084885</v>
       </c>
       <c r="O10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,O$9))</f>
-        <v>0.26910506771371479</v>
+        <v>0.2664236603669965</v>
       </c>
       <c r="P10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,P$9))</f>
-        <v>0.30366278279276282</v>
+        <v>0.30110815606389463</v>
       </c>
       <c r="Q10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Q$9))</f>
-        <v>0.34543894815797949</v>
+        <v>0.34303758410994234</v>
       </c>
       <c r="R10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,R$9))</f>
-        <v>0.39447645120038111</v>
+        <v>0.39225498923554947</v>
       </c>
       <c r="S10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,S$9))</f>
-        <v>0.45008738819399363</v>
+        <v>0.44806994402765193</v>
       </c>
       <c r="T10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,T$9))</f>
-        <v>0.51074095969281419</v>
+        <v>0.50894603305264141</v>
       </c>
       <c r="U10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,U$9))</f>
-        <v>0.57414447400000002</v>
+        <v>0.57258215349999997</v>
       </c>
       <c r="V10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,V$9))</f>
-        <v>0.63754798830718573</v>
+        <v>0.63621827394735875</v>
       </c>
       <c r="W10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,W$9))</f>
-        <v>0.6982015598060064</v>
+        <v>0.69709436297234806</v>
       </c>
       <c r="X10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,X$9))</f>
-        <v>0.75381249679961881</v>
+        <v>0.75290931776445058</v>
       </c>
       <c r="Y10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Y$9))</f>
-        <v>0.80284999984202055</v>
+        <v>0.80212672289005771</v>
       </c>
       <c r="Z10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Z$9))</f>
-        <v>0.84462616520723721</v>
+        <v>0.84405615093610531</v>
       </c>
       <c r="AA10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AA$9))</f>
-        <v>0.87918388028628536</v>
+        <v>0.87874064663300366</v>
       </c>
       <c r="AB10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AB$9))</f>
-        <v>0.90708103164962861</v>
+        <v>0.90674014324915131</v>
       </c>
       <c r="AC10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AC$9))</f>
-        <v>0.9291608951714847</v>
+        <v>0.92890101035393924</v>
       </c>
       <c r="AD10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AD$9))</f>
-        <v>0.94636489666472501</v>
+        <v>0.94616812753448176</v>
       </c>
       <c r="AE10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AE$9))</f>
-        <v>0.95960685966391612</v>
+        <v>0.95945867083612479</v>
       </c>
       <c r="AF10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AF$9))</f>
-        <v>0.96970362496371199</v>
+        <v>0.96959247776729196</v>
       </c>
       <c r="AG10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AG$9))</f>
-        <v>0.97734704662061023</v>
+        <v>0.97726394056400334</v>
       </c>
       <c r="AH10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AH$9))</f>
-        <v>0.9831017923312273</v>
+        <v>0.983039798498478</v>
       </c>
       <c r="AI10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AI$9))</f>
-        <v>0.98741679392424109</v>
+        <v>0.98737063037907702</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
@@ -8383,14 +8411,14 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="E11" s="16">
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="F11" s="16">
         <f>E11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="G11" s="5" t="str">
         <f>IF(E11=F11,"n/a",IF(OR(C11="battery electric vehicle",C11="natural gas vehicle",C11="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -8398,111 +8426,111 @@
       </c>
       <c r="I11" s="16">
         <f>E11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="J11" s="16">
         <f t="shared" si="0"/>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="K11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,K$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="L11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,L$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="M11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,M$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="N11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,N$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="O11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,O$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="P11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,P$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Q11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Q$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="R11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,R$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="S11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,S$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="T11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,T$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="U11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,U$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="V11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,V$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="W11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,W$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="X11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,X$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Y11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Y$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Z11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Z$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AA11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AA$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AB11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AB$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AC11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AC$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AD11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AD$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AE11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AE$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AF11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AF$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AG11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AG$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AH11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AH$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AI11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AI$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
@@ -8636,14 +8664,14 @@
         <v>40</v>
       </c>
       <c r="D13">
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="E13" s="16">
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="F13" s="16">
         <f>E13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="G13" s="5" t="str">
         <f>IF(E13=F13,"n/a",IF(OR(C13="battery electric vehicle",C13="natural gas vehicle",C13="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -8651,111 +8679,111 @@
       </c>
       <c r="I13" s="16">
         <f>E13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="J13" s="16">
         <f t="shared" si="0"/>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="K13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,K$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="L13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,L$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="M13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,M$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="N13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,N$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="O13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,O$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="P13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,P$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Q13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Q$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="R13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,R$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="S13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,S$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="T13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,T$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="U13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,U$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="V13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,V$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="W13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,W$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="X13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,X$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Y13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Y$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Z13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Z$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AA13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AA$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AB13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AB$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AC13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AC$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AD13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AD$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AE13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AE$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AF13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AF$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AG13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AG$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AH13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AH$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AI13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AI$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.25">
@@ -8763,13 +8791,13 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="E14" s="16">
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="F14" s="23">
-        <v>0.10239066607264966</v>
+        <v>9.1008967024832244E-2</v>
       </c>
       <c r="G14" s="5" t="str">
         <f>IF(E14=F14,"n/a",IF(OR(C14="battery electric vehicle",C14="natural gas vehicle",C14="plugin hybrid vehicle",C14="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -8777,111 +8805,111 @@
       </c>
       <c r="I14">
         <f>D14</f>
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="K14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:K$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,K$9))</f>
-        <v>1.7532504683762919E-2</v>
+        <v>1.4397694324839349E-2</v>
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:L$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>1.9136207820162347E-2</v>
+        <v>1.5845542549472465E-2</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:M$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>2.1419075932136523E-2</v>
+        <v>1.7906551515517257E-2</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:N$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>2.4601163379775384E-2</v>
+        <v>2.0779389734213474E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:O$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>2.8909159345260678E-2</v>
+        <v>2.4668715737751964E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:P$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>3.4516734368895005E-2</v>
+        <v>2.9731322000837702E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Q$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>4.1454074547037548E-2</v>
+        <v>3.5994461002455284E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:R$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>4.9516267970164535E-2</v>
+        <v>4.3273135072103008E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:S$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
-        <v>5.8232082536324822E-2</v>
+        <v>5.1141908512416123E-2</v>
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:T$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>6.694789710248511E-2</v>
+        <v>5.9010681952729238E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:U$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>7.5010090525612097E-2</v>
+        <v>6.6289356022376955E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:V$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>8.1947430703754653E-2</v>
+        <v>7.2552495023994537E-2</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:W$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>8.7555005727388974E-2</v>
+        <v>7.7615101287080282E-2</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:X$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>9.1863001692874258E-2</v>
+        <v>8.1504427290618769E-2</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Y$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>9.5045089140513128E-2</v>
+        <v>8.4377265509314986E-2</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Z$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>9.7327957252487315E-2</v>
+        <v>8.6438274475359775E-2</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AA$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>9.8931660388886733E-2</v>
+        <v>8.7886122699992894E-2</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AB$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>0.1000416949472914</v>
+        <v>8.8888279226465708E-2</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AC$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>0.10080217496242386</v>
+        <v>8.9574852454881629E-2</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AD$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>0.10131951705381374</v>
+        <v>9.0041916970468053E-2</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AE$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>0.10166977091237364</v>
+        <v>9.0358131621282672E-2</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AF$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>0.1019061316961364</v>
+        <v>9.0571521826350254E-2</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AG$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>0.10206528444191545</v>
+        <v>9.0715207409543072E-2</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AH$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>0.10217229100021745</v>
+        <v>9.0811814600702825E-2</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AI$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>0.1022441654605116</v>
+        <v>9.0876703985384694E-2</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
@@ -9151,10 +9179,10 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.328639128</v>
+        <v>0.327825113</v>
       </c>
       <c r="E17">
-        <v>0.328639128</v>
+        <v>0.327825113</v>
       </c>
       <c r="F17">
         <v>0.3</v>
@@ -9165,111 +9193,111 @@
       </c>
       <c r="I17" s="16">
         <f t="shared" ref="I17:I37" si="2">D17</f>
-        <v>0.328639128</v>
+        <v>0.327825113</v>
       </c>
       <c r="J17">
         <f t="shared" si="0"/>
-        <v>0.328639128</v>
+        <v>0.327825113</v>
       </c>
       <c r="K17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,K$9))</f>
-        <v>0.32762040015730876</v>
+        <v>0.32683534063894454</v>
       </c>
       <c r="L17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,L$9))</f>
-        <v>0.32728089234755592</v>
+        <v>0.32650548271971053</v>
       </c>
       <c r="M17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,M$9))</f>
-        <v>0.32683562599529409</v>
+        <v>0.32607287225172482</v>
       </c>
       <c r="N17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,N$9))</f>
-        <v>0.3262571344990054</v>
+        <v>0.32551082332154191</v>
       </c>
       <c r="O17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,O$9))</f>
-        <v>0.32551469017338575</v>
+        <v>0.32478948162229127</v>
       </c>
       <c r="P17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,P$9))</f>
-        <v>0.3245766371953786</v>
+        <v>0.32387809108997362</v>
       </c>
       <c r="Q17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Q$9))</f>
-        <v>0.32341462007324273</v>
+        <v>0.32274910218600394</v>
       </c>
       <c r="R17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,R$9))</f>
-        <v>0.32200987964580063</v>
+        <v>0.32138428894416071</v>
       </c>
       <c r="S17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,S$9))</f>
-        <v>0.32036097380721384</v>
+        <v>0.31978225024783452</v>
       </c>
       <c r="T17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,T$9))</f>
-        <v>0.31849103359800773</v>
+        <v>0.31796545967989537</v>
       </c>
       <c r="U17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,U$9))</f>
-        <v>0.31645153276761123</v>
+        <v>0.3159839279422888</v>
       </c>
       <c r="V17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,V$9))</f>
-        <v>0.314319564</v>
+        <v>0.3139125565</v>
       </c>
       <c r="W17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,W$9))</f>
-        <v>0.31218759523238876</v>
+        <v>0.31184118505771119</v>
       </c>
       <c r="X17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,X$9))</f>
-        <v>0.31014809440199226</v>
+        <v>0.30985965332010462</v>
       </c>
       <c r="Y17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Y$9))</f>
-        <v>0.30827815419278615</v>
+        <v>0.30804286275216547</v>
       </c>
       <c r="Z17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Z$9))</f>
-        <v>0.30662924835419936</v>
+        <v>0.30644082405583928</v>
       </c>
       <c r="AA17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AA$9))</f>
-        <v>0.30522450792675726</v>
+        <v>0.30507601081399605</v>
       </c>
       <c r="AB17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AB$9))</f>
-        <v>0.30406249080462139</v>
+        <v>0.30394702191002637</v>
       </c>
       <c r="AC17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AC$9))</f>
-        <v>0.30312443782661425</v>
+        <v>0.30303563137770873</v>
       </c>
       <c r="AD17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AD$9))</f>
-        <v>0.30238199350099459</v>
+        <v>0.30231428967845808</v>
       </c>
       <c r="AE17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AE$9))</f>
-        <v>0.3018035020047059</v>
+        <v>0.30175224074827517</v>
       </c>
       <c r="AF17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AF$9))</f>
-        <v>0.30135823565244407</v>
+        <v>0.30131963028028946</v>
       </c>
       <c r="AG17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AG$9))</f>
-        <v>0.30101872784269124</v>
+        <v>0.30098977236105545</v>
       </c>
       <c r="AH17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AH$9))</f>
-        <v>0.30076171470346302</v>
+        <v>0.30074006435173656</v>
       </c>
       <c r="AI17" s="25">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AI$9))</f>
-        <v>0.30056820905547738</v>
+        <v>0.30055205874900526</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
@@ -9277,125 +9305,125 @@
         <v>38</v>
       </c>
       <c r="D18">
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="E18">
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="F18" s="16">
         <f>E18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="J18" s="16">
         <f t="shared" ref="J18:J37" si="3">E18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="K18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,K$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="L18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,L$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="M18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,M$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="N18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,N$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="O18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,O$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="P18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,P$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="Q18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Q$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="R18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,R$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="S18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,S$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="T18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,T$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="U18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,U$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="V18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,V$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="W18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,W$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="X18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,X$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="Y18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Y$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="Z18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Z$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AA18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AA$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AB18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AB$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AC18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AC$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AD18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AD$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AE18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AE$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AF18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AF$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AG18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AG$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AH18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AH$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AI18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AI$9))</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
@@ -9403,14 +9431,14 @@
         <v>39</v>
       </c>
       <c r="D19">
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="E19">
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="F19" s="16">
         <f>E19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="G19" s="5" t="str">
         <f>IF(E19=F19,"n/a",IF(OR(C19="battery electric vehicle",C19="natural gas vehicle",C19="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -9418,111 +9446,111 @@
       </c>
       <c r="I19" s="16">
         <f t="shared" si="2"/>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="J19" s="16">
         <f t="shared" si="3"/>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="K19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,K$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="L19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,L$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="M19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,M$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="N19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,N$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="O19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,O$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="P19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,P$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="Q19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Q$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="R19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,R$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="S19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,S$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="T19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,T$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="U19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,U$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="V19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,V$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="W19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,W$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="X19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,X$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="Y19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Y$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="Z19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Z$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AA19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AA$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AB19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AB$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AC19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AC$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AD19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AD$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AE19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AE$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AF19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AF$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AG19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AG$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AH19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AH$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AI19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AI$9))</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
@@ -9656,124 +9684,124 @@
         <v>41</v>
       </c>
       <c r="D21">
-        <v>1.003192E-3</v>
+        <v>1.004397E-3</v>
       </c>
       <c r="E21">
-        <v>1.003192E-3</v>
+        <v>1.004397E-3</v>
       </c>
       <c r="F21" s="16">
-        <v>1.235708268868196E-3</v>
+        <v>1.0088530556553437E-3</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I21" s="16">
         <f t="shared" si="2"/>
-        <v>1.003192E-3</v>
+        <v>1.004397E-3</v>
       </c>
       <c r="J21" s="16">
         <f t="shared" si="3"/>
-        <v>1.003192E-3</v>
+        <v>1.004397E-3</v>
       </c>
       <c r="K21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,K$9))</f>
-        <v>1.0114628802088777E-3</v>
+        <v>1.0045555071991257E-3</v>
       </c>
       <c r="L21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,L$9))</f>
-        <v>1.0142192870790641E-3</v>
+        <v>1.0046083323303825E-3</v>
       </c>
       <c r="M21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,M$9))</f>
-        <v>1.0178343297884813E-3</v>
+        <v>1.0046776127793937E-3</v>
       </c>
       <c r="N21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,N$9))</f>
-        <v>1.0225310050604737E-3</v>
+        <v>1.0047676221645819E-3</v>
       </c>
       <c r="O21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,O$9))</f>
-        <v>1.0285587858097846E-3</v>
+        <v>1.0048831415070687E-3</v>
       </c>
       <c r="P21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,P$9))</f>
-        <v>1.0361746803456418E-3</v>
+        <v>1.0050290962399662E-3</v>
       </c>
       <c r="Q21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Q$9))</f>
-        <v>1.0456089021417803E-3</v>
+        <v>1.0052098982870363E-3</v>
       </c>
       <c r="R21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,R$9))</f>
-        <v>1.0570137536762662E-3</v>
+        <v>1.0054284664475612E-3</v>
       </c>
       <c r="S21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,S$9))</f>
-        <v>1.0704009431641303E-3</v>
+        <v>1.0056850251035077E-3</v>
       </c>
       <c r="T21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,T$9))</f>
-        <v>1.0855826735733526E-3</v>
+        <v>1.005975975220578E-3</v>
       </c>
       <c r="U21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,U$9))</f>
-        <v>1.1021410381798931E-3</v>
+        <v>1.0062933078296352E-3</v>
       </c>
       <c r="V21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,V$9))</f>
-        <v>1.1194501344340981E-3</v>
+        <v>1.0066250278276717E-3</v>
       </c>
       <c r="W21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,W$9))</f>
-        <v>1.1367592306883029E-3</v>
+        <v>1.0069567478257085E-3</v>
       </c>
       <c r="X21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,X$9))</f>
-        <v>1.1533175952948434E-3</v>
+        <v>1.0072740804347657E-3</v>
       </c>
       <c r="Y21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Y$9))</f>
-        <v>1.1684993257040656E-3</v>
+        <v>1.007565030551836E-3</v>
       </c>
       <c r="Z21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Z$9))</f>
-        <v>1.1818865151919297E-3</v>
+        <v>1.0078215892077825E-3</v>
       </c>
       <c r="AA21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AA$9))</f>
-        <v>1.1932913667264157E-3</v>
+        <v>1.0080401573683074E-3</v>
       </c>
       <c r="AB21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AB$9))</f>
-        <v>1.2027255885225542E-3</v>
+        <v>1.0082209594153774E-3</v>
       </c>
       <c r="AC21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AC$9))</f>
-        <v>1.2103414830584114E-3</v>
+        <v>1.008366914148275E-3</v>
       </c>
       <c r="AD21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AD$9))</f>
-        <v>1.2163692638077223E-3</v>
+        <v>1.0084824334907617E-3</v>
       </c>
       <c r="AE21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AE$9))</f>
-        <v>1.2210659390797147E-3</v>
+        <v>1.00857244287595E-3</v>
       </c>
       <c r="AF21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AF$9))</f>
-        <v>1.2246809817891319E-3</v>
+        <v>1.0086417233249611E-3</v>
       </c>
       <c r="AG21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AG$9))</f>
-        <v>1.2274373886593183E-3</v>
+        <v>1.008694548456218E-3</v>
       </c>
       <c r="AH21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AH$9))</f>
-        <v>1.2295240351585918E-3</v>
+        <v>1.0087345379717005E-3</v>
       </c>
       <c r="AI21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AI$9))</f>
-        <v>1.2310950750057041E-3</v>
+        <v>1.0087646461487737E-3</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
@@ -9781,14 +9809,14 @@
         <v>42</v>
       </c>
       <c r="D22">
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="E22">
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="F22" s="16">
         <f>E22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="G22" s="5" t="str">
         <f>IF(E22=F22,"n/a",IF(OR(C22="battery electric vehicle",C22="natural gas vehicle",C22="plugin hybrid vehicle",C22="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -9796,111 +9824,111 @@
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="J22" s="16">
         <f t="shared" si="3"/>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="K22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,K$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="L22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,L$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="M22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,M$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="N22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,N$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="O22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,O$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="P22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,P$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="Q22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Q$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="R22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,R$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="S22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,S$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="T22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,T$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="U22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,U$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="V22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,V$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="W22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,W$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="X22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,X$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="Y22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Y$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="Z22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Z$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AA22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AA$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AB22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AB$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AC22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AC$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AD22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AD$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AE22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AE$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AF22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AF$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AG22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AG$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AH22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AH$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AI22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AI$9))</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
     </row>
     <row r="23" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -10043,10 +10071,10 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0.12184009799999999</v>
+        <v>0.121750944</v>
       </c>
       <c r="E24">
-        <v>0.12184009799999999</v>
+        <v>0.121750944</v>
       </c>
       <c r="F24" s="26">
         <v>0.75</v>
@@ -10057,111 +10085,111 @@
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>0.12184009799999999</v>
+        <v>0.121750944</v>
       </c>
       <c r="J24" s="16">
         <f t="shared" si="3"/>
-        <v>0.12184009799999999</v>
+        <v>0.121750944</v>
       </c>
       <c r="K24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
-        <v>0.1441844927675226</v>
+        <v>0.14409851008133101</v>
       </c>
       <c r="L24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
-        <v>0.15163112984748478</v>
+        <v>0.15154620405378205</v>
       </c>
       <c r="M24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
-        <v>0.16139743516937402</v>
+        <v>0.16131389549595992</v>
       </c>
       <c r="N24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
-        <v>0.17408585087869802</v>
+        <v>0.17400411205728125</v>
       </c>
       <c r="O24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
-        <v>0.19037034651074775</v>
+        <v>0.19029091892874461</v>
       </c>
       <c r="P24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
-        <v>0.21094524902648606</v>
+        <v>0.21086874161632621</v>
       </c>
       <c r="Q24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
-        <v>0.23643249715649947</v>
+        <v>0.23635960712164891</v>
       </c>
       <c r="R24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
-        <v>0.26724354731268585</v>
+        <v>0.2671750302541378</v>
       </c>
       <c r="S24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
-        <v>0.30341003010412881</v>
+        <v>0.30334664611217177</v>
       </c>
       <c r="T24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
-        <v>0.34442459795552233</v>
+        <v>0.34436703511319711</v>
       </c>
       <c r="U24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
-        <v>0.38915824493495493</v>
+        <v>0.38910703108681111</v>
       </c>
       <c r="V24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
-        <v>0.43592004900000003</v>
+        <v>0.43587547199999999</v>
       </c>
       <c r="W24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
-        <v>0.48268185306504513</v>
+        <v>0.48264391291318898</v>
       </c>
       <c r="X24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
-        <v>0.52741550004447768</v>
+        <v>0.52738390888680287</v>
       </c>
       <c r="Y24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
-        <v>0.56843006789587125</v>
+        <v>0.5684042978878282</v>
       </c>
       <c r="Z24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
-        <v>0.6045965506873141</v>
+        <v>0.60457591374586217</v>
       </c>
       <c r="AA24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
-        <v>0.63540760084350045</v>
+        <v>0.63539133687835103</v>
       </c>
       <c r="AB24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
-        <v>0.66089484897351403</v>
+        <v>0.6608822023836739</v>
       </c>
       <c r="AC24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
-        <v>0.68146975148925226</v>
+        <v>0.68146002507125536</v>
       </c>
       <c r="AD24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
-        <v>0.69775424712130196</v>
+        <v>0.6977468319427188</v>
       </c>
       <c r="AE24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
-        <v>0.71044266283062596</v>
+        <v>0.7104370485040401</v>
       </c>
       <c r="AF24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
-        <v>0.72020896815251523</v>
+        <v>0.72020473994621803</v>
       </c>
       <c r="AG24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
-        <v>0.72765560523247741</v>
+        <v>0.72765243391866896</v>
       </c>
       <c r="AH24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
-        <v>0.73329283512126131</v>
+        <v>0.73329046389289587</v>
       </c>
       <c r="AI24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
-        <v>0.73753711549443191</v>
+        <v>0.73753534665181442</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
@@ -10169,14 +10197,14 @@
         <v>38</v>
       </c>
       <c r="D25">
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="E25">
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="F25" s="16">
         <f>E25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="G25" s="5" t="str">
         <f>IF(E25=F25,"n/a",IF(OR(C25="battery electric vehicle",C25="natural gas vehicle",C25="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -10184,111 +10212,111 @@
       </c>
       <c r="I25" s="16">
         <f t="shared" si="2"/>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="J25" s="16">
         <f t="shared" si="3"/>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="K25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,K$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="L25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,L$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="M25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,M$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="N25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,N$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="O25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,O$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="P25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,P$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="Q25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Q$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="R25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,R$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="S25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,S$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="T25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,T$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="U25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,U$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="V25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,V$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="W25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,W$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="X25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,X$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="Y25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Y$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="Z25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Z$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AA25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AA$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AB25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AB$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AC25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AC$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AD25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AD$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AE25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AE$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AF25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AF$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AG25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AG$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AH25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AH$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AI25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AI$9))</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
@@ -10296,14 +10324,14 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="E26">
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="F26" s="16">
         <f>E26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="G26" s="5" t="str">
         <f>IF(E26=F26,"n/a",IF(OR(C26="battery electric vehicle",C26="natural gas vehicle",C26="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -10311,111 +10339,111 @@
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="J26" s="16">
         <f t="shared" si="3"/>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="K26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,K$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="L26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,L$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="M26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,M$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="N26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,N$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="O26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,O$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="P26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,P$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="Q26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Q$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="R26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,R$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="S26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,S$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="T26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,T$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="U26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,U$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="V26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,V$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="W26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,W$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="X26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,X$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="Y26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Y$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="Z26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Z$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AA26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AA$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AB26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AB$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AC26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AC$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AD26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AD$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AE26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AE$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AF26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AF$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AG26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AG$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AH26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AH$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AI26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AI$9))</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
@@ -10676,14 +10704,14 @@
         <v>42</v>
       </c>
       <c r="D29">
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="E29">
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="F29" s="16">
         <f>E29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="G29" s="5" t="str">
         <f>IF(E29=F29,"n/a",IF(OR(C29="battery electric vehicle",C29="natural gas vehicle",C29="plugin hybrid vehicle",C29="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -10691,111 +10719,111 @@
       </c>
       <c r="I29" s="16">
         <f t="shared" si="2"/>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="J29" s="16">
         <f t="shared" si="3"/>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="K29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,K$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="L29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,L$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="M29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,M$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="N29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,N$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="O29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,O$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="P29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,P$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="Q29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Q$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="R29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,R$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="S29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,S$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="T29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,T$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="U29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,U$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="V29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,V$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="W29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,W$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="X29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,X$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="Y29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Y$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="Z29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Z$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AA29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AA$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AB29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AB$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AC29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AC$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AD29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AD$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AE29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AE$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AF29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AF$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AG29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AG$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AH29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AH$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AI29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AI$9))</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
     </row>
     <row r="30" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -10805,14 +10833,14 @@
         <v>43</v>
       </c>
       <c r="D30" s="20">
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="E30" s="6">
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="F30" s="20">
         <f>E30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="G30" s="6" t="str">
         <f>IF(E30=F30,"n/a",IF(OR(C30="battery electric vehicle",C30="natural gas vehicle",C30="plugin hybrid vehicle",C30="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -10820,111 +10848,111 @@
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="J30" s="16">
         <f t="shared" si="3"/>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="K30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,K$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="L30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,L$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="M30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,M$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="N30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,N$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="O30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,O$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="P30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,P$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="Q30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Q$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="R30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,R$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="S30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,S$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="T30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,T$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="U30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,U$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="V30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,V$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="W30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,W$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="X30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,X$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="Y30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Y$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="Z30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Z$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AA30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AA$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AB30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AB$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AC30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AC$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AD30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AD$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AE30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AE$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AF30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AF$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AG30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AG$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AH30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AH$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AI30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AI$9))</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
@@ -10938,10 +10966,10 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>4.8089680000000003E-3</v>
+        <v>4.7883190000000001E-3</v>
       </c>
       <c r="E31">
-        <v>4.8089680000000003E-3</v>
+        <v>4.7883190000000001E-3</v>
       </c>
       <c r="F31" s="16">
         <v>0.25</v>
@@ -10952,111 +10980,111 @@
       </c>
       <c r="I31" s="16">
         <f t="shared" si="2"/>
-        <v>4.8089680000000003E-3</v>
+        <v>4.7883190000000001E-3</v>
       </c>
       <c r="J31" s="16">
         <f t="shared" si="3"/>
-        <v>4.8089680000000003E-3</v>
+        <v>4.7883190000000001E-3</v>
       </c>
       <c r="K31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:K$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,K$9))</f>
-        <v>1.3530704607224994E-2</v>
+        <v>1.3510790116712284E-2</v>
       </c>
       <c r="L31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:L$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,L$9))</f>
-        <v>1.6437366787908719E-2</v>
+        <v>1.6417697084763962E-2</v>
       </c>
       <c r="M31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:M$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,M$9))</f>
-        <v>2.0249470160118424E-2</v>
+        <v>2.0230121496947643E-2</v>
       </c>
       <c r="N31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:N$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,N$9))</f>
-        <v>2.520216728756761E-2</v>
+        <v>2.5183235720577509E-2</v>
       </c>
       <c r="O31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:O$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,O$9))</f>
-        <v>3.155853017687181E-2</v>
+        <v>3.1540133917132673E-2</v>
       </c>
       <c r="P31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:P$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,P$9))</f>
-        <v>3.9589576993249581E-2</v>
+        <v>3.9571857075888714E-2</v>
       </c>
       <c r="Q31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Q$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Q$9))</f>
-        <v>4.9538070445221086E-2</v>
+        <v>4.9521188349862154E-2</v>
       </c>
       <c r="R31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:R$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,R$9))</f>
-        <v>6.1564615216299301E-2</v>
+        <v>6.1548745948044818E-2</v>
       </c>
       <c r="S31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:S$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,S$9))</f>
-        <v>7.5681557751488576E-2</v>
+        <v>7.566687735520887E-2</v>
       </c>
       <c r="T31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:T$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,T$9))</f>
-        <v>9.1690863959189184E-2</v>
+        <v>9.1677531802121917E-2</v>
       </c>
       <c r="U31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:U$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,U$9))</f>
-        <v>0.10915184647827197</v>
+        <v>0.10913998481474232</v>
       </c>
       <c r="V31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:V$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,V$9))</f>
-        <v>0.12740448400000001</v>
+        <v>0.12739415949999999</v>
       </c>
       <c r="W31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:W$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,W$9))</f>
-        <v>0.14565712152172802</v>
+        <v>0.14564833418525766</v>
       </c>
       <c r="X31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:X$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,X$9))</f>
-        <v>0.16311810404081081</v>
+        <v>0.16311078719787805</v>
       </c>
       <c r="Y31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Y$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Y$9))</f>
-        <v>0.17912741024851142</v>
+        <v>0.17912144164479113</v>
       </c>
       <c r="Z31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Z$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Z$9))</f>
-        <v>0.1932443527837007</v>
+        <v>0.19323957305195516</v>
       </c>
       <c r="AA31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AA$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AA$9))</f>
-        <v>0.2052708975547789</v>
+        <v>0.20526713065013782</v>
       </c>
       <c r="AB31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AB$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AB$9))</f>
-        <v>0.21521939100675044</v>
+        <v>0.21521646192411131</v>
       </c>
       <c r="AC31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AC$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AC$9))</f>
-        <v>0.2232504378231282</v>
+        <v>0.22324818508286734</v>
       </c>
       <c r="AD31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AD$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AD$9))</f>
-        <v>0.22960680071243239</v>
+        <v>0.2296050832794225</v>
       </c>
       <c r="AE31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AE$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AE$9))</f>
-        <v>0.23455949783988159</v>
+        <v>0.23455819750305237</v>
       </c>
       <c r="AF31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AF$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AF$9))</f>
-        <v>0.23837160121209131</v>
+        <v>0.23837062191523606</v>
       </c>
       <c r="AG31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AG$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AG$9))</f>
-        <v>0.241278263392775</v>
+        <v>0.24127752888328771</v>
       </c>
       <c r="AH31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AH$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AH$9))</f>
-        <v>0.24347865569679086</v>
+        <v>0.2434781064954705</v>
       </c>
       <c r="AI31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AI$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AI$9))</f>
-        <v>0.24513533496186604</v>
+        <v>0.24513492527939293</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
@@ -11064,14 +11092,14 @@
         <v>38</v>
       </c>
       <c r="D32">
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="E32">
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="F32" s="16">
         <f>E32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="G32" s="5" t="str">
         <f>IF(E32=F32,"n/a",IF(OR(C32="battery electric vehicle",C32="natural gas vehicle",C32="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -11079,111 +11107,111 @@
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="J32" s="16">
         <f t="shared" si="3"/>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="K32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,K$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="L32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,L$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="M32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,M$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="N32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,N$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="O32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,O$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="P32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,P$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="Q32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Q$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="R32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,R$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="S32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,S$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="T32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,T$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="U32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,U$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="V32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,V$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="W32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,W$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="X32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,X$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="Y32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Y$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="Z32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Z$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AA32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AA$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AB32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AB$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AC32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AC$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AD32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AD$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AE32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AE$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AF32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AF$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AG32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AG$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AH32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AH$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AI32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AI$9))</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.25">
@@ -11191,14 +11219,14 @@
         <v>39</v>
       </c>
       <c r="D33">
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="E33">
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="F33" s="16">
         <f>E33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="G33" s="5" t="str">
         <f>IF(E33=F33,"n/a",IF(OR(C33="battery electric vehicle",C33="natural gas vehicle",C33="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -11206,111 +11234,111 @@
       </c>
       <c r="I33" s="16">
         <f t="shared" si="2"/>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="J33" s="16">
         <f t="shared" si="3"/>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="K33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,K$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="L33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,L$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="M33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,M$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="N33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,N$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="O33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,O$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="P33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,P$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="Q33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Q$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="R33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,R$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="S33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,S$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="T33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,T$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="U33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,U$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="V33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,V$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="W33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,W$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="X33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,X$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="Y33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Y$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="Z33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Z$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AA33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AA$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AB33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AB$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AC33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AC$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AD33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AD$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AE33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AE$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AF33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AF$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AG33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AG$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AH33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AH$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AI33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AI$9))</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.25">
@@ -17057,11 +17085,11 @@
       </c>
       <c r="D80">
         <f t="shared" ref="D80:F86" si="6">D10</f>
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="E80">
         <f t="shared" si="6"/>
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="F80">
         <f t="shared" si="6"/>
@@ -17073,111 +17101,111 @@
       </c>
       <c r="I80" s="16">
         <f t="shared" si="5"/>
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="J80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,J$9))</f>
-        <v>0.20192405133527508</v>
+        <v>0.19899617946551834</v>
       </c>
       <c r="K80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,K$9))</f>
-        <v>0.21912805282851533</v>
+        <v>0.21626329664606081</v>
       </c>
       <c r="L80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,L$9))</f>
-        <v>0.24120791635037137</v>
+        <v>0.23842416375084885</v>
       </c>
       <c r="M80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,M$9))</f>
-        <v>0.26910506771371479</v>
+        <v>0.2664236603669965</v>
       </c>
       <c r="N80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,N$9))</f>
-        <v>0.30366278279276282</v>
+        <v>0.30110815606389463</v>
       </c>
       <c r="O80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,O$9))</f>
-        <v>0.34543894815797949</v>
+        <v>0.34303758410994234</v>
       </c>
       <c r="P80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,P$9))</f>
-        <v>0.39447645120038111</v>
+        <v>0.39225498923554947</v>
       </c>
       <c r="Q80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Q$9))</f>
-        <v>0.45008738819399363</v>
+        <v>0.44806994402765193</v>
       </c>
       <c r="R80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,R$9))</f>
-        <v>0.51074095969281419</v>
+        <v>0.50894603305264141</v>
       </c>
       <c r="S80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,S$9))</f>
-        <v>0.57414447400000002</v>
+        <v>0.57258215349999997</v>
       </c>
       <c r="T80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,T$9))</f>
-        <v>0.63754798830718573</v>
+        <v>0.63621827394735875</v>
       </c>
       <c r="U80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,U$9))</f>
-        <v>0.6982015598060064</v>
+        <v>0.69709436297234806</v>
       </c>
       <c r="V80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,V$9))</f>
-        <v>0.75381249679961881</v>
+        <v>0.75290931776445058</v>
       </c>
       <c r="W80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,W$9))</f>
-        <v>0.80284999984202055</v>
+        <v>0.80212672289005771</v>
       </c>
       <c r="X80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,X$9))</f>
-        <v>0.84462616520723721</v>
+        <v>0.84405615093610531</v>
       </c>
       <c r="Y80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Y$9))</f>
-        <v>0.87918388028628536</v>
+        <v>0.87874064663300366</v>
       </c>
       <c r="Z80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Z$9))</f>
-        <v>0.90708103164962861</v>
+        <v>0.90674014324915131</v>
       </c>
       <c r="AA80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AA$9))</f>
-        <v>0.9291608951714847</v>
+        <v>0.92890101035393924</v>
       </c>
       <c r="AB80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AB$9))</f>
-        <v>0.94636489666472501</v>
+        <v>0.94616812753448176</v>
       </c>
       <c r="AC80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AC$9))</f>
-        <v>0.95960685966391612</v>
+        <v>0.95945867083612479</v>
       </c>
       <c r="AD80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AD$9))</f>
-        <v>0.96970362496371199</v>
+        <v>0.96959247776729196</v>
       </c>
       <c r="AE80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AE$9))</f>
-        <v>0.97734704662061023</v>
+        <v>0.97726394056400334</v>
       </c>
       <c r="AF80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AF$9))</f>
-        <v>0.9831017923312273</v>
+        <v>0.983039798498478</v>
       </c>
       <c r="AG80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AG$9))</f>
-        <v>0.98741679392424109</v>
+        <v>0.98737063037907702</v>
       </c>
       <c r="AH80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AH$9))</f>
-        <v>0.99064229953383387</v>
+        <v>0.99060796928242567</v>
       </c>
       <c r="AI80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AI$9))</f>
-        <v>0.99304784793611733</v>
+        <v>0.99302234283162671</v>
       </c>
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.25">
@@ -17186,15 +17214,15 @@
       </c>
       <c r="D81">
         <f t="shared" si="6"/>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="E81">
         <f t="shared" si="6"/>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="F81">
         <f t="shared" si="6"/>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="G81" s="5" t="str">
         <f>IF(E81=F81,"n/a",IF(OR(C81="battery electric vehicle",C81="natural gas vehicle",C81="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -17202,111 +17230,111 @@
       </c>
       <c r="I81" s="16">
         <f t="shared" si="5"/>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="J81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,J$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="K81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,K$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="L81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,L$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="M81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,M$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="N81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,N$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="O81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,O$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="P81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,P$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Q81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Q$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="R81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,R$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="S81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,S$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="T81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,T$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="U81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,U$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="V81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,V$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="W81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,W$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="X81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,X$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Y81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Y$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Z81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Z$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AA81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AA$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AB81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AB$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AC81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AC$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AD81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AD$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AE81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AE$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AF81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AF$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AG81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AG$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AH81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AH$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AI81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AI$9))</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.25">
@@ -17444,15 +17472,15 @@
       </c>
       <c r="D83">
         <f t="shared" si="6"/>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="E83">
         <f t="shared" si="6"/>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="F83">
         <f t="shared" si="6"/>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="G83" s="5" t="str">
         <f>IF(E83=F83,"n/a",IF(OR(C83="battery electric vehicle",C83="natural gas vehicle",C83="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -17460,111 +17488,111 @@
       </c>
       <c r="I83" s="16">
         <f t="shared" si="5"/>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="J83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,J$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="K83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,K$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="L83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,L$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="M83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,M$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="N83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,N$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="O83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,O$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="P83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,P$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Q83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Q$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="R83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,R$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="S83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,S$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="T83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,T$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="U83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,U$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="V83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,V$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="W83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,W$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="X83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,X$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Y83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Y$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Z83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Z$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AA83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AA$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AB83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AB$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AC83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AC$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AD83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AD$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AE83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AE$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AF83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AF$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AG83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AG$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AH83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AH$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AI83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AI$9))</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.25">
@@ -17573,15 +17601,15 @@
       </c>
       <c r="D84">
         <f t="shared" si="6"/>
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="E84">
         <f t="shared" si="6"/>
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="F84">
         <f t="shared" si="6"/>
-        <v>0.10239066607264966</v>
+        <v>9.1008967024832244E-2</v>
       </c>
       <c r="G84" s="5" t="str">
         <f>IF(E84=F84,"n/a",IF(OR(C84="battery electric vehicle",C84="natural gas vehicle",C84="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -17589,111 +17617,111 @@
       </c>
       <c r="I84" s="16">
         <f t="shared" si="5"/>
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="J84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,J$9))</f>
-        <v>1.5378299625391417E-2</v>
+        <v>1.2452844371960014E-2</v>
       </c>
       <c r="K84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,K$9))</f>
-        <v>1.5825738596288972E-2</v>
+        <v>1.2856799259209385E-2</v>
       </c>
       <c r="L84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,L$9))</f>
-        <v>1.6422470125358253E-2</v>
+        <v>1.3395537798366533E-2</v>
       </c>
       <c r="M84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,M$9))</f>
-        <v>1.7215045665964251E-2</v>
+        <v>1.4111087368176831E-2</v>
       </c>
       <c r="N84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,N$9))</f>
-        <v>1.8262017764989459E-2</v>
+        <v>1.5056310121944961E-2</v>
       </c>
       <c r="O84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,O$9))</f>
-        <v>1.9635127408011214E-2</v>
+        <v>1.6295974941294988E-2</v>
       </c>
       <c r="P84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,P$9))</f>
-        <v>2.1419075932136523E-2</v>
+        <v>1.7906551515517261E-2</v>
       </c>
       <c r="Q84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Q$9))</f>
-        <v>2.370862118462793E-2</v>
+        <v>1.9973588708248197E-2</v>
       </c>
       <c r="R84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,R$9))</f>
-        <v>2.6601383198249652E-2</v>
+        <v>2.2585219408872568E-2</v>
       </c>
       <c r="S84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,S$9))</f>
-        <v>3.0184804464321601E-2</v>
+        <v>2.5820388063492336E-2</v>
       </c>
       <c r="T84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,T$9))</f>
-        <v>3.4516734368895005E-2</v>
+        <v>2.9731322000837706E-2</v>
       </c>
       <c r="U84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,U$9))</f>
-        <v>3.9601620069100008E-2</v>
+        <v>3.4322036183783898E-2</v>
       </c>
       <c r="V84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,V$9))</f>
-        <v>4.5368130204196222E-2</v>
+        <v>3.9528131546403743E-2</v>
       </c>
       <c r="W84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,W$9))</f>
-        <v>5.1657530341761002E-2</v>
+        <v>4.5206300165332253E-2</v>
       </c>
       <c r="X84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,X$9))</f>
-        <v>5.8232082536324822E-2</v>
+        <v>5.1141908512416123E-2</v>
       </c>
       <c r="Y84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Y$9))</f>
-        <v>6.4806634730888643E-2</v>
+        <v>5.707751685949998E-2</v>
       </c>
       <c r="Z84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Z$9))</f>
-        <v>7.1096034868453423E-2</v>
+        <v>6.2755685478428497E-2</v>
       </c>
       <c r="AA84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AA$9))</f>
-        <v>7.6862545003549651E-2</v>
+        <v>6.7961780841048341E-2</v>
       </c>
       <c r="AB84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AB$9))</f>
-        <v>8.194743070375464E-2</v>
+        <v>7.2552495023994523E-2</v>
       </c>
       <c r="AC84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AC$9))</f>
-        <v>8.6279360608328054E-2</v>
+        <v>7.6463428961339897E-2</v>
       </c>
       <c r="AD84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AD$9))</f>
-        <v>8.9862781874400013E-2</v>
+        <v>7.9698597615959682E-2</v>
       </c>
       <c r="AE84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AE$9))</f>
-        <v>9.2755543888021721E-2</v>
+        <v>8.231022831658405E-2</v>
       </c>
       <c r="AF84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AF$9))</f>
-        <v>9.5045089140513128E-2</v>
+        <v>8.4377265509314986E-2</v>
       </c>
       <c r="AG84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AG$9))</f>
-        <v>9.6829037664638448E-2</v>
+        <v>8.5987842083537255E-2</v>
       </c>
       <c r="AH84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AH$9))</f>
-        <v>9.8202147307660206E-2</v>
+        <v>8.7227506902887289E-2</v>
       </c>
       <c r="AI84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AI$9))</f>
-        <v>9.9249119406685404E-2</v>
+        <v>8.8172729656655416E-2</v>
       </c>
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.25">
@@ -18966,111 +18994,111 @@
       </c>
       <c r="B2">
         <f>Data!I10</f>
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="C2">
         <f>Data!J10</f>
-        <v>0.148288948</v>
+        <v>0.14516430699999999</v>
       </c>
       <c r="D2">
         <f>Data!K10</f>
-        <v>0.18868208833608399</v>
+        <v>0.18570563616387542</v>
       </c>
       <c r="E2">
         <f>Data!L10</f>
-        <v>0.20192405133527508</v>
+        <v>0.19899617946551834</v>
       </c>
       <c r="F2">
         <f>Data!M10</f>
-        <v>0.21912805282851533</v>
+        <v>0.21626329664606081</v>
       </c>
       <c r="G2">
         <f>Data!N10</f>
-        <v>0.24120791635037137</v>
+        <v>0.23842416375084885</v>
       </c>
       <c r="H2">
         <f>Data!O10</f>
-        <v>0.26910506771371479</v>
+        <v>0.2664236603669965</v>
       </c>
       <c r="I2">
         <f>Data!P10</f>
-        <v>0.30366278279276282</v>
+        <v>0.30110815606389463</v>
       </c>
       <c r="J2">
         <f>Data!Q10</f>
-        <v>0.34543894815797949</v>
+        <v>0.34303758410994234</v>
       </c>
       <c r="K2">
         <f>Data!R10</f>
-        <v>0.39447645120038111</v>
+        <v>0.39225498923554947</v>
       </c>
       <c r="L2">
         <f>Data!S10</f>
-        <v>0.45008738819399363</v>
+        <v>0.44806994402765193</v>
       </c>
       <c r="M2">
         <f>Data!T10</f>
-        <v>0.51074095969281419</v>
+        <v>0.50894603305264141</v>
       </c>
       <c r="N2">
         <f>Data!U10</f>
-        <v>0.57414447400000002</v>
+        <v>0.57258215349999997</v>
       </c>
       <c r="O2">
         <f>Data!V10</f>
-        <v>0.63754798830718573</v>
+        <v>0.63621827394735875</v>
       </c>
       <c r="P2">
         <f>Data!W10</f>
-        <v>0.6982015598060064</v>
+        <v>0.69709436297234806</v>
       </c>
       <c r="Q2">
         <f>Data!X10</f>
-        <v>0.75381249679961881</v>
+        <v>0.75290931776445058</v>
       </c>
       <c r="R2">
         <f>Data!Y10</f>
-        <v>0.80284999984202055</v>
+        <v>0.80212672289005771</v>
       </c>
       <c r="S2">
         <f>Data!Z10</f>
-        <v>0.84462616520723721</v>
+        <v>0.84405615093610531</v>
       </c>
       <c r="T2">
         <f>Data!AA10</f>
-        <v>0.87918388028628536</v>
+        <v>0.87874064663300366</v>
       </c>
       <c r="U2">
         <f>Data!AB10</f>
-        <v>0.90708103164962861</v>
+        <v>0.90674014324915131</v>
       </c>
       <c r="V2">
         <f>Data!AC10</f>
-        <v>0.9291608951714847</v>
+        <v>0.92890101035393924</v>
       </c>
       <c r="W2">
         <f>Data!AD10</f>
-        <v>0.94636489666472501</v>
+        <v>0.94616812753448176</v>
       </c>
       <c r="X2">
         <f>Data!AE10</f>
-        <v>0.95960685966391612</v>
+        <v>0.95945867083612479</v>
       </c>
       <c r="Y2">
         <f>Data!AF10</f>
-        <v>0.96970362496371199</v>
+        <v>0.96959247776729196</v>
       </c>
       <c r="Z2">
         <f>Data!AG10</f>
-        <v>0.97734704662061023</v>
+        <v>0.97726394056400334</v>
       </c>
       <c r="AA2">
         <f>Data!AH10</f>
-        <v>0.9831017923312273</v>
+        <v>0.983039798498478</v>
       </c>
       <c r="AB2">
         <f>Data!AI10</f>
-        <v>0.98741679392424109</v>
+        <v>0.98737063037907702</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -19079,111 +19107,111 @@
       </c>
       <c r="B3">
         <f>Data!I11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="C3">
         <f>Data!J11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="D3">
         <f>Data!K11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="E3">
         <f>Data!L11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="F3">
         <f>Data!M11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="G3">
         <f>Data!N11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="H3">
         <f>Data!O11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="I3">
         <f>Data!P11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="J3">
         <f>Data!Q11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="K3">
         <f>Data!R11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="L3">
         <f>Data!S11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="M3">
         <f>Data!T11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="N3">
         <f>Data!U11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="O3">
         <f>Data!V11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="P3">
         <f>Data!W11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Q3">
         <f>Data!X11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="R3">
         <f>Data!Y11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="S3">
         <f>Data!Z11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="T3">
         <f>Data!AA11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="U3">
         <f>Data!AB11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="V3">
         <f>Data!AC11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="W3">
         <f>Data!AD11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="X3">
         <f>Data!AE11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Y3">
         <f>Data!AF11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="Z3">
         <f>Data!AG11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AA3">
         <f>Data!AH11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
       <c r="AB3">
         <f>Data!AI11</f>
-        <v>1.0097E-4</v>
+        <v>1.2431200000000001E-4</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -19305,111 +19333,111 @@
       </c>
       <c r="B5">
         <f>Data!I13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="C5">
         <f>Data!J13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="D5">
         <f>Data!K13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="E5">
         <f>Data!L13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="F5">
         <f>Data!M13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="G5">
         <f>Data!N13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="H5">
         <f>Data!O13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="I5">
         <f>Data!P13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="K5">
         <f>Data!R13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="L5">
         <f>Data!S13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="M5">
         <f>Data!T13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="N5">
         <f>Data!U13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="O5">
         <f>Data!V13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="P5">
         <f>Data!W13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI13</f>
-        <v>6.7382960000000006E-2</v>
+        <v>6.7834564E-2</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -19418,111 +19446,111 @@
       </c>
       <c r="B6">
         <f>Data!I14</f>
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="C6">
         <f>Data!J14</f>
-        <v>1.4073499E-2</v>
+        <v>1.1274849999999999E-2</v>
       </c>
       <c r="D6">
         <f>Data!K14</f>
-        <v>1.7532504683762919E-2</v>
+        <v>1.4397694324839349E-2</v>
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>1.9136207820162347E-2</v>
+        <v>1.5845542549472465E-2</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>2.1419075932136523E-2</v>
+        <v>1.7906551515517257E-2</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>2.4601163379775384E-2</v>
+        <v>2.0779389734213474E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>2.8909159345260678E-2</v>
+        <v>2.4668715737751964E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>3.4516734368895005E-2</v>
+        <v>2.9731322000837702E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>4.1454074547037548E-2</v>
+        <v>3.5994461002455284E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>4.9516267970164535E-2</v>
+        <v>4.3273135072103008E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
-        <v>5.8232082536324822E-2</v>
+        <v>5.1141908512416123E-2</v>
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>6.694789710248511E-2</v>
+        <v>5.9010681952729238E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>7.5010090525612097E-2</v>
+        <v>6.6289356022376955E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>8.1947430703754653E-2</v>
+        <v>7.2552495023994537E-2</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>8.7555005727388974E-2</v>
+        <v>7.7615101287080282E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>9.1863001692874258E-2</v>
+        <v>8.1504427290618769E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>9.5045089140513128E-2</v>
+        <v>8.4377265509314986E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>9.7327957252487315E-2</v>
+        <v>8.6438274475359775E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>9.8931660388886733E-2</v>
+        <v>8.7886122699992894E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>0.1000416949472914</v>
+        <v>8.8888279226465708E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>0.10080217496242386</v>
+        <v>8.9574852454881629E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>0.10131951705381374</v>
+        <v>9.0041916970468053E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>0.10166977091237364</v>
+        <v>9.0358131621282672E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>0.1019061316961364</v>
+        <v>9.0571521826350254E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>0.10206528444191545</v>
+        <v>9.0715207409543072E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>0.10217229100021745</v>
+        <v>9.0811814600702825E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>0.1022441654605116</v>
+        <v>9.0876703985384694E-2</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -19886,111 +19914,111 @@
       </c>
       <c r="B2">
         <f>Data!I17</f>
-        <v>0.328639128</v>
+        <v>0.327825113</v>
       </c>
       <c r="C2">
         <f>Data!J17</f>
-        <v>0.328639128</v>
+        <v>0.327825113</v>
       </c>
       <c r="D2">
         <f>Data!K17</f>
-        <v>0.32762040015730876</v>
+        <v>0.32683534063894454</v>
       </c>
       <c r="E2">
         <f>Data!L17</f>
-        <v>0.32728089234755592</v>
+        <v>0.32650548271971053</v>
       </c>
       <c r="F2">
         <f>Data!M17</f>
-        <v>0.32683562599529409</v>
+        <v>0.32607287225172482</v>
       </c>
       <c r="G2">
         <f>Data!N17</f>
-        <v>0.3262571344990054</v>
+        <v>0.32551082332154191</v>
       </c>
       <c r="H2">
         <f>Data!O17</f>
-        <v>0.32551469017338575</v>
+        <v>0.32478948162229127</v>
       </c>
       <c r="I2">
         <f>Data!P17</f>
-        <v>0.3245766371953786</v>
+        <v>0.32387809108997362</v>
       </c>
       <c r="J2">
         <f>Data!Q17</f>
-        <v>0.32341462007324273</v>
+        <v>0.32274910218600394</v>
       </c>
       <c r="K2">
         <f>Data!R17</f>
-        <v>0.32200987964580063</v>
+        <v>0.32138428894416071</v>
       </c>
       <c r="L2">
         <f>Data!S17</f>
-        <v>0.32036097380721384</v>
+        <v>0.31978225024783452</v>
       </c>
       <c r="M2">
         <f>Data!T17</f>
-        <v>0.31849103359800773</v>
+        <v>0.31796545967989537</v>
       </c>
       <c r="N2">
         <f>Data!U17</f>
-        <v>0.31645153276761123</v>
+        <v>0.3159839279422888</v>
       </c>
       <c r="O2">
         <f>Data!V17</f>
-        <v>0.314319564</v>
+        <v>0.3139125565</v>
       </c>
       <c r="P2">
         <f>Data!W17</f>
-        <v>0.31218759523238876</v>
+        <v>0.31184118505771119</v>
       </c>
       <c r="Q2">
         <f>Data!X17</f>
-        <v>0.31014809440199226</v>
+        <v>0.30985965332010462</v>
       </c>
       <c r="R2">
         <f>Data!Y17</f>
-        <v>0.30827815419278615</v>
+        <v>0.30804286275216547</v>
       </c>
       <c r="S2">
         <f>Data!Z17</f>
-        <v>0.30662924835419936</v>
+        <v>0.30644082405583928</v>
       </c>
       <c r="T2">
         <f>Data!AA17</f>
-        <v>0.30522450792675726</v>
+        <v>0.30507601081399605</v>
       </c>
       <c r="U2">
         <f>Data!AB17</f>
-        <v>0.30406249080462139</v>
+        <v>0.30394702191002637</v>
       </c>
       <c r="V2">
         <f>Data!AC17</f>
-        <v>0.30312443782661425</v>
+        <v>0.30303563137770873</v>
       </c>
       <c r="W2">
         <f>Data!AD17</f>
-        <v>0.30238199350099459</v>
+        <v>0.30231428967845808</v>
       </c>
       <c r="X2">
         <f>Data!AE17</f>
-        <v>0.3018035020047059</v>
+        <v>0.30175224074827517</v>
       </c>
       <c r="Y2">
         <f>Data!AF17</f>
-        <v>0.30135823565244407</v>
+        <v>0.30131963028028946</v>
       </c>
       <c r="Z2">
         <f>Data!AG17</f>
-        <v>0.30101872784269124</v>
+        <v>0.30098977236105545</v>
       </c>
       <c r="AA2">
         <f>Data!AH17</f>
-        <v>0.30076171470346302</v>
+        <v>0.30074006435173656</v>
       </c>
       <c r="AB2">
         <f>Data!AI17</f>
-        <v>0.30056820905547738</v>
+        <v>0.30055205874900526</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -19999,111 +20027,111 @@
       </c>
       <c r="B3">
         <f>Data!I18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="C3">
         <f>Data!J18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="D3">
         <f>Data!K18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="E3">
         <f>Data!L18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="F3">
         <f>Data!M18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="G3">
         <f>Data!N18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="H3">
         <f>Data!O18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="I3">
         <f>Data!P18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="J3">
         <f>Data!Q18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="K3">
         <f>Data!R18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="L3">
         <f>Data!S18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="M3">
         <f>Data!T18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="N3">
         <f>Data!U18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="O3">
         <f>Data!V18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="P3">
         <f>Data!W18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="Q3">
         <f>Data!X18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="R3">
         <f>Data!Y18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="S3">
         <f>Data!Z18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="T3">
         <f>Data!AA18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="U3">
         <f>Data!AB18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="V3">
         <f>Data!AC18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="W3">
         <f>Data!AD18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="X3">
         <f>Data!AE18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="Y3">
         <f>Data!AF18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="Z3">
         <f>Data!AG18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AA3">
         <f>Data!AH18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
       <c r="AB3">
         <f>Data!AI18</f>
-        <v>0.250478074</v>
+        <v>0.24903946699999999</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -20112,111 +20140,111 @@
       </c>
       <c r="B4">
         <f>Data!I19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="C4">
         <f>Data!J19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="D4">
         <f>Data!K19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="E4">
         <f>Data!L19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="F4">
         <f>Data!M19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="G4">
         <f>Data!N19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="H4">
         <f>Data!O19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="I4">
         <f>Data!P19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="J4">
         <f>Data!Q19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="K4">
         <f>Data!R19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="L4">
         <f>Data!S19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="M4">
         <f>Data!T19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="N4">
         <f>Data!U19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="O4">
         <f>Data!V19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="P4">
         <f>Data!W19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="Q4">
         <f>Data!X19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="R4">
         <f>Data!Y19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="S4">
         <f>Data!Z19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="T4">
         <f>Data!AA19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="U4">
         <f>Data!AB19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="V4">
         <f>Data!AC19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="W4">
         <f>Data!AD19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="X4">
         <f>Data!AE19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="Y4">
         <f>Data!AF19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="Z4">
         <f>Data!AG19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AA4">
         <f>Data!AH19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
       <c r="AB4">
         <f>Data!AI19</f>
-        <v>0.76148265500000001</v>
+        <v>0.76294610699999998</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -20338,111 +20366,111 @@
       </c>
       <c r="B6">
         <f>Data!I21</f>
-        <v>1.003192E-3</v>
+        <v>1.004397E-3</v>
       </c>
       <c r="C6">
         <f>Data!J21</f>
-        <v>1.003192E-3</v>
+        <v>1.004397E-3</v>
       </c>
       <c r="D6">
         <f>Data!K21</f>
-        <v>1.0114628802088777E-3</v>
+        <v>1.0045555071991257E-3</v>
       </c>
       <c r="E6">
         <f>Data!L21</f>
-        <v>1.0142192870790641E-3</v>
+        <v>1.0046083323303825E-3</v>
       </c>
       <c r="F6">
         <f>Data!M21</f>
-        <v>1.0178343297884813E-3</v>
+        <v>1.0046776127793937E-3</v>
       </c>
       <c r="G6">
         <f>Data!N21</f>
-        <v>1.0225310050604737E-3</v>
+        <v>1.0047676221645819E-3</v>
       </c>
       <c r="H6">
         <f>Data!O21</f>
-        <v>1.0285587858097846E-3</v>
+        <v>1.0048831415070687E-3</v>
       </c>
       <c r="I6">
         <f>Data!P21</f>
-        <v>1.0361746803456418E-3</v>
+        <v>1.0050290962399662E-3</v>
       </c>
       <c r="J6">
         <f>Data!Q21</f>
-        <v>1.0456089021417803E-3</v>
+        <v>1.0052098982870363E-3</v>
       </c>
       <c r="K6">
         <f>Data!R21</f>
-        <v>1.0570137536762662E-3</v>
+        <v>1.0054284664475612E-3</v>
       </c>
       <c r="L6">
         <f>Data!S21</f>
-        <v>1.0704009431641303E-3</v>
+        <v>1.0056850251035077E-3</v>
       </c>
       <c r="M6">
         <f>Data!T21</f>
-        <v>1.0855826735733526E-3</v>
+        <v>1.005975975220578E-3</v>
       </c>
       <c r="N6">
         <f>Data!U21</f>
-        <v>1.1021410381798931E-3</v>
+        <v>1.0062933078296352E-3</v>
       </c>
       <c r="O6">
         <f>Data!V21</f>
-        <v>1.1194501344340981E-3</v>
+        <v>1.0066250278276717E-3</v>
       </c>
       <c r="P6">
         <f>Data!W21</f>
-        <v>1.1367592306883029E-3</v>
+        <v>1.0069567478257085E-3</v>
       </c>
       <c r="Q6">
         <f>Data!X21</f>
-        <v>1.1533175952948434E-3</v>
+        <v>1.0072740804347657E-3</v>
       </c>
       <c r="R6">
         <f>Data!Y21</f>
-        <v>1.1684993257040656E-3</v>
+        <v>1.007565030551836E-3</v>
       </c>
       <c r="S6">
         <f>Data!Z21</f>
-        <v>1.1818865151919297E-3</v>
+        <v>1.0078215892077825E-3</v>
       </c>
       <c r="T6">
         <f>Data!AA21</f>
-        <v>1.1932913667264157E-3</v>
+        <v>1.0080401573683074E-3</v>
       </c>
       <c r="U6">
         <f>Data!AB21</f>
-        <v>1.2027255885225542E-3</v>
+        <v>1.0082209594153774E-3</v>
       </c>
       <c r="V6">
         <f>Data!AC21</f>
-        <v>1.2103414830584114E-3</v>
+        <v>1.008366914148275E-3</v>
       </c>
       <c r="W6">
         <f>Data!AD21</f>
-        <v>1.2163692638077223E-3</v>
+        <v>1.0084824334907617E-3</v>
       </c>
       <c r="X6">
         <f>Data!AE21</f>
-        <v>1.2210659390797147E-3</v>
+        <v>1.00857244287595E-3</v>
       </c>
       <c r="Y6">
         <f>Data!AF21</f>
-        <v>1.2246809817891319E-3</v>
+        <v>1.0086417233249611E-3</v>
       </c>
       <c r="Z6">
         <f>Data!AG21</f>
-        <v>1.2274373886593183E-3</v>
+        <v>1.008694548456218E-3</v>
       </c>
       <c r="AA6">
         <f>Data!AH21</f>
-        <v>1.2295240351585918E-3</v>
+        <v>1.0087345379717005E-3</v>
       </c>
       <c r="AB6">
         <f>Data!AI21</f>
-        <v>1.2310950750057041E-3</v>
+        <v>1.0087646461487737E-3</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -20451,111 +20479,111 @@
       </c>
       <c r="B7">
         <f>Data!I22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="C7">
         <f>Data!J22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="D7">
         <f>Data!K22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="E7">
         <f>Data!L22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="F7">
         <f>Data!M22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="G7">
         <f>Data!N22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="H7">
         <f>Data!O22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="I7">
         <f>Data!P22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="J7">
         <f>Data!Q22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="K7">
         <f>Data!R22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="L7">
         <f>Data!S22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="M7">
         <f>Data!T22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="N7">
         <f>Data!U22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="O7">
         <f>Data!V22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="P7">
         <f>Data!W22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="Q7">
         <f>Data!X22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="R7">
         <f>Data!Y22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="S7">
         <f>Data!Z22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="T7">
         <f>Data!AA22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="U7">
         <f>Data!AB22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="V7">
         <f>Data!AC22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="W7">
         <f>Data!AD22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="X7">
         <f>Data!AE22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="Y7">
         <f>Data!AF22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="Z7">
         <f>Data!AG22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AA7">
         <f>Data!AH22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
       <c r="AB7">
         <f>Data!AI22</f>
-        <v>6.0223199999999996E-4</v>
+        <v>5.9752799999999995E-4</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -20806,111 +20834,111 @@
       </c>
       <c r="B2">
         <f>Data!I24</f>
-        <v>0.12184009799999999</v>
+        <v>0.121750944</v>
       </c>
       <c r="C2">
         <f>Data!J24</f>
-        <v>0.12184009799999999</v>
+        <v>0.121750944</v>
       </c>
       <c r="D2">
         <f>Data!K24</f>
-        <v>0.1441844927675226</v>
+        <v>0.14409851008133101</v>
       </c>
       <c r="E2">
         <f>Data!L24</f>
-        <v>0.15163112984748478</v>
+        <v>0.15154620405378205</v>
       </c>
       <c r="F2">
         <f>Data!M24</f>
-        <v>0.16139743516937402</v>
+        <v>0.16131389549595992</v>
       </c>
       <c r="G2">
         <f>Data!N24</f>
-        <v>0.17408585087869802</v>
+        <v>0.17400411205728125</v>
       </c>
       <c r="H2">
         <f>Data!O24</f>
-        <v>0.19037034651074775</v>
+        <v>0.19029091892874461</v>
       </c>
       <c r="I2">
         <f>Data!P24</f>
-        <v>0.21094524902648606</v>
+        <v>0.21086874161632621</v>
       </c>
       <c r="J2">
         <f>Data!Q24</f>
-        <v>0.23643249715649947</v>
+        <v>0.23635960712164891</v>
       </c>
       <c r="K2">
         <f>Data!R24</f>
-        <v>0.26724354731268585</v>
+        <v>0.2671750302541378</v>
       </c>
       <c r="L2">
         <f>Data!S24</f>
-        <v>0.30341003010412881</v>
+        <v>0.30334664611217177</v>
       </c>
       <c r="M2">
         <f>Data!T24</f>
-        <v>0.34442459795552233</v>
+        <v>0.34436703511319711</v>
       </c>
       <c r="N2">
         <f>Data!U24</f>
-        <v>0.38915824493495493</v>
+        <v>0.38910703108681111</v>
       </c>
       <c r="O2">
         <f>Data!V24</f>
-        <v>0.43592004900000003</v>
+        <v>0.43587547199999999</v>
       </c>
       <c r="P2">
         <f>Data!W24</f>
-        <v>0.48268185306504513</v>
+        <v>0.48264391291318898</v>
       </c>
       <c r="Q2">
         <f>Data!X24</f>
-        <v>0.52741550004447768</v>
+        <v>0.52738390888680287</v>
       </c>
       <c r="R2">
         <f>Data!Y24</f>
-        <v>0.56843006789587125</v>
+        <v>0.5684042978878282</v>
       </c>
       <c r="S2">
         <f>Data!Z24</f>
-        <v>0.6045965506873141</v>
+        <v>0.60457591374586217</v>
       </c>
       <c r="T2">
         <f>Data!AA24</f>
-        <v>0.63540760084350045</v>
+        <v>0.63539133687835103</v>
       </c>
       <c r="U2">
         <f>Data!AB24</f>
-        <v>0.66089484897351403</v>
+        <v>0.6608822023836739</v>
       </c>
       <c r="V2">
         <f>Data!AC24</f>
-        <v>0.68146975148925226</v>
+        <v>0.68146002507125536</v>
       </c>
       <c r="W2">
         <f>Data!AD24</f>
-        <v>0.69775424712130196</v>
+        <v>0.6977468319427188</v>
       </c>
       <c r="X2">
         <f>Data!AE24</f>
-        <v>0.71044266283062596</v>
+        <v>0.7104370485040401</v>
       </c>
       <c r="Y2">
         <f>Data!AF24</f>
-        <v>0.72020896815251523</v>
+        <v>0.72020473994621803</v>
       </c>
       <c r="Z2">
         <f>Data!AG24</f>
-        <v>0.72765560523247741</v>
+        <v>0.72765243391866896</v>
       </c>
       <c r="AA2">
         <f>Data!AH24</f>
-        <v>0.73329283512126131</v>
+        <v>0.73329046389289587</v>
       </c>
       <c r="AB2">
         <f>Data!AI24</f>
-        <v>0.73753711549443191</v>
+        <v>0.73753534665181442</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -20919,111 +20947,111 @@
       </c>
       <c r="B3">
         <f>Data!I25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="C3">
         <f>Data!J25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="D3">
         <f>Data!K25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="E3">
         <f>Data!L25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="F3">
         <f>Data!M25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="G3">
         <f>Data!N25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="H3">
         <f>Data!O25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="I3">
         <f>Data!P25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="J3">
         <f>Data!Q25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="K3">
         <f>Data!R25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="L3">
         <f>Data!S25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="M3">
         <f>Data!T25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="N3">
         <f>Data!U25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="O3">
         <f>Data!V25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="P3">
         <f>Data!W25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="Q3">
         <f>Data!X25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="R3">
         <f>Data!Y25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="S3">
         <f>Data!Z25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="T3">
         <f>Data!AA25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="U3">
         <f>Data!AB25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="V3">
         <f>Data!AC25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="W3">
         <f>Data!AD25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="X3">
         <f>Data!AE25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="Y3">
         <f>Data!AF25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="Z3">
         <f>Data!AG25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AA3">
         <f>Data!AH25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
       <c r="AB3">
         <f>Data!AI25</f>
-        <v>1.5737247999999999E-2</v>
+        <v>1.5712292999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -21032,111 +21060,111 @@
       </c>
       <c r="B4">
         <f>Data!I26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="C4">
         <f>Data!J26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="D4">
         <f>Data!K26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="E4">
         <f>Data!L26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="F4">
         <f>Data!M26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="G4">
         <f>Data!N26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="H4">
         <f>Data!O26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="I4">
         <f>Data!P26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="J4">
         <f>Data!Q26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="K4">
         <f>Data!R26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="L4">
         <f>Data!S26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="M4">
         <f>Data!T26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="N4">
         <f>Data!U26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="O4">
         <f>Data!V26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="P4">
         <f>Data!W26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="Q4">
         <f>Data!X26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="R4">
         <f>Data!Y26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="S4">
         <f>Data!Z26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="T4">
         <f>Data!AA26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="U4">
         <f>Data!AB26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="V4">
         <f>Data!AC26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="W4">
         <f>Data!AD26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="X4">
         <f>Data!AE26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="Y4">
         <f>Data!AF26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="Z4">
         <f>Data!AG26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AA4">
         <f>Data!AH26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
       <c r="AB4">
         <f>Data!AI26</f>
-        <v>0.37956814</v>
+        <v>0.37953625800000002</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -21371,111 +21399,111 @@
       </c>
       <c r="B7">
         <f>Data!I29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="C7">
         <f>Data!J29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="D7">
         <f>Data!K29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="E7">
         <f>Data!L29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="F7">
         <f>Data!M29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="G7">
         <f>Data!N29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="H7">
         <f>Data!O29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="I7">
         <f>Data!P29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="J7">
         <f>Data!Q29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="K7">
         <f>Data!R29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="L7">
         <f>Data!S29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="M7">
         <f>Data!T29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="N7">
         <f>Data!U29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="O7">
         <f>Data!V29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="P7">
         <f>Data!W29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="Q7">
         <f>Data!X29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="R7">
         <f>Data!Y29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="S7">
         <f>Data!Z29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="T7">
         <f>Data!AA29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="U7">
         <f>Data!AB29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="V7">
         <f>Data!AC29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="W7">
         <f>Data!AD29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="X7">
         <f>Data!AE29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="Y7">
         <f>Data!AF29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="Z7">
         <f>Data!AG29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AA7">
         <f>Data!AH29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
       <c r="AB7">
         <f>Data!AI29</f>
-        <v>5.5449391000000001E-2</v>
+        <v>5.5457042999999998E-2</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -21484,111 +21512,111 @@
       </c>
       <c r="B8">
         <f>Data!I30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="C8">
         <f>Data!J30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="D8">
         <f>Data!K30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="E8">
         <f>Data!L30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="F8">
         <f>Data!M30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="G8">
         <f>Data!N30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="H8">
         <f>Data!O30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="I8">
         <f>Data!P30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="J8">
         <f>Data!Q30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="K8">
         <f>Data!R30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="L8">
         <f>Data!S30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="M8">
         <f>Data!T30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="N8">
         <f>Data!U30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="O8">
         <f>Data!V30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="P8">
         <f>Data!W30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="Q8">
         <f>Data!X30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="R8">
         <f>Data!Y30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="S8">
         <f>Data!Z30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="T8">
         <f>Data!AA30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="U8">
         <f>Data!AB30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="V8">
         <f>Data!AC30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="W8">
         <f>Data!AD30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="X8">
         <f>Data!AE30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="Y8">
         <f>Data!AF30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="Z8">
         <f>Data!AG30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AA8">
         <f>Data!AH30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
       <c r="AB8">
         <f>Data!AI30</f>
-        <v>2.0286950000000001E-3</v>
+        <v>2.025855E-3</v>
       </c>
     </row>
   </sheetData>
@@ -21726,111 +21754,111 @@
       </c>
       <c r="B2">
         <f>Data!I31</f>
-        <v>4.8089680000000003E-3</v>
+        <v>4.7883190000000001E-3</v>
       </c>
       <c r="C2">
         <f>Data!J31</f>
-        <v>4.8089680000000003E-3</v>
+        <v>4.7883190000000001E-3</v>
       </c>
       <c r="D2">
         <f>Data!K31</f>
-        <v>1.3530704607224994E-2</v>
+        <v>1.3510790116712284E-2</v>
       </c>
       <c r="E2">
         <f>Data!L31</f>
-        <v>1.6437366787908719E-2</v>
+        <v>1.6417697084763962E-2</v>
       </c>
       <c r="F2">
         <f>Data!M31</f>
-        <v>2.0249470160118424E-2</v>
+        <v>2.0230121496947643E-2</v>
       </c>
       <c r="G2">
         <f>Data!N31</f>
-        <v>2.520216728756761E-2</v>
+        <v>2.5183235720577509E-2</v>
       </c>
       <c r="H2">
         <f>Data!O31</f>
-        <v>3.155853017687181E-2</v>
+        <v>3.1540133917132673E-2</v>
       </c>
       <c r="I2">
         <f>Data!P31</f>
-        <v>3.9589576993249581E-2</v>
+        <v>3.9571857075888714E-2</v>
       </c>
       <c r="J2">
         <f>Data!Q31</f>
-        <v>4.9538070445221086E-2</v>
+        <v>4.9521188349862154E-2</v>
       </c>
       <c r="K2">
         <f>Data!R31</f>
-        <v>6.1564615216299301E-2</v>
+        <v>6.1548745948044818E-2</v>
       </c>
       <c r="L2">
         <f>Data!S31</f>
-        <v>7.5681557751488576E-2</v>
+        <v>7.566687735520887E-2</v>
       </c>
       <c r="M2">
         <f>Data!T31</f>
-        <v>9.1690863959189184E-2</v>
+        <v>9.1677531802121917E-2</v>
       </c>
       <c r="N2">
         <f>Data!U31</f>
-        <v>0.10915184647827197</v>
+        <v>0.10913998481474232</v>
       </c>
       <c r="O2">
         <f>Data!V31</f>
-        <v>0.12740448400000001</v>
+        <v>0.12739415949999999</v>
       </c>
       <c r="P2">
         <f>Data!W31</f>
-        <v>0.14565712152172802</v>
+        <v>0.14564833418525766</v>
       </c>
       <c r="Q2">
         <f>Data!X31</f>
-        <v>0.16311810404081081</v>
+        <v>0.16311078719787805</v>
       </c>
       <c r="R2">
         <f>Data!Y31</f>
-        <v>0.17912741024851142</v>
+        <v>0.17912144164479113</v>
       </c>
       <c r="S2">
         <f>Data!Z31</f>
-        <v>0.1932443527837007</v>
+        <v>0.19323957305195516</v>
       </c>
       <c r="T2">
         <f>Data!AA31</f>
-        <v>0.2052708975547789</v>
+        <v>0.20526713065013782</v>
       </c>
       <c r="U2">
         <f>Data!AB31</f>
-        <v>0.21521939100675044</v>
+        <v>0.21521646192411131</v>
       </c>
       <c r="V2">
         <f>Data!AC31</f>
-        <v>0.2232504378231282</v>
+        <v>0.22324818508286734</v>
       </c>
       <c r="W2">
         <f>Data!AD31</f>
-        <v>0.22960680071243239</v>
+        <v>0.2296050832794225</v>
       </c>
       <c r="X2">
         <f>Data!AE31</f>
-        <v>0.23455949783988159</v>
+        <v>0.23455819750305237</v>
       </c>
       <c r="Y2">
         <f>Data!AF31</f>
-        <v>0.23837160121209131</v>
+        <v>0.23837062191523606</v>
       </c>
       <c r="Z2">
         <f>Data!AG31</f>
-        <v>0.241278263392775</v>
+        <v>0.24127752888328771</v>
       </c>
       <c r="AA2">
         <f>Data!AH31</f>
-        <v>0.24347865569679086</v>
+        <v>0.2434781064954705</v>
       </c>
       <c r="AB2">
         <f>Data!AI31</f>
-        <v>0.24513533496186604</v>
+        <v>0.24513492527939293</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -21839,111 +21867,111 @@
       </c>
       <c r="B3">
         <f>Data!I32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="C3">
         <f>Data!J32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="D3">
         <f>Data!K32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="E3">
         <f>Data!L32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="F3">
         <f>Data!M32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="G3">
         <f>Data!N32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="H3">
         <f>Data!O32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="I3">
         <f>Data!P32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="J3">
         <f>Data!Q32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="K3">
         <f>Data!R32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="L3">
         <f>Data!S32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="M3">
         <f>Data!T32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="N3">
         <f>Data!U32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="O3">
         <f>Data!V32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="P3">
         <f>Data!W32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="Q3">
         <f>Data!X32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="R3">
         <f>Data!Y32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="S3">
         <f>Data!Z32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="T3">
         <f>Data!AA32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="U3">
         <f>Data!AB32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="V3">
         <f>Data!AC32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="W3">
         <f>Data!AD32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="X3">
         <f>Data!AE32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="Y3">
         <f>Data!AF32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="Z3">
         <f>Data!AG32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AA3">
         <f>Data!AH32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
       <c r="AB3">
         <f>Data!AI32</f>
-        <v>2.2159679000000002E-2</v>
+        <v>2.2122091999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -21952,111 +21980,111 @@
       </c>
       <c r="B4">
         <f>Data!I33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="C4">
         <f>Data!J33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="D4">
         <f>Data!K33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="E4">
         <f>Data!L33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="F4">
         <f>Data!M33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="G4">
         <f>Data!N33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="H4">
         <f>Data!O33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="I4">
         <f>Data!P33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="J4">
         <f>Data!Q33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="K4">
         <f>Data!R33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="L4">
         <f>Data!S33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="M4">
         <f>Data!T33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="N4">
         <f>Data!U33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="O4">
         <f>Data!V33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="P4">
         <f>Data!W33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="Q4">
         <f>Data!X33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="R4">
         <f>Data!Y33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="S4">
         <f>Data!Z33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="T4">
         <f>Data!AA33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="U4">
         <f>Data!AB33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="V4">
         <f>Data!AC33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="W4">
         <f>Data!AD33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="X4">
         <f>Data!AE33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="Y4">
         <f>Data!AF33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="Z4">
         <f>Data!AG33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AA4">
         <f>Data!AH33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
       <c r="AB4">
         <f>Data!AI33</f>
-        <v>7.5358100000000002E-4</v>
+        <v>7.5376100000000004E-4</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
